--- a/danhsachisbn.xlsx
+++ b/danhsachisbn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/cào data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1BEFEF6-75ED-7449-B8F6-FBA1F6FB7920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DE398F-D67C-0741-8D1E-207B210D4B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,10 +16,45 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$2058</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$1984</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+  <si>
+    <t>9781789894547</t>
+  </si>
+  <si>
+    <t>9781444939453</t>
+  </si>
+  <si>
+    <t>9780316381251</t>
+  </si>
+  <si>
+    <t>9798339702337</t>
+  </si>
+  <si>
+    <t>9780763692766</t>
+  </si>
+  <si>
+    <t>9781409539117</t>
+  </si>
+  <si>
+    <t>9781803701332</t>
+  </si>
+  <si>
+    <t>9781536213911</t>
+  </si>
+  <si>
+    <t>9780399554520</t>
+  </si>
+  <si>
+    <t>9780399553578</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -27,7 +62,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,6 +143,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -117,12 +159,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -132,7 +189,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -175,6 +232,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -182,7 +242,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 7" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="94">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -279,6 +339,846 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -554,7 +1454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q2058"/>
+  <dimension ref="A1:Q1984"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" style="1" customWidth="1"/>
@@ -575,8 +1475,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="1">
-        <v>9781790000000</v>
+      <c r="A1" s="22" t="s">
+        <v>0</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="8"/>
@@ -587,8 +1487,8 @@
       <c r="N1" s="16"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>9781440000000</v>
+      <c r="A2" s="22" t="s">
+        <v>1</v>
       </c>
       <c r="C2" s="15"/>
       <c r="D2" s="8"/>
@@ -599,8 +1499,8 @@
       <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>9798340000000</v>
+      <c r="A3" s="22" t="s">
+        <v>2</v>
       </c>
       <c r="C3" s="15"/>
       <c r="D3" s="8"/>
@@ -611,8 +1511,8 @@
       <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>9780760000000</v>
+      <c r="A4" s="22" t="s">
+        <v>3</v>
       </c>
       <c r="C4" s="15"/>
       <c r="D4" s="8"/>
@@ -623,8 +1523,8 @@
       <c r="N4" s="16"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>9781410000000</v>
+      <c r="A5" s="22" t="s">
+        <v>4</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="8"/>
@@ -634,8 +1534,8 @@
       <c r="L5" s="15"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>9781800000000</v>
+      <c r="A6" s="22" t="s">
+        <v>5</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="8"/>
@@ -646,8 +1546,8 @@
       <c r="N6" s="16"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>9781540000000</v>
+      <c r="A7" s="22" t="s">
+        <v>6</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="8"/>
@@ -658,8 +1558,8 @@
       <c r="N7" s="16"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>9780010000000</v>
+      <c r="A8" s="22" t="s">
+        <v>7</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="8"/>
@@ -670,511 +1570,927 @@
       <c r="N8" s="16"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>9780400000000</v>
+      <c r="A9" s="22" t="s">
+        <v>8</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="8"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>9780810000000</v>
+      <c r="A10" s="22" t="s">
+        <v>9</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>9780060000000</v>
-      </c>
-      <c r="C11" s="15"/>
+      <c r="A11"/>
       <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>9781250000000</v>
-      </c>
-      <c r="C12" s="15"/>
+      <c r="A12"/>
       <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>9781960000000</v>
-      </c>
-      <c r="C13" s="15"/>
+      <c r="A13"/>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>9780320000000</v>
-      </c>
-      <c r="C14" s="15"/>
+      <c r="A14"/>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>9781470000000</v>
-      </c>
-      <c r="C15" s="15"/>
+      <c r="A15"/>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>9781650000000</v>
-      </c>
-      <c r="C16" s="15"/>
+      <c r="A16"/>
       <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>9781770000000</v>
-      </c>
-      <c r="C17" s="15"/>
+      <c r="A17"/>
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>9780880000000</v>
-      </c>
-      <c r="C18" s="15"/>
+      <c r="A18"/>
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>9781950000000</v>
-      </c>
-      <c r="C19" s="15"/>
+      <c r="A19"/>
       <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>9781430000000</v>
-      </c>
-      <c r="C20" s="15"/>
+      <c r="A20"/>
       <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>9780590000000</v>
-      </c>
-      <c r="C21" s="15"/>
+      <c r="A21"/>
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>9780550000000</v>
-      </c>
-      <c r="C22" s="15"/>
+      <c r="A22"/>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>9781110000000</v>
-      </c>
+      <c r="A23"/>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>9781320000000</v>
-      </c>
+      <c r="A24"/>
       <c r="D24" s="8"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>9780140000000</v>
-      </c>
+      <c r="A25"/>
       <c r="D25" s="8"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>9780380000000</v>
-      </c>
+      <c r="A26"/>
       <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>9780440000000</v>
-      </c>
+      <c r="A27"/>
       <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
-        <v>9780530000000</v>
-      </c>
+      <c r="A28"/>
       <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
-        <v>9780700000000</v>
-      </c>
+      <c r="A29"/>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
-        <v>9780820000000</v>
-      </c>
+      <c r="A30"/>
       <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
-        <v>9789390000000</v>
-      </c>
+      <c r="A31"/>
       <c r="D31" s="8"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
-        <v>9781740000000</v>
-      </c>
+      <c r="A32"/>
       <c r="D32" s="8"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A33"/>
       <c r="D33" s="8"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="D34" s="8"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="D35" s="8"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36"/>
       <c r="D36" s="8"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37"/>
+      <c r="C37" s="2"/>
       <c r="D37" s="8"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E37" s="3"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="2"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="N37" s="20"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="7"/>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38"/>
+      <c r="C38" s="2"/>
       <c r="D38" s="8"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G38"/>
+      <c r="H38" s="2"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="6"/>
+      <c r="N38" s="20"/>
+      <c r="O38" s="3"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="7"/>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39"/>
+      <c r="C39" s="2"/>
       <c r="D39" s="8"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E39" s="3"/>
+      <c r="G39"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+      <c r="Q39" s="7"/>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40"/>
+      <c r="C40" s="2"/>
       <c r="D40" s="8"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E40" s="3"/>
+      <c r="F40" s="9"/>
+      <c r="G40"/>
+      <c r="J40" s="8"/>
+      <c r="K40" s="8"/>
+      <c r="L40" s="8"/>
+      <c r="Q40" s="7"/>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41"/>
+      <c r="C41" s="2"/>
       <c r="D41" s="8"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E41" s="3"/>
+      <c r="G41"/>
+      <c r="J41" s="8"/>
+      <c r="K41" s="8"/>
+      <c r="L41" s="8"/>
+      <c r="Q41" s="7"/>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42"/>
+      <c r="C42" s="2"/>
       <c r="D42" s="8"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E42" s="3"/>
+      <c r="G42"/>
+      <c r="J42" s="8"/>
+      <c r="K42" s="8"/>
+      <c r="L42" s="8"/>
+      <c r="Q42" s="7"/>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43"/>
+      <c r="C43" s="2"/>
       <c r="D43" s="8"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E43" s="3"/>
+      <c r="F43" s="9"/>
+      <c r="G43"/>
+      <c r="J43" s="8"/>
+      <c r="K43" s="8"/>
+      <c r="L43" s="8"/>
+      <c r="Q43" s="7"/>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44"/>
+      <c r="C44" s="2"/>
       <c r="D44" s="8"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E44" s="3"/>
+      <c r="F44" s="9"/>
+      <c r="G44"/>
+      <c r="J44" s="8"/>
+      <c r="K44" s="8"/>
+      <c r="L44" s="8"/>
+      <c r="N44" s="3"/>
+      <c r="Q44" s="7"/>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45"/>
+      <c r="C45" s="2"/>
       <c r="D45" s="8"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F45" s="9"/>
+      <c r="G45"/>
+      <c r="J45" s="8"/>
+      <c r="K45" s="8"/>
+      <c r="L45" s="10"/>
+      <c r="N45" s="21"/>
+      <c r="Q45" s="7"/>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46"/>
+      <c r="C46" s="2"/>
       <c r="D46" s="8"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G46"/>
+      <c r="J46" s="8"/>
+      <c r="K46" s="8"/>
+      <c r="L46" s="10"/>
+      <c r="Q46" s="7"/>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47"/>
+      <c r="C47" s="2"/>
       <c r="D47" s="8"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G47"/>
+      <c r="J47" s="8"/>
+      <c r="K47" s="8"/>
+      <c r="L47" s="10"/>
+      <c r="Q47" s="7"/>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48"/>
+      <c r="C48" s="2"/>
       <c r="D48" s="8"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G48"/>
+      <c r="J48" s="8"/>
+      <c r="K48" s="8"/>
+      <c r="L48" s="10"/>
+      <c r="Q48" s="7"/>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A49"/>
+      <c r="C49" s="2"/>
       <c r="D49" s="8"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G49"/>
+      <c r="J49" s="8"/>
+      <c r="K49" s="8"/>
+      <c r="L49" s="10"/>
+      <c r="N49" s="21"/>
+      <c r="Q49" s="7"/>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50"/>
+      <c r="C50" s="2"/>
       <c r="D50" s="8"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F50" s="9"/>
+      <c r="G50"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="10"/>
+      <c r="Q50" s="7"/>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A51"/>
+      <c r="C51" s="2"/>
       <c r="D51" s="8"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G51"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="Q51" s="7"/>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A52"/>
+      <c r="C52" s="2"/>
       <c r="D52" s="8"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G52"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="Q52" s="7"/>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A53"/>
+      <c r="C53" s="2"/>
       <c r="D53" s="8"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E53" s="11"/>
+      <c r="G53"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="Q53" s="7"/>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A54"/>
+      <c r="C54" s="2"/>
       <c r="D54" s="8"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G54"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="Q54" s="7"/>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A55"/>
+      <c r="C55" s="2"/>
       <c r="D55" s="8"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G55"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="Q55" s="7"/>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A56"/>
+      <c r="C56" s="2"/>
       <c r="D56" s="8"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G56"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="Q56" s="7"/>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A57"/>
+      <c r="C57" s="2"/>
       <c r="D57" s="8"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G57"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="Q57" s="7"/>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A58"/>
+      <c r="C58" s="2"/>
       <c r="D58" s="8"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G58"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="Q58" s="7"/>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A59"/>
+      <c r="C59" s="2"/>
       <c r="D59" s="8"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G59"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="Q59" s="7"/>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A60"/>
+      <c r="C60" s="2"/>
       <c r="D60" s="8"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G60"/>
+      <c r="J60" s="8"/>
+      <c r="K60" s="8"/>
+      <c r="L60" s="8"/>
+      <c r="Q60" s="7"/>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A61"/>
+      <c r="C61" s="2"/>
       <c r="D61" s="8"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E61" s="11"/>
+      <c r="G61"/>
+      <c r="J61" s="8"/>
+      <c r="K61" s="8"/>
+      <c r="L61" s="8"/>
+      <c r="N61" s="21"/>
+      <c r="Q61" s="7"/>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A62"/>
+      <c r="C62" s="2"/>
       <c r="D62" s="8"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G62"/>
+      <c r="J62" s="8"/>
+      <c r="K62" s="8"/>
+      <c r="L62" s="8"/>
+      <c r="Q62" s="7"/>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A63"/>
+      <c r="C63" s="2"/>
       <c r="D63" s="8"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G63"/>
+      <c r="J63" s="8"/>
+      <c r="K63" s="8"/>
+      <c r="L63" s="8"/>
+      <c r="N63" s="21"/>
+      <c r="Q63" s="7"/>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64"/>
+      <c r="C64" s="2"/>
       <c r="D64" s="8"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G64"/>
+      <c r="J64" s="8"/>
+      <c r="K64" s="8"/>
+      <c r="L64" s="8"/>
+      <c r="Q64" s="7"/>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A65"/>
+      <c r="C65" s="2"/>
       <c r="D65" s="8"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="F65" s="9"/>
+      <c r="G65"/>
+      <c r="J65" s="8"/>
+      <c r="K65" s="8"/>
+      <c r="L65" s="8"/>
+      <c r="Q65" s="7"/>
+    </row>
+    <row r="66" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A66"/>
+      <c r="C66" s="2"/>
       <c r="D66" s="8"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E66" s="11"/>
+      <c r="G66"/>
+      <c r="J66" s="8"/>
+      <c r="K66" s="8"/>
+      <c r="L66" s="8"/>
+      <c r="Q66" s="7"/>
+    </row>
+    <row r="67" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A67"/>
+      <c r="C67" s="2"/>
       <c r="D67" s="8"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G67"/>
+      <c r="J67" s="8"/>
+      <c r="K67" s="8"/>
+      <c r="L67" s="8"/>
+      <c r="Q67" s="7"/>
+    </row>
+    <row r="68" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A68"/>
+      <c r="C68" s="2"/>
       <c r="D68" s="8"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G68"/>
+      <c r="J68" s="8"/>
+      <c r="K68" s="8"/>
+      <c r="L68" s="8"/>
+      <c r="Q68" s="7"/>
+    </row>
+    <row r="69" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A69"/>
+      <c r="C69" s="2"/>
       <c r="D69" s="8"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G69"/>
+      <c r="J69" s="8"/>
+      <c r="K69" s="8"/>
+      <c r="L69" s="8"/>
+      <c r="Q69" s="7"/>
+    </row>
+    <row r="70" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A70"/>
+      <c r="C70" s="2"/>
       <c r="D70" s="8"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G70"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+      <c r="Q70" s="7"/>
+    </row>
+    <row r="71" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A71"/>
+      <c r="C71" s="2"/>
       <c r="D71" s="8"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E71" s="11"/>
+      <c r="G71"/>
+      <c r="J71" s="8"/>
+      <c r="K71" s="8"/>
+      <c r="L71" s="8"/>
+      <c r="Q71" s="7"/>
+    </row>
+    <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72"/>
+      <c r="C72" s="2"/>
       <c r="D72" s="8"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G72"/>
+      <c r="J72" s="8"/>
+      <c r="K72" s="8"/>
+      <c r="L72" s="8"/>
+      <c r="Q72" s="7"/>
+    </row>
+    <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73"/>
+      <c r="C73" s="2"/>
       <c r="D73" s="8"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G73"/>
+      <c r="J73" s="8"/>
+      <c r="K73" s="8"/>
+      <c r="L73" s="8"/>
+      <c r="Q73" s="7"/>
+    </row>
+    <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74"/>
+      <c r="C74" s="2"/>
       <c r="D74" s="8"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G74"/>
+      <c r="J74" s="8"/>
+      <c r="K74" s="8"/>
+      <c r="L74" s="8"/>
+      <c r="N74" s="21"/>
+      <c r="Q74" s="7"/>
+    </row>
+    <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75"/>
+      <c r="C75" s="2"/>
       <c r="D75" s="8"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E75" s="11"/>
+      <c r="G75"/>
+      <c r="J75" s="8"/>
+      <c r="K75" s="8"/>
+      <c r="L75" s="8"/>
+      <c r="N75" s="21"/>
+      <c r="Q75" s="7"/>
+    </row>
+    <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76"/>
+      <c r="C76" s="2"/>
       <c r="D76" s="8"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G76"/>
+      <c r="J76" s="8"/>
+      <c r="K76" s="8"/>
+      <c r="L76" s="10"/>
+      <c r="Q76" s="7"/>
+    </row>
+    <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77"/>
+      <c r="C77" s="2"/>
       <c r="D77" s="8"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G77"/>
+      <c r="J77" s="8"/>
+      <c r="K77" s="8"/>
+      <c r="L77" s="10"/>
+      <c r="Q77" s="7"/>
+    </row>
+    <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78"/>
+      <c r="C78" s="2"/>
       <c r="D78" s="8"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G78"/>
+      <c r="J78" s="8"/>
+      <c r="K78" s="8"/>
+      <c r="L78" s="10"/>
+      <c r="N78" s="21"/>
+      <c r="Q78" s="7"/>
+    </row>
+    <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79"/>
+      <c r="C79" s="2"/>
       <c r="D79" s="8"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="E79" s="11"/>
+      <c r="G79"/>
+      <c r="J79" s="8"/>
+      <c r="K79" s="8"/>
+      <c r="L79" s="10"/>
+      <c r="Q79" s="7"/>
+    </row>
+    <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80"/>
+      <c r="C80" s="2"/>
       <c r="D80" s="8"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G80"/>
+      <c r="J80" s="8"/>
+      <c r="K80" s="8"/>
+      <c r="L80" s="8"/>
+      <c r="Q80" s="7"/>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81"/>
+      <c r="C81" s="2"/>
       <c r="D81" s="8"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G81"/>
+      <c r="J81" s="8"/>
+      <c r="K81" s="8"/>
+      <c r="L81" s="8"/>
+      <c r="Q81" s="7"/>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82"/>
+      <c r="C82" s="2"/>
       <c r="D82" s="8"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G82"/>
+      <c r="J82" s="8"/>
+      <c r="K82" s="8"/>
+      <c r="L82" s="8"/>
+      <c r="Q82" s="7"/>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83"/>
+      <c r="C83" s="2"/>
       <c r="D83" s="8"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G83"/>
+      <c r="J83" s="8"/>
+      <c r="K83" s="8"/>
+      <c r="L83" s="8"/>
+      <c r="Q83" s="7"/>
+    </row>
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84"/>
+      <c r="C84" s="2"/>
       <c r="D84" s="8"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G84"/>
+      <c r="J84" s="8"/>
+      <c r="K84" s="8"/>
+      <c r="L84" s="8"/>
+      <c r="Q84" s="7"/>
+    </row>
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85"/>
+      <c r="C85" s="2"/>
       <c r="D85" s="8"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G85"/>
+      <c r="J85" s="8"/>
+      <c r="K85" s="8"/>
+      <c r="L85" s="8"/>
+      <c r="Q85" s="7"/>
+    </row>
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86"/>
+      <c r="C86" s="2"/>
       <c r="D86" s="8"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G86"/>
+      <c r="J86" s="8"/>
+      <c r="K86" s="8"/>
+      <c r="L86" s="8"/>
+      <c r="Q86" s="7"/>
+    </row>
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87"/>
+      <c r="C87" s="2"/>
       <c r="D87" s="8"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G87"/>
+      <c r="J87" s="8"/>
+      <c r="K87" s="8"/>
+      <c r="L87" s="8"/>
+      <c r="Q87" s="7"/>
+    </row>
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88"/>
+      <c r="C88" s="2"/>
       <c r="D88" s="8"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G88"/>
+      <c r="J88" s="8"/>
+      <c r="K88" s="8"/>
+      <c r="L88" s="8"/>
+      <c r="Q88" s="7"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89"/>
+      <c r="C89" s="2"/>
       <c r="D89" s="8"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G89"/>
+      <c r="J89" s="8"/>
+      <c r="K89" s="8"/>
+      <c r="L89" s="8"/>
+      <c r="Q89" s="7"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90"/>
+      <c r="C90" s="2"/>
       <c r="D90" s="8"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G90"/>
+      <c r="J90" s="8"/>
+      <c r="K90" s="8"/>
+      <c r="L90" s="8"/>
+      <c r="Q90" s="7"/>
+    </row>
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91"/>
+      <c r="C91" s="2"/>
       <c r="D91" s="8"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G91"/>
+      <c r="J91" s="8"/>
+      <c r="K91" s="8"/>
+      <c r="L91" s="8"/>
+      <c r="Q91" s="7"/>
+    </row>
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92"/>
+      <c r="C92" s="2"/>
       <c r="D92" s="8"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G92"/>
+      <c r="J92" s="8"/>
+      <c r="K92" s="8"/>
+      <c r="L92" s="8"/>
+      <c r="Q92" s="7"/>
+    </row>
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93"/>
+      <c r="C93" s="2"/>
       <c r="D93" s="8"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G93"/>
+      <c r="J93" s="8"/>
+      <c r="K93" s="8"/>
+      <c r="L93" s="8"/>
+      <c r="Q93" s="7"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94"/>
+      <c r="C94" s="2"/>
       <c r="D94" s="8"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G94"/>
+      <c r="J94" s="8"/>
+      <c r="K94" s="8"/>
+      <c r="L94" s="8"/>
+      <c r="Q94" s="7"/>
+    </row>
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95"/>
+      <c r="C95" s="2"/>
       <c r="D95" s="8"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G95"/>
+      <c r="J95" s="8"/>
+      <c r="K95" s="8"/>
+      <c r="L95" s="8"/>
+      <c r="Q95" s="7"/>
+    </row>
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96"/>
+      <c r="C96" s="2"/>
       <c r="D96" s="8"/>
+      <c r="G96"/>
+      <c r="J96" s="8"/>
+      <c r="K96" s="8"/>
+      <c r="L96" s="8"/>
+      <c r="Q96" s="7"/>
     </row>
     <row r="97" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A97"/>
+      <c r="C97" s="2"/>
       <c r="D97" s="8"/>
+      <c r="G97"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="Q97" s="7"/>
     </row>
     <row r="98" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A98"/>
+      <c r="C98" s="2"/>
       <c r="D98" s="8"/>
+      <c r="G98"/>
+      <c r="J98" s="8"/>
+      <c r="K98" s="8"/>
+      <c r="L98" s="8"/>
+      <c r="Q98" s="7"/>
     </row>
     <row r="99" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A99"/>
+      <c r="C99" s="2"/>
       <c r="D99" s="8"/>
+      <c r="G99"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="Q99" s="7"/>
     </row>
     <row r="100" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A100"/>
+      <c r="C100" s="2"/>
       <c r="D100" s="8"/>
+      <c r="G100"/>
+      <c r="J100" s="8"/>
+      <c r="K100" s="8"/>
+      <c r="L100" s="8"/>
+      <c r="Q100" s="7"/>
     </row>
     <row r="101" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A101"/>
+      <c r="C101" s="2"/>
       <c r="D101" s="8"/>
+      <c r="G101"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="Q101" s="7"/>
     </row>
     <row r="102" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A102"/>
+      <c r="C102" s="2"/>
       <c r="D102" s="8"/>
+      <c r="G102"/>
+      <c r="J102" s="8"/>
+      <c r="K102" s="8"/>
+      <c r="L102" s="8"/>
+      <c r="Q102" s="7"/>
     </row>
     <row r="103" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A103"/>
+      <c r="C103" s="2"/>
       <c r="D103" s="8"/>
+      <c r="G103"/>
+      <c r="J103" s="8"/>
+      <c r="K103" s="8"/>
+      <c r="L103" s="8"/>
+      <c r="Q103" s="7"/>
     </row>
     <row r="104" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A104"/>
+      <c r="C104" s="2"/>
       <c r="D104" s="8"/>
+      <c r="G104"/>
+      <c r="J104" s="8"/>
+      <c r="K104" s="8"/>
+      <c r="L104" s="8"/>
+      <c r="Q104" s="7"/>
     </row>
     <row r="105" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A105"/>
+      <c r="C105" s="2"/>
       <c r="D105" s="8"/>
+      <c r="G105"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="Q105" s="7"/>
     </row>
     <row r="106" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A106"/>
+      <c r="C106" s="2"/>
       <c r="D106" s="8"/>
+      <c r="F106" s="12"/>
+      <c r="G106"/>
+      <c r="J106" s="8"/>
+      <c r="K106" s="8"/>
+      <c r="L106" s="8"/>
+      <c r="Q106" s="7"/>
     </row>
     <row r="107" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A107"/>
+      <c r="C107" s="2"/>
       <c r="D107" s="8"/>
+      <c r="G107"/>
+      <c r="J107" s="8"/>
+      <c r="K107" s="8"/>
+      <c r="L107" s="8"/>
+      <c r="Q107" s="7"/>
     </row>
     <row r="108" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A108"/>
+      <c r="C108" s="2"/>
       <c r="D108" s="8"/>
+      <c r="G108"/>
+      <c r="J108" s="8"/>
+      <c r="K108" s="8"/>
+      <c r="L108" s="8"/>
+      <c r="Q108" s="7"/>
     </row>
     <row r="109" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A109"/>
+      <c r="C109" s="2"/>
       <c r="D109" s="8"/>
+      <c r="G109"/>
+      <c r="J109" s="8"/>
+      <c r="K109" s="8"/>
+      <c r="L109" s="8"/>
+      <c r="Q109" s="7"/>
     </row>
     <row r="110" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A110"/>
+      <c r="C110" s="2"/>
       <c r="D110" s="8"/>
+      <c r="G110"/>
+      <c r="J110" s="8"/>
+      <c r="K110" s="8"/>
+      <c r="L110" s="8"/>
+      <c r="Q110" s="7"/>
     </row>
     <row r="111" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A111"/>
       <c r="C111" s="2"/>
       <c r="D111" s="8"/>
-      <c r="E111" s="3"/>
-      <c r="F111" s="4"/>
-      <c r="G111" s="3"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="6"/>
-      <c r="K111" s="6"/>
-      <c r="L111" s="6"/>
-      <c r="N111" s="20"/>
-      <c r="O111" s="3"/>
-      <c r="P111" s="2"/>
+      <c r="G111"/>
+      <c r="J111" s="8"/>
+      <c r="K111" s="8"/>
+      <c r="L111" s="8"/>
       <c r="Q111" s="7"/>
     </row>
     <row r="112" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A112"/>
       <c r="C112" s="2"/>
       <c r="D112" s="8"/>
+      <c r="F112" s="12"/>
       <c r="G112"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="5"/>
-      <c r="J112" s="6"/>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6"/>
-      <c r="N112" s="20"/>
-      <c r="O112" s="3"/>
-      <c r="P112" s="2"/>
+      <c r="J112" s="8"/>
+      <c r="K112" s="8"/>
+      <c r="L112" s="8"/>
       <c r="Q112" s="7"/>
     </row>
     <row r="113" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A113"/>
       <c r="C113" s="2"/>
       <c r="D113" s="8"/>
-      <c r="E113" s="3"/>
       <c r="G113"/>
       <c r="J113" s="8"/>
       <c r="K113" s="8"/>
@@ -1183,14 +2499,19 @@
     </row>
     <row r="114" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A114"/>
-      <c r="C114" s="2"/>
+      <c r="C114" s="13"/>
       <c r="D114" s="8"/>
       <c r="E114" s="3"/>
-      <c r="F114" s="9"/>
-      <c r="G114"/>
-      <c r="J114" s="8"/>
-      <c r="K114" s="8"/>
-      <c r="L114" s="8"/>
+      <c r="F114" s="4"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="2"/>
+      <c r="I114" s="5"/>
+      <c r="J114" s="6"/>
+      <c r="K114" s="6"/>
+      <c r="L114" s="6"/>
+      <c r="N114" s="20"/>
+      <c r="O114" s="3"/>
+      <c r="P114" s="2"/>
       <c r="Q114" s="7"/>
     </row>
     <row r="115" spans="1:17" x14ac:dyDescent="0.2">
@@ -1199,17 +2520,23 @@
       <c r="D115" s="8"/>
       <c r="E115" s="3"/>
       <c r="G115"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-      <c r="L115" s="8"/>
+      <c r="H115" s="2"/>
+      <c r="I115" s="5"/>
+      <c r="J115" s="6"/>
+      <c r="K115" s="6"/>
+      <c r="L115" s="6"/>
+      <c r="N115" s="20"/>
+      <c r="O115" s="3"/>
+      <c r="P115" s="2"/>
       <c r="Q115" s="7"/>
     </row>
     <row r="116" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A116"/>
-      <c r="C116" s="2"/>
+      <c r="C116" s="13"/>
       <c r="D116" s="8"/>
       <c r="E116" s="3"/>
       <c r="G116"/>
+      <c r="I116" s="5"/>
       <c r="J116" s="8"/>
       <c r="K116" s="8"/>
       <c r="L116" s="8"/>
@@ -1222,6 +2549,7 @@
       <c r="E117" s="3"/>
       <c r="F117" s="9"/>
       <c r="G117"/>
+      <c r="I117" s="5"/>
       <c r="J117" s="8"/>
       <c r="K117" s="8"/>
       <c r="L117" s="8"/>
@@ -1232,51 +2560,60 @@
       <c r="C118" s="2"/>
       <c r="D118" s="8"/>
       <c r="E118" s="3"/>
-      <c r="F118" s="9"/>
       <c r="G118"/>
+      <c r="I118" s="5"/>
       <c r="J118" s="8"/>
       <c r="K118" s="8"/>
       <c r="L118" s="8"/>
-      <c r="N118" s="3"/>
       <c r="Q118" s="7"/>
     </row>
     <row r="119" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A119"/>
       <c r="C119" s="2"/>
       <c r="D119" s="8"/>
-      <c r="F119" s="9"/>
+      <c r="E119" s="3"/>
       <c r="G119"/>
+      <c r="I119" s="5"/>
       <c r="J119" s="8"/>
       <c r="K119" s="8"/>
-      <c r="L119" s="10"/>
-      <c r="N119" s="21"/>
+      <c r="L119" s="8"/>
       <c r="Q119" s="7"/>
     </row>
     <row r="120" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A120"/>
       <c r="C120" s="2"/>
       <c r="D120" s="8"/>
-      <c r="G120"/>
+      <c r="E120" s="3"/>
+      <c r="F120" s="4"/>
+      <c r="G120" s="3"/>
+      <c r="I120" s="5"/>
       <c r="J120" s="8"/>
       <c r="K120" s="8"/>
-      <c r="L120" s="10"/>
+      <c r="L120" s="8"/>
+      <c r="N120" s="20"/>
+      <c r="O120" s="3"/>
       <c r="Q120" s="7"/>
     </row>
     <row r="121" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A121"/>
       <c r="C121" s="2"/>
       <c r="D121" s="8"/>
+      <c r="E121" s="3"/>
       <c r="G121"/>
+      <c r="I121" s="5"/>
       <c r="J121" s="8"/>
       <c r="K121" s="8"/>
-      <c r="L121" s="10"/>
+      <c r="L121" s="8"/>
       <c r="Q121" s="7"/>
     </row>
     <row r="122" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A122"/>
       <c r="C122" s="2"/>
       <c r="D122" s="8"/>
+      <c r="E122" s="3"/>
+      <c r="F122" s="9"/>
       <c r="G122"/>
+      <c r="I122" s="5"/>
       <c r="J122" s="8"/>
       <c r="K122" s="8"/>
       <c r="L122" s="10"/>
@@ -1286,19 +2623,21 @@
       <c r="A123"/>
       <c r="C123" s="2"/>
       <c r="D123" s="8"/>
+      <c r="E123" s="3"/>
       <c r="G123"/>
+      <c r="I123" s="5"/>
       <c r="J123" s="8"/>
       <c r="K123" s="8"/>
       <c r="L123" s="10"/>
-      <c r="N123" s="21"/>
       <c r="Q123" s="7"/>
     </row>
     <row r="124" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A124"/>
       <c r="C124" s="2"/>
       <c r="D124" s="8"/>
-      <c r="F124" s="9"/>
+      <c r="E124" s="3"/>
       <c r="G124"/>
+      <c r="I124" s="5"/>
       <c r="J124" s="8"/>
       <c r="K124" s="8"/>
       <c r="L124" s="10"/>
@@ -1306,831 +2645,337 @@
     </row>
     <row r="125" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A125"/>
-      <c r="C125" s="2"/>
       <c r="D125" s="8"/>
-      <c r="G125"/>
-      <c r="J125" s="8"/>
-      <c r="K125" s="8"/>
-      <c r="L125" s="8"/>
-      <c r="Q125" s="7"/>
     </row>
     <row r="126" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A126"/>
-      <c r="C126" s="2"/>
       <c r="D126" s="8"/>
-      <c r="G126"/>
-      <c r="J126" s="8"/>
-      <c r="K126" s="8"/>
-      <c r="L126" s="8"/>
-      <c r="Q126" s="7"/>
     </row>
     <row r="127" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A127"/>
-      <c r="C127" s="2"/>
       <c r="D127" s="8"/>
-      <c r="E127" s="11"/>
-      <c r="G127"/>
-      <c r="J127" s="8"/>
-      <c r="K127" s="8"/>
-      <c r="L127" s="8"/>
-      <c r="Q127" s="7"/>
     </row>
     <row r="128" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A128"/>
-      <c r="C128" s="2"/>
       <c r="D128" s="8"/>
-      <c r="G128"/>
-      <c r="J128" s="8"/>
-      <c r="K128" s="8"/>
-      <c r="L128" s="8"/>
-      <c r="Q128" s="7"/>
-    </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A129"/>
-      <c r="C129" s="2"/>
       <c r="D129" s="8"/>
-      <c r="G129"/>
-      <c r="J129" s="8"/>
-      <c r="K129" s="8"/>
-      <c r="L129" s="8"/>
-      <c r="Q129" s="7"/>
-    </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A130"/>
-      <c r="C130" s="2"/>
       <c r="D130" s="8"/>
-      <c r="G130"/>
-      <c r="J130" s="8"/>
-      <c r="K130" s="8"/>
-      <c r="L130" s="8"/>
-      <c r="Q130" s="7"/>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A131"/>
-      <c r="C131" s="2"/>
       <c r="D131" s="8"/>
-      <c r="G131"/>
-      <c r="J131" s="8"/>
-      <c r="K131" s="8"/>
-      <c r="L131" s="8"/>
-      <c r="Q131" s="7"/>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A132"/>
-      <c r="C132" s="2"/>
       <c r="D132" s="8"/>
-      <c r="G132"/>
-      <c r="J132" s="8"/>
-      <c r="K132" s="8"/>
-      <c r="L132" s="8"/>
-      <c r="Q132" s="7"/>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A133"/>
-      <c r="C133" s="2"/>
       <c r="D133" s="8"/>
-      <c r="G133"/>
-      <c r="J133" s="8"/>
-      <c r="K133" s="8"/>
-      <c r="L133" s="8"/>
-      <c r="Q133" s="7"/>
-    </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A134"/>
-      <c r="C134" s="2"/>
       <c r="D134" s="8"/>
-      <c r="G134"/>
-      <c r="J134" s="8"/>
-      <c r="K134" s="8"/>
-      <c r="L134" s="8"/>
-      <c r="Q134" s="7"/>
-    </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A135"/>
-      <c r="C135" s="2"/>
       <c r="D135" s="8"/>
-      <c r="E135" s="11"/>
-      <c r="G135"/>
-      <c r="J135" s="8"/>
-      <c r="K135" s="8"/>
-      <c r="L135" s="8"/>
-      <c r="N135" s="21"/>
-      <c r="Q135" s="7"/>
-    </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A136"/>
-      <c r="C136" s="2"/>
       <c r="D136" s="8"/>
-      <c r="G136"/>
-      <c r="J136" s="8"/>
-      <c r="K136" s="8"/>
-      <c r="L136" s="8"/>
-      <c r="Q136" s="7"/>
-    </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A137"/>
-      <c r="C137" s="2"/>
       <c r="D137" s="8"/>
-      <c r="G137"/>
-      <c r="J137" s="8"/>
-      <c r="K137" s="8"/>
-      <c r="L137" s="8"/>
-      <c r="N137" s="21"/>
-      <c r="Q137" s="7"/>
-    </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A138"/>
-      <c r="C138" s="2"/>
       <c r="D138" s="8"/>
-      <c r="G138"/>
-      <c r="J138" s="8"/>
-      <c r="K138" s="8"/>
-      <c r="L138" s="8"/>
-      <c r="Q138" s="7"/>
-    </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A139"/>
-      <c r="C139" s="2"/>
       <c r="D139" s="8"/>
-      <c r="F139" s="9"/>
-      <c r="G139"/>
-      <c r="J139" s="8"/>
-      <c r="K139" s="8"/>
-      <c r="L139" s="8"/>
-      <c r="Q139" s="7"/>
-    </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A140"/>
-      <c r="C140" s="2"/>
       <c r="D140" s="8"/>
-      <c r="E140" s="11"/>
-      <c r="G140"/>
-      <c r="J140" s="8"/>
-      <c r="K140" s="8"/>
-      <c r="L140" s="8"/>
-      <c r="Q140" s="7"/>
-    </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A141"/>
-      <c r="C141" s="2"/>
       <c r="D141" s="8"/>
-      <c r="G141"/>
-      <c r="J141" s="8"/>
-      <c r="K141" s="8"/>
-      <c r="L141" s="8"/>
-      <c r="Q141" s="7"/>
-    </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A142"/>
-      <c r="C142" s="2"/>
       <c r="D142" s="8"/>
-      <c r="G142"/>
-      <c r="J142" s="8"/>
-      <c r="K142" s="8"/>
-      <c r="L142" s="8"/>
-      <c r="Q142" s="7"/>
-    </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A143"/>
-      <c r="C143" s="2"/>
       <c r="D143" s="8"/>
-      <c r="G143"/>
-      <c r="J143" s="8"/>
-      <c r="K143" s="8"/>
-      <c r="L143" s="8"/>
-      <c r="Q143" s="7"/>
-    </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A144"/>
-      <c r="C144" s="2"/>
       <c r="D144" s="8"/>
-      <c r="G144"/>
-      <c r="J144" s="8"/>
-      <c r="K144" s="8"/>
-      <c r="L144" s="8"/>
-      <c r="Q144" s="7"/>
-    </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A145"/>
-      <c r="C145" s="2"/>
       <c r="D145" s="8"/>
-      <c r="E145" s="11"/>
-      <c r="G145"/>
-      <c r="J145" s="8"/>
-      <c r="K145" s="8"/>
-      <c r="L145" s="8"/>
-      <c r="Q145" s="7"/>
-    </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A146"/>
-      <c r="C146" s="2"/>
       <c r="D146" s="8"/>
-      <c r="G146"/>
-      <c r="J146" s="8"/>
-      <c r="K146" s="8"/>
-      <c r="L146" s="8"/>
-      <c r="Q146" s="7"/>
-    </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A147"/>
-      <c r="C147" s="2"/>
       <c r="D147" s="8"/>
-      <c r="G147"/>
-      <c r="J147" s="8"/>
-      <c r="K147" s="8"/>
-      <c r="L147" s="8"/>
-      <c r="Q147" s="7"/>
-    </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A148"/>
-      <c r="C148" s="2"/>
       <c r="D148" s="8"/>
-      <c r="G148"/>
-      <c r="J148" s="8"/>
-      <c r="K148" s="8"/>
-      <c r="L148" s="8"/>
-      <c r="N148" s="21"/>
-      <c r="Q148" s="7"/>
-    </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A149"/>
-      <c r="C149" s="2"/>
       <c r="D149" s="8"/>
-      <c r="E149" s="11"/>
-      <c r="G149"/>
-      <c r="J149" s="8"/>
-      <c r="K149" s="8"/>
-      <c r="L149" s="8"/>
-      <c r="N149" s="21"/>
-      <c r="Q149" s="7"/>
-    </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A150"/>
-      <c r="C150" s="2"/>
       <c r="D150" s="8"/>
-      <c r="G150"/>
-      <c r="J150" s="8"/>
-      <c r="K150" s="8"/>
-      <c r="L150" s="10"/>
-      <c r="Q150" s="7"/>
-    </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A151"/>
-      <c r="C151" s="2"/>
       <c r="D151" s="8"/>
-      <c r="G151"/>
-      <c r="J151" s="8"/>
-      <c r="K151" s="8"/>
-      <c r="L151" s="10"/>
-      <c r="Q151" s="7"/>
-    </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A152"/>
-      <c r="C152" s="2"/>
       <c r="D152" s="8"/>
-      <c r="G152"/>
-      <c r="J152" s="8"/>
-      <c r="K152" s="8"/>
-      <c r="L152" s="10"/>
-      <c r="N152" s="21"/>
-      <c r="Q152" s="7"/>
-    </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A153"/>
-      <c r="C153" s="2"/>
       <c r="D153" s="8"/>
-      <c r="E153" s="11"/>
-      <c r="G153"/>
-      <c r="J153" s="8"/>
-      <c r="K153" s="8"/>
-      <c r="L153" s="10"/>
-      <c r="Q153" s="7"/>
-    </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A154"/>
-      <c r="C154" s="2"/>
       <c r="D154" s="8"/>
-      <c r="G154"/>
-      <c r="J154" s="8"/>
-      <c r="K154" s="8"/>
-      <c r="L154" s="8"/>
-      <c r="Q154" s="7"/>
-    </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A155"/>
-      <c r="C155" s="2"/>
       <c r="D155" s="8"/>
-      <c r="G155"/>
-      <c r="J155" s="8"/>
-      <c r="K155" s="8"/>
-      <c r="L155" s="8"/>
-      <c r="Q155" s="7"/>
-    </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A156"/>
-      <c r="C156" s="2"/>
       <c r="D156" s="8"/>
-      <c r="G156"/>
-      <c r="J156" s="8"/>
-      <c r="K156" s="8"/>
-      <c r="L156" s="8"/>
-      <c r="Q156" s="7"/>
-    </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A157"/>
-      <c r="C157" s="2"/>
       <c r="D157" s="8"/>
-      <c r="G157"/>
-      <c r="J157" s="8"/>
-      <c r="K157" s="8"/>
-      <c r="L157" s="8"/>
-      <c r="Q157" s="7"/>
-    </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A158"/>
-      <c r="C158" s="2"/>
       <c r="D158" s="8"/>
-      <c r="G158"/>
-      <c r="J158" s="8"/>
-      <c r="K158" s="8"/>
-      <c r="L158" s="8"/>
-      <c r="Q158" s="7"/>
-    </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A159"/>
-      <c r="C159" s="2"/>
       <c r="D159" s="8"/>
-      <c r="G159"/>
-      <c r="J159" s="8"/>
-      <c r="K159" s="8"/>
-      <c r="L159" s="8"/>
-      <c r="Q159" s="7"/>
-    </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A160"/>
-      <c r="C160" s="2"/>
       <c r="D160" s="8"/>
-      <c r="G160"/>
-      <c r="J160" s="8"/>
-      <c r="K160" s="8"/>
-      <c r="L160" s="8"/>
-      <c r="Q160" s="7"/>
-    </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A161"/>
-      <c r="C161" s="2"/>
       <c r="D161" s="8"/>
-      <c r="G161"/>
-      <c r="J161" s="8"/>
-      <c r="K161" s="8"/>
-      <c r="L161" s="8"/>
-      <c r="Q161" s="7"/>
-    </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A162"/>
-      <c r="C162" s="2"/>
       <c r="D162" s="8"/>
-      <c r="G162"/>
-      <c r="J162" s="8"/>
-      <c r="K162" s="8"/>
-      <c r="L162" s="8"/>
-      <c r="Q162" s="7"/>
-    </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A163"/>
-      <c r="C163" s="2"/>
       <c r="D163" s="8"/>
-      <c r="G163"/>
-      <c r="J163" s="8"/>
-      <c r="K163" s="8"/>
-      <c r="L163" s="8"/>
-      <c r="Q163" s="7"/>
-    </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A164"/>
-      <c r="C164" s="2"/>
       <c r="D164" s="8"/>
-      <c r="G164"/>
-      <c r="J164" s="8"/>
-      <c r="K164" s="8"/>
-      <c r="L164" s="8"/>
-      <c r="Q164" s="7"/>
-    </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A165"/>
-      <c r="C165" s="2"/>
       <c r="D165" s="8"/>
-      <c r="G165"/>
-      <c r="J165" s="8"/>
-      <c r="K165" s="8"/>
-      <c r="L165" s="8"/>
-      <c r="Q165" s="7"/>
-    </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A166"/>
-      <c r="C166" s="2"/>
       <c r="D166" s="8"/>
-      <c r="G166"/>
-      <c r="J166" s="8"/>
-      <c r="K166" s="8"/>
-      <c r="L166" s="8"/>
-      <c r="Q166" s="7"/>
-    </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A167"/>
-      <c r="C167" s="2"/>
       <c r="D167" s="8"/>
-      <c r="G167"/>
-      <c r="J167" s="8"/>
-      <c r="K167" s="8"/>
-      <c r="L167" s="8"/>
-      <c r="Q167" s="7"/>
-    </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A168"/>
-      <c r="C168" s="2"/>
       <c r="D168" s="8"/>
-      <c r="G168"/>
-      <c r="J168" s="8"/>
-      <c r="K168" s="8"/>
-      <c r="L168" s="8"/>
-      <c r="Q168" s="7"/>
-    </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A169"/>
-      <c r="C169" s="2"/>
       <c r="D169" s="8"/>
-      <c r="G169"/>
-      <c r="J169" s="8"/>
-      <c r="K169" s="8"/>
-      <c r="L169" s="8"/>
-      <c r="Q169" s="7"/>
-    </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A170"/>
-      <c r="C170" s="2"/>
       <c r="D170" s="8"/>
-      <c r="G170"/>
-      <c r="J170" s="8"/>
-      <c r="K170" s="8"/>
-      <c r="L170" s="8"/>
-      <c r="Q170" s="7"/>
-    </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A171"/>
-      <c r="C171" s="2"/>
       <c r="D171" s="8"/>
-      <c r="G171"/>
-      <c r="J171" s="8"/>
-      <c r="K171" s="8"/>
-      <c r="L171" s="8"/>
-      <c r="Q171" s="7"/>
-    </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A172"/>
-      <c r="C172" s="2"/>
       <c r="D172" s="8"/>
-      <c r="G172"/>
-      <c r="J172" s="8"/>
-      <c r="K172" s="8"/>
-      <c r="L172" s="8"/>
-      <c r="Q172" s="7"/>
-    </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A173"/>
-      <c r="C173" s="2"/>
       <c r="D173" s="8"/>
-      <c r="G173"/>
-      <c r="J173" s="8"/>
-      <c r="K173" s="8"/>
-      <c r="L173" s="8"/>
-      <c r="Q173" s="7"/>
-    </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A174"/>
-      <c r="C174" s="2"/>
       <c r="D174" s="8"/>
-      <c r="G174"/>
-      <c r="J174" s="8"/>
-      <c r="K174" s="8"/>
-      <c r="L174" s="8"/>
-      <c r="Q174" s="7"/>
-    </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A175"/>
-      <c r="C175" s="2"/>
       <c r="D175" s="8"/>
-      <c r="G175"/>
-      <c r="J175" s="8"/>
-      <c r="K175" s="8"/>
-      <c r="L175" s="8"/>
-      <c r="Q175" s="7"/>
-    </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A176"/>
-      <c r="C176" s="2"/>
       <c r="D176" s="8"/>
-      <c r="G176"/>
-      <c r="J176" s="8"/>
-      <c r="K176" s="8"/>
-      <c r="L176" s="8"/>
-      <c r="Q176" s="7"/>
-    </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A177"/>
-      <c r="C177" s="2"/>
       <c r="D177" s="8"/>
-      <c r="G177"/>
-      <c r="J177" s="8"/>
-      <c r="K177" s="8"/>
-      <c r="L177" s="8"/>
-      <c r="Q177" s="7"/>
-    </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A178"/>
-      <c r="C178" s="2"/>
       <c r="D178" s="8"/>
-      <c r="G178"/>
-      <c r="J178" s="8"/>
-      <c r="K178" s="8"/>
-      <c r="L178" s="8"/>
-      <c r="Q178" s="7"/>
-    </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A179"/>
-      <c r="C179" s="2"/>
       <c r="D179" s="8"/>
-      <c r="G179"/>
-      <c r="J179" s="8"/>
-      <c r="K179" s="8"/>
-      <c r="L179" s="8"/>
-      <c r="Q179" s="7"/>
-    </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A180"/>
-      <c r="C180" s="2"/>
       <c r="D180" s="8"/>
-      <c r="F180" s="12"/>
-      <c r="G180"/>
-      <c r="J180" s="8"/>
-      <c r="K180" s="8"/>
-      <c r="L180" s="8"/>
-      <c r="Q180" s="7"/>
-    </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A181"/>
-      <c r="C181" s="2"/>
       <c r="D181" s="8"/>
-      <c r="G181"/>
-      <c r="J181" s="8"/>
-      <c r="K181" s="8"/>
-      <c r="L181" s="8"/>
-      <c r="Q181" s="7"/>
-    </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A182"/>
-      <c r="C182" s="2"/>
       <c r="D182" s="8"/>
-      <c r="G182"/>
-      <c r="J182" s="8"/>
-      <c r="K182" s="8"/>
-      <c r="L182" s="8"/>
-      <c r="Q182" s="7"/>
-    </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A183"/>
-      <c r="C183" s="2"/>
       <c r="D183" s="8"/>
-      <c r="G183"/>
-      <c r="J183" s="8"/>
-      <c r="K183" s="8"/>
-      <c r="L183" s="8"/>
-      <c r="Q183" s="7"/>
-    </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A184"/>
-      <c r="C184" s="2"/>
       <c r="D184" s="8"/>
-      <c r="G184"/>
-      <c r="J184" s="8"/>
-      <c r="K184" s="8"/>
-      <c r="L184" s="8"/>
-      <c r="Q184" s="7"/>
-    </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A185"/>
-      <c r="C185" s="2"/>
       <c r="D185" s="8"/>
-      <c r="G185"/>
-      <c r="J185" s="8"/>
-      <c r="K185" s="8"/>
-      <c r="L185" s="8"/>
-      <c r="Q185" s="7"/>
-    </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A186"/>
-      <c r="C186" s="2"/>
       <c r="D186" s="8"/>
-      <c r="F186" s="12"/>
-      <c r="G186"/>
-      <c r="J186" s="8"/>
-      <c r="K186" s="8"/>
-      <c r="L186" s="8"/>
-      <c r="Q186" s="7"/>
-    </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A187"/>
-      <c r="C187" s="2"/>
       <c r="D187" s="8"/>
-      <c r="G187"/>
-      <c r="J187" s="8"/>
-      <c r="K187" s="8"/>
-      <c r="L187" s="8"/>
-      <c r="Q187" s="7"/>
-    </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A188"/>
-      <c r="C188" s="13"/>
       <c r="D188" s="8"/>
-      <c r="E188" s="3"/>
-      <c r="F188" s="4"/>
-      <c r="G188" s="3"/>
-      <c r="H188" s="2"/>
-      <c r="I188" s="5"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
-      <c r="N188" s="20"/>
-      <c r="O188" s="3"/>
-      <c r="P188" s="2"/>
-      <c r="Q188" s="7"/>
-    </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A189"/>
-      <c r="C189" s="2"/>
       <c r="D189" s="8"/>
-      <c r="E189" s="3"/>
-      <c r="G189"/>
-      <c r="H189" s="2"/>
-      <c r="I189" s="5"/>
-      <c r="J189" s="6"/>
-      <c r="K189" s="6"/>
-      <c r="L189" s="6"/>
-      <c r="N189" s="20"/>
-      <c r="O189" s="3"/>
-      <c r="P189" s="2"/>
-      <c r="Q189" s="7"/>
-    </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A190"/>
-      <c r="C190" s="13"/>
       <c r="D190" s="8"/>
-      <c r="E190" s="3"/>
-      <c r="G190"/>
-      <c r="I190" s="5"/>
-      <c r="J190" s="8"/>
-      <c r="K190" s="8"/>
-      <c r="L190" s="8"/>
-      <c r="Q190" s="7"/>
-    </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A191"/>
-      <c r="C191" s="2"/>
       <c r="D191" s="8"/>
-      <c r="E191" s="3"/>
-      <c r="F191" s="9"/>
-      <c r="G191"/>
-      <c r="I191" s="5"/>
-      <c r="J191" s="8"/>
-      <c r="K191" s="8"/>
-      <c r="L191" s="8"/>
-      <c r="Q191" s="7"/>
-    </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A192"/>
-      <c r="C192" s="2"/>
       <c r="D192" s="8"/>
-      <c r="E192" s="3"/>
-      <c r="G192"/>
-      <c r="I192" s="5"/>
-      <c r="J192" s="8"/>
-      <c r="K192" s="8"/>
-      <c r="L192" s="8"/>
-      <c r="Q192" s="7"/>
-    </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A193"/>
-      <c r="C193" s="2"/>
       <c r="D193" s="8"/>
-      <c r="E193" s="3"/>
-      <c r="G193"/>
-      <c r="I193" s="5"/>
-      <c r="J193" s="8"/>
-      <c r="K193" s="8"/>
-      <c r="L193" s="8"/>
-      <c r="Q193" s="7"/>
-    </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A194"/>
-      <c r="C194" s="2"/>
       <c r="D194" s="8"/>
-      <c r="E194" s="3"/>
-      <c r="F194" s="4"/>
-      <c r="G194" s="3"/>
-      <c r="I194" s="5"/>
-      <c r="J194" s="8"/>
-      <c r="K194" s="8"/>
-      <c r="L194" s="8"/>
-      <c r="N194" s="20"/>
-      <c r="O194" s="3"/>
-      <c r="Q194" s="7"/>
-    </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A195"/>
-      <c r="C195" s="2"/>
       <c r="D195" s="8"/>
-      <c r="E195" s="3"/>
-      <c r="G195"/>
-      <c r="I195" s="5"/>
-      <c r="J195" s="8"/>
-      <c r="K195" s="8"/>
-      <c r="L195" s="8"/>
-      <c r="Q195" s="7"/>
-    </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A196"/>
-      <c r="C196" s="2"/>
       <c r="D196" s="8"/>
-      <c r="E196" s="3"/>
-      <c r="F196" s="9"/>
-      <c r="G196"/>
-      <c r="I196" s="5"/>
-      <c r="J196" s="8"/>
-      <c r="K196" s="8"/>
-      <c r="L196" s="10"/>
-      <c r="Q196" s="7"/>
-    </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A197"/>
-      <c r="C197" s="2"/>
       <c r="D197" s="8"/>
-      <c r="E197" s="3"/>
-      <c r="G197"/>
-      <c r="I197" s="5"/>
-      <c r="J197" s="8"/>
-      <c r="K197" s="8"/>
-      <c r="L197" s="10"/>
-      <c r="Q197" s="7"/>
-    </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A198"/>
-      <c r="C198" s="2"/>
       <c r="D198" s="8"/>
-      <c r="E198" s="3"/>
-      <c r="G198"/>
-      <c r="I198" s="5"/>
-      <c r="J198" s="8"/>
-      <c r="K198" s="8"/>
-      <c r="L198" s="10"/>
-      <c r="Q198" s="7"/>
-    </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A199"/>
       <c r="D199" s="8"/>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A200"/>
       <c r="D200" s="8"/>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A201"/>
       <c r="D201" s="8"/>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A202"/>
       <c r="D202" s="8"/>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A203"/>
       <c r="D203" s="8"/>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A204"/>
       <c r="D204" s="8"/>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A205"/>
       <c r="D205" s="8"/>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A206"/>
       <c r="D206" s="8"/>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A207"/>
       <c r="D207" s="8"/>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A208"/>
       <c r="D208" s="8"/>
     </row>
@@ -9238,332 +10083,66 @@
       <c r="A1984"/>
       <c r="D1984" s="8"/>
     </row>
-    <row r="1985" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1985"/>
-      <c r="D1985" s="8"/>
-    </row>
-    <row r="1986" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1986"/>
-      <c r="D1986" s="8"/>
-    </row>
-    <row r="1987" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1987"/>
-      <c r="D1987" s="8"/>
-    </row>
-    <row r="1988" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1988"/>
-      <c r="D1988" s="8"/>
-    </row>
-    <row r="1989" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1989"/>
-      <c r="D1989" s="8"/>
-    </row>
-    <row r="1990" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1990"/>
-      <c r="D1990" s="8"/>
-    </row>
-    <row r="1991" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1991"/>
-      <c r="D1991" s="8"/>
-    </row>
-    <row r="1992" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1992"/>
-      <c r="D1992" s="8"/>
-    </row>
-    <row r="1993" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1993"/>
-      <c r="D1993" s="8"/>
-    </row>
-    <row r="1994" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1994"/>
-      <c r="D1994" s="8"/>
-    </row>
-    <row r="1995" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1995"/>
-      <c r="D1995" s="8"/>
-    </row>
-    <row r="1996" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1996"/>
-      <c r="D1996" s="8"/>
-    </row>
-    <row r="1997" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1997"/>
-      <c r="D1997" s="8"/>
-    </row>
-    <row r="1998" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1998"/>
-      <c r="D1998" s="8"/>
-    </row>
-    <row r="1999" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1999"/>
-      <c r="D1999" s="8"/>
-    </row>
-    <row r="2000" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2000"/>
-      <c r="D2000" s="8"/>
-    </row>
-    <row r="2001" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2001"/>
-      <c r="D2001" s="8"/>
-    </row>
-    <row r="2002" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2002"/>
-      <c r="D2002" s="8"/>
-    </row>
-    <row r="2003" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2003"/>
-      <c r="D2003" s="8"/>
-    </row>
-    <row r="2004" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2004"/>
-      <c r="D2004" s="8"/>
-    </row>
-    <row r="2005" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2005"/>
-      <c r="D2005" s="8"/>
-    </row>
-    <row r="2006" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2006"/>
-      <c r="D2006" s="8"/>
-    </row>
-    <row r="2007" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2007"/>
-      <c r="D2007" s="8"/>
-    </row>
-    <row r="2008" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2008"/>
-      <c r="D2008" s="8"/>
-    </row>
-    <row r="2009" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2009"/>
-      <c r="D2009" s="8"/>
-    </row>
-    <row r="2010" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2010"/>
-      <c r="D2010" s="8"/>
-    </row>
-    <row r="2011" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2011"/>
-      <c r="D2011" s="8"/>
-    </row>
-    <row r="2012" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2012"/>
-      <c r="D2012" s="8"/>
-    </row>
-    <row r="2013" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2013"/>
-      <c r="D2013" s="8"/>
-    </row>
-    <row r="2014" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2014"/>
-      <c r="D2014" s="8"/>
-    </row>
-    <row r="2015" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2015"/>
-      <c r="D2015" s="8"/>
-    </row>
-    <row r="2016" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2016"/>
-      <c r="D2016" s="8"/>
-    </row>
-    <row r="2017" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2017"/>
-      <c r="D2017" s="8"/>
-    </row>
-    <row r="2018" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2018"/>
-      <c r="D2018" s="8"/>
-    </row>
-    <row r="2019" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2019"/>
-      <c r="D2019" s="8"/>
-    </row>
-    <row r="2020" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2020"/>
-      <c r="D2020" s="8"/>
-    </row>
-    <row r="2021" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2021"/>
-      <c r="D2021" s="8"/>
-    </row>
-    <row r="2022" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2022"/>
-      <c r="D2022" s="8"/>
-    </row>
-    <row r="2023" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2023"/>
-      <c r="D2023" s="8"/>
-    </row>
-    <row r="2024" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2024"/>
-      <c r="D2024" s="8"/>
-    </row>
-    <row r="2025" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2025"/>
-      <c r="D2025" s="8"/>
-    </row>
-    <row r="2026" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2026"/>
-      <c r="D2026" s="8"/>
-    </row>
-    <row r="2027" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2027"/>
-      <c r="D2027" s="8"/>
-    </row>
-    <row r="2028" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2028"/>
-      <c r="D2028" s="8"/>
-    </row>
-    <row r="2029" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2029"/>
-      <c r="D2029" s="8"/>
-    </row>
-    <row r="2030" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2030"/>
-      <c r="D2030" s="8"/>
-    </row>
-    <row r="2031" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2031"/>
-      <c r="D2031" s="8"/>
-    </row>
-    <row r="2032" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2032"/>
-      <c r="D2032" s="8"/>
-    </row>
-    <row r="2033" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2033"/>
-      <c r="D2033" s="8"/>
-    </row>
-    <row r="2034" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2034"/>
-      <c r="D2034" s="8"/>
-    </row>
-    <row r="2035" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2035"/>
-      <c r="D2035" s="8"/>
-    </row>
-    <row r="2036" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2036"/>
-      <c r="D2036" s="8"/>
-    </row>
-    <row r="2037" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2037"/>
-      <c r="D2037" s="8"/>
-    </row>
-    <row r="2038" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2038"/>
-      <c r="D2038" s="8"/>
-    </row>
-    <row r="2039" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2039"/>
-      <c r="D2039" s="8"/>
-    </row>
-    <row r="2040" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2040"/>
-      <c r="D2040" s="8"/>
-    </row>
-    <row r="2041" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2041"/>
-      <c r="D2041" s="8"/>
-    </row>
-    <row r="2042" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2042"/>
-      <c r="D2042" s="8"/>
-    </row>
-    <row r="2043" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2043"/>
-      <c r="D2043" s="8"/>
-    </row>
-    <row r="2044" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2044"/>
-      <c r="D2044" s="8"/>
-    </row>
-    <row r="2045" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2045"/>
-      <c r="D2045" s="8"/>
-    </row>
-    <row r="2046" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2046"/>
-      <c r="D2046" s="8"/>
-    </row>
-    <row r="2047" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2047"/>
-      <c r="D2047" s="8"/>
-    </row>
-    <row r="2048" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2048"/>
-      <c r="D2048" s="8"/>
-    </row>
-    <row r="2049" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2049"/>
-      <c r="D2049" s="8"/>
-    </row>
-    <row r="2050" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2050"/>
-      <c r="D2050" s="8"/>
-    </row>
-    <row r="2051" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2051"/>
-      <c r="D2051" s="8"/>
-    </row>
-    <row r="2052" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2052"/>
-      <c r="D2052" s="8"/>
-    </row>
-    <row r="2053" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2053"/>
-      <c r="D2053" s="8"/>
-    </row>
-    <row r="2054" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2054"/>
-      <c r="D2054" s="8"/>
-    </row>
-    <row r="2055" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2055"/>
-      <c r="D2055" s="8"/>
-    </row>
-    <row r="2056" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2056"/>
-      <c r="D2056" s="8"/>
-    </row>
-    <row r="2057" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2057"/>
-      <c r="D2057" s="8"/>
-    </row>
-    <row r="2058" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2058"/>
-      <c r="D2058" s="8"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A33 A2059:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="1"/>
+  <conditionalFormatting sqref="A1">
+    <cfRule type="duplicateValues" dxfId="93" priority="84"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E119">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="92" priority="83"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E127">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="duplicateValues" dxfId="91" priority="82"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E135">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="duplicateValues" dxfId="90" priority="81"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E140">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  <conditionalFormatting sqref="A5">
+    <cfRule type="duplicateValues" dxfId="89" priority="80"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E145">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  <conditionalFormatting sqref="A6">
+    <cfRule type="duplicateValues" dxfId="88" priority="79"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E149">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  <conditionalFormatting sqref="A7">
+    <cfRule type="duplicateValues" dxfId="87" priority="78"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E153">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  <conditionalFormatting sqref="A8">
+    <cfRule type="duplicateValues" dxfId="86" priority="77"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G112">
-    <cfRule type="duplicateValues" dxfId="1" priority="10"/>
+  <conditionalFormatting sqref="A9">
+    <cfRule type="duplicateValues" dxfId="85" priority="76"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G189">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="A10">
+    <cfRule type="duplicateValues" dxfId="84" priority="75"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1985:A1048576">
+    <cfRule type="duplicateValues" dxfId="9" priority="85"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45">
+    <cfRule type="duplicateValues" dxfId="8" priority="93"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E53">
+    <cfRule type="duplicateValues" dxfId="7" priority="92"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="duplicateValues" dxfId="6" priority="91"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66">
+    <cfRule type="duplicateValues" dxfId="5" priority="90"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E71">
+    <cfRule type="duplicateValues" dxfId="4" priority="89"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E75">
+    <cfRule type="duplicateValues" dxfId="3" priority="88"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79">
+    <cfRule type="duplicateValues" dxfId="2" priority="87"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G115">
+    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
   </conditionalFormatting>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/danhsachisbn.xlsx
+++ b/danhsachisbn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/cào data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DE398F-D67C-0741-8D1E-207B210D4B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977CAF7-4F98-504A-AAA1-0572AA82B9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14700" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t>9781789894547</t>
   </si>
@@ -53,6 +53,66 @@
   </si>
   <si>
     <t>9780399553578</t>
+  </si>
+  <si>
+    <t>9780811827782</t>
+  </si>
+  <si>
+    <t>9780063306608</t>
+  </si>
+  <si>
+    <t>9781250108081</t>
+  </si>
+  <si>
+    <t>9781250108098</t>
+  </si>
+  <si>
+    <t>9781250199348</t>
+  </si>
+  <si>
+    <t>9781250813466</t>
+  </si>
+  <si>
+    <t>9781250199324</t>
+  </si>
+  <si>
+    <t>9781958627051</t>
+  </si>
+  <si>
+    <t>9780316353229</t>
+  </si>
+  <si>
+    <t>9781465491503</t>
+  </si>
+  <si>
+    <t>9781646387465</t>
+  </si>
+  <si>
+    <t>9781774470381</t>
+  </si>
+  <si>
+    <t>9780877797296</t>
+  </si>
+  <si>
+    <t>9781951056773</t>
+  </si>
+  <si>
+    <t>9781959284048</t>
+  </si>
+  <si>
+    <t>9781426220586</t>
+  </si>
+  <si>
+    <t>9780590431620</t>
+  </si>
+  <si>
+    <t>9781788950787</t>
+  </si>
+  <si>
+    <t>9780545639149</t>
+  </si>
+  <si>
+    <t>9781107549876</t>
   </si>
 </sst>
 </file>
@@ -242,107 +302,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 7" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="94">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="50">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -648,7 +608,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -658,7 +618,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -668,7 +628,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -678,7 +638,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -688,7 +648,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -698,7 +658,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -708,7 +668,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -718,7 +678,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -728,7 +688,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -738,347 +698,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1584,83 +1204,123 @@
       <c r="D10" s="8"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11"/>
+      <c r="A11" s="22" t="s">
+        <v>10</v>
+      </c>
       <c r="D11" s="8"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12"/>
+      <c r="A12" s="22" t="s">
+        <v>11</v>
+      </c>
       <c r="D12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13"/>
+      <c r="A13" s="22" t="s">
+        <v>12</v>
+      </c>
       <c r="D13" s="8"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14"/>
+      <c r="A14" s="22" t="s">
+        <v>13</v>
+      </c>
       <c r="D14" s="8"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15"/>
+      <c r="A15" s="22" t="s">
+        <v>14</v>
+      </c>
       <c r="D15" s="8"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16"/>
+      <c r="A16" s="22" t="s">
+        <v>15</v>
+      </c>
       <c r="D16" s="8"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17"/>
+      <c r="A17" s="22" t="s">
+        <v>16</v>
+      </c>
       <c r="D17" s="8"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18"/>
+      <c r="A18" s="22" t="s">
+        <v>17</v>
+      </c>
       <c r="D18" s="8"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19"/>
+      <c r="A19" s="22" t="s">
+        <v>18</v>
+      </c>
       <c r="D19" s="8"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20"/>
+      <c r="A20" s="22" t="s">
+        <v>19</v>
+      </c>
       <c r="D20" s="8"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21"/>
+      <c r="A21" s="22" t="s">
+        <v>20</v>
+      </c>
       <c r="D21" s="8"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22"/>
+      <c r="A22" s="22" t="s">
+        <v>21</v>
+      </c>
       <c r="D22" s="8"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23"/>
+      <c r="A23" s="22" t="s">
+        <v>22</v>
+      </c>
       <c r="D23" s="8"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24"/>
+      <c r="A24" s="22" t="s">
+        <v>23</v>
+      </c>
       <c r="D24" s="8"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25"/>
+      <c r="A25" s="22" t="s">
+        <v>24</v>
+      </c>
       <c r="D25" s="8"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26"/>
+      <c r="A26" s="22" t="s">
+        <v>25</v>
+      </c>
       <c r="D26" s="8"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27"/>
+      <c r="A27" s="22" t="s">
+        <v>26</v>
+      </c>
       <c r="D27" s="8"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28"/>
+      <c r="A28" s="22" t="s">
+        <v>27</v>
+      </c>
       <c r="D28" s="8"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29"/>
+      <c r="A29" s="22" t="s">
+        <v>28</v>
+      </c>
       <c r="D29" s="8"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30"/>
+      <c r="A30" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="D30" s="8"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
@@ -10084,65 +9744,125 @@
       <c r="D1984" s="8"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A1985:A1048576">
+    <cfRule type="duplicateValues" dxfId="39" priority="115"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E45">
+    <cfRule type="duplicateValues" dxfId="38" priority="123"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E53">
+    <cfRule type="duplicateValues" dxfId="37" priority="122"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E61">
+    <cfRule type="duplicateValues" dxfId="36" priority="121"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E66">
+    <cfRule type="duplicateValues" dxfId="35" priority="120"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E71">
+    <cfRule type="duplicateValues" dxfId="34" priority="119"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E75">
+    <cfRule type="duplicateValues" dxfId="33" priority="118"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79">
+    <cfRule type="duplicateValues" dxfId="32" priority="117"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G38">
+    <cfRule type="duplicateValues" dxfId="31" priority="124"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G115">
+    <cfRule type="duplicateValues" dxfId="30" priority="116"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="93" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="92" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="91" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="90" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="89" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="88" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="87" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="86" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="85" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="84" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1985:A1048576">
-    <cfRule type="duplicateValues" dxfId="9" priority="85"/>
+  <conditionalFormatting sqref="A11">
+    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
-    <cfRule type="duplicateValues" dxfId="8" priority="93"/>
+  <conditionalFormatting sqref="A12">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="7" priority="92"/>
+  <conditionalFormatting sqref="A13">
+    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
-    <cfRule type="duplicateValues" dxfId="6" priority="91"/>
+  <conditionalFormatting sqref="A14">
+    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E66">
-    <cfRule type="duplicateValues" dxfId="5" priority="90"/>
+  <conditionalFormatting sqref="A15">
+    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E71">
-    <cfRule type="duplicateValues" dxfId="4" priority="89"/>
+  <conditionalFormatting sqref="A16">
+    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E75">
-    <cfRule type="duplicateValues" dxfId="3" priority="88"/>
+  <conditionalFormatting sqref="A17">
+    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E79">
-    <cfRule type="duplicateValues" dxfId="2" priority="87"/>
+  <conditionalFormatting sqref="A18">
+    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
-    <cfRule type="duplicateValues" dxfId="1" priority="94"/>
+  <conditionalFormatting sqref="A19">
+    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G115">
-    <cfRule type="duplicateValues" dxfId="0" priority="86"/>
+  <conditionalFormatting sqref="A20">
+    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A21">
+    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A22">
+    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A23">
+    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A24">
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A25">
+    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A26">
+    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A27">
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A28">
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A29">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A30">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/danhsachisbn.xlsx
+++ b/danhsachisbn.xlsx
@@ -8,22 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/cào data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0977CAF7-4F98-504A-AAA1-0572AA82B9C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D78E245-C6FA-9041-96F4-BAACDD2C0277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="14700" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19200" yWindow="600" windowWidth="19200" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$S$1984</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$2:$S$1942</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+  <si>
+    <t>isbn</t>
+  </si>
   <si>
     <t>9781789894547</t>
   </si>
@@ -33,87 +36,6 @@
   <si>
     <t>9780316381251</t>
   </si>
-  <si>
-    <t>9798339702337</t>
-  </si>
-  <si>
-    <t>9780763692766</t>
-  </si>
-  <si>
-    <t>9781409539117</t>
-  </si>
-  <si>
-    <t>9781803701332</t>
-  </si>
-  <si>
-    <t>9781536213911</t>
-  </si>
-  <si>
-    <t>9780399554520</t>
-  </si>
-  <si>
-    <t>9780399553578</t>
-  </si>
-  <si>
-    <t>9780811827782</t>
-  </si>
-  <si>
-    <t>9780063306608</t>
-  </si>
-  <si>
-    <t>9781250108081</t>
-  </si>
-  <si>
-    <t>9781250108098</t>
-  </si>
-  <si>
-    <t>9781250199348</t>
-  </si>
-  <si>
-    <t>9781250813466</t>
-  </si>
-  <si>
-    <t>9781250199324</t>
-  </si>
-  <si>
-    <t>9781958627051</t>
-  </si>
-  <si>
-    <t>9780316353229</t>
-  </si>
-  <si>
-    <t>9781465491503</t>
-  </si>
-  <si>
-    <t>9781646387465</t>
-  </si>
-  <si>
-    <t>9781774470381</t>
-  </si>
-  <si>
-    <t>9780877797296</t>
-  </si>
-  <si>
-    <t>9781951056773</t>
-  </si>
-  <si>
-    <t>9781959284048</t>
-  </si>
-  <si>
-    <t>9781426220586</t>
-  </si>
-  <si>
-    <t>9780590431620</t>
-  </si>
-  <si>
-    <t>9781788950787</t>
-  </si>
-  <si>
-    <t>9780545639149</t>
-  </si>
-  <si>
-    <t>9781107549876</t>
-  </si>
 </sst>
 </file>
 
@@ -122,7 +44,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,13 +119,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF0F1111"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -249,7 +164,7 @@
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -283,16 +198,13 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -302,277 +214,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 7" xfId="1" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="11">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -679,126 +321,6 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -1074,7 +596,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q1984"/>
+  <dimension ref="A1:Q1942"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20.33203125" style="1" customWidth="1"/>
@@ -1086,7 +608,7 @@
     <col min="7" max="7" width="12.33203125" style="1" customWidth="1"/>
     <col min="9" max="9" width="9" style="8"/>
     <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="65.5" style="18" customWidth="1"/>
+    <col min="14" max="14" width="65.5" style="17" customWidth="1"/>
     <col min="15" max="15" width="26.6640625" customWidth="1"/>
     <col min="16" max="16" width="21.33203125" customWidth="1"/>
     <col min="17" max="17" width="42.83203125" customWidth="1"/>
@@ -1094,20 +616,13 @@
     <col min="19" max="19" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15"/>
-      <c r="D1" s="8"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="15"/>
-      <c r="L1" s="15"/>
-      <c r="N1" s="16"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="15"/>
@@ -1116,252 +631,362 @@
       <c r="J2" s="15"/>
       <c r="K2" s="15"/>
       <c r="L2" s="15"/>
-      <c r="N2" s="19"/>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A3" s="22" t="s">
+      <c r="N2" s="16"/>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="15"/>
       <c r="D3" s="8"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-      <c r="N3" s="19"/>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A4" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="15"/>
       <c r="D4" s="8"/>
-      <c r="I4" s="17"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="N4" s="16"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="15"/>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A5"/>
+      <c r="C5" s="2"/>
       <c r="D5" s="8"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="22" t="s">
-        <v>5</v>
-      </c>
-      <c r="C6" s="15"/>
+      <c r="G5"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="10"/>
+      <c r="Q5" s="7"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A6"/>
+      <c r="C6" s="2"/>
       <c r="D6" s="8"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="15"/>
-      <c r="N6" s="16"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A7" s="22" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="15"/>
+      <c r="G6"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="10"/>
+      <c r="Q6" s="7"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7"/>
+      <c r="C7" s="2"/>
       <c r="D7" s="8"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
-      <c r="L7" s="15"/>
-      <c r="N7" s="16"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="15"/>
+      <c r="G7"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="10"/>
+      <c r="N7" s="19"/>
+      <c r="Q7" s="7"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A8"/>
+      <c r="C8" s="2"/>
       <c r="D8" s="8"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="16"/>
-      <c r="K8" s="15"/>
-      <c r="L8" s="16"/>
-      <c r="N8" s="16"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="15"/>
+      <c r="F8" s="9"/>
+      <c r="G8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="10"/>
+      <c r="Q8" s="7"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A9"/>
+      <c r="C9" s="2"/>
       <c r="D9" s="8"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A10" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="15"/>
+      <c r="G9"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="Q9" s="7"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10"/>
+      <c r="C10" s="2"/>
       <c r="D10" s="8"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
-        <v>10</v>
-      </c>
+      <c r="G10"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="Q10" s="7"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11"/>
+      <c r="C11" s="2"/>
       <c r="D11" s="8"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A12" s="22" t="s">
-        <v>11</v>
-      </c>
+      <c r="E11" s="11"/>
+      <c r="G11"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="Q11" s="7"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12"/>
+      <c r="C12" s="2"/>
       <c r="D12" s="8"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A13" s="22" t="s">
-        <v>12</v>
-      </c>
+      <c r="G12"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="Q12" s="7"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13"/>
+      <c r="C13" s="2"/>
       <c r="D13" s="8"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A14" s="22" t="s">
-        <v>13</v>
-      </c>
+      <c r="G13"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="Q13" s="7"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14"/>
+      <c r="C14" s="2"/>
       <c r="D14" s="8"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A15" s="22" t="s">
-        <v>14</v>
-      </c>
+      <c r="G14"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="Q14" s="7"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15"/>
+      <c r="C15" s="2"/>
       <c r="D15" s="8"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A16" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="G15"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="8"/>
+      <c r="Q15" s="7"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16"/>
+      <c r="C16" s="2"/>
       <c r="D16" s="8"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="22" t="s">
-        <v>16</v>
-      </c>
+      <c r="G16"/>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="Q16" s="7"/>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A17"/>
+      <c r="C17" s="2"/>
       <c r="D17" s="8"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
-        <v>17</v>
-      </c>
+      <c r="G17"/>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="Q17" s="7"/>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A18"/>
+      <c r="C18" s="2"/>
       <c r="D18" s="8"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="22" t="s">
-        <v>18</v>
-      </c>
+      <c r="G18"/>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="Q18" s="7"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19"/>
+      <c r="C19" s="2"/>
       <c r="D19" s="8"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="22" t="s">
-        <v>19</v>
-      </c>
+      <c r="E19" s="11"/>
+      <c r="G19"/>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="N19" s="19"/>
+      <c r="Q19" s="7"/>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A20"/>
+      <c r="C20" s="2"/>
       <c r="D20" s="8"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="22" t="s">
-        <v>20</v>
-      </c>
+      <c r="G20"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="Q20" s="7"/>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A21"/>
+      <c r="C21" s="2"/>
       <c r="D21" s="8"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="22" t="s">
-        <v>21</v>
-      </c>
+      <c r="G21"/>
+      <c r="J21" s="8"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="N21" s="19"/>
+      <c r="Q21" s="7"/>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A22"/>
+      <c r="C22" s="2"/>
       <c r="D22" s="8"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="22" t="s">
-        <v>22</v>
-      </c>
+      <c r="G22"/>
+      <c r="J22" s="8"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="Q22" s="7"/>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A23"/>
+      <c r="C23" s="2"/>
       <c r="D23" s="8"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="22" t="s">
-        <v>23</v>
-      </c>
+      <c r="F23" s="9"/>
+      <c r="G23"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="Q23" s="7"/>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A24"/>
+      <c r="C24" s="2"/>
       <c r="D24" s="8"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="22" t="s">
-        <v>24</v>
-      </c>
+      <c r="E24" s="11"/>
+      <c r="G24"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="Q24" s="7"/>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A25"/>
+      <c r="C25" s="2"/>
       <c r="D25" s="8"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="22" t="s">
-        <v>25</v>
-      </c>
+      <c r="G25"/>
+      <c r="J25" s="8"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="8"/>
+      <c r="Q25" s="7"/>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A26"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="8"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="22" t="s">
-        <v>26</v>
-      </c>
+      <c r="G26"/>
+      <c r="J26" s="8"/>
+      <c r="K26" s="8"/>
+      <c r="L26" s="8"/>
+      <c r="Q26" s="7"/>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A27"/>
+      <c r="C27" s="2"/>
       <c r="D27" s="8"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="22" t="s">
-        <v>27</v>
-      </c>
+      <c r="G27"/>
+      <c r="J27" s="8"/>
+      <c r="K27" s="8"/>
+      <c r="L27" s="8"/>
+      <c r="Q27" s="7"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A28"/>
+      <c r="C28" s="2"/>
       <c r="D28" s="8"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="22" t="s">
-        <v>28</v>
-      </c>
+      <c r="G28"/>
+      <c r="J28" s="8"/>
+      <c r="K28" s="8"/>
+      <c r="L28" s="8"/>
+      <c r="Q28" s="7"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A29"/>
+      <c r="C29" s="2"/>
       <c r="D29" s="8"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="22" t="s">
-        <v>29</v>
-      </c>
+      <c r="E29" s="11"/>
+      <c r="G29"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="Q29" s="7"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A30"/>
+      <c r="C30" s="2"/>
       <c r="D30" s="8"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G30"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="Q30" s="7"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31"/>
+      <c r="C31" s="2"/>
       <c r="D31" s="8"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="G31"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="Q31" s="7"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32"/>
+      <c r="C32" s="2"/>
       <c r="D32" s="8"/>
+      <c r="G32"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="N32" s="19"/>
+      <c r="Q32" s="7"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33"/>
+      <c r="C33" s="2"/>
       <c r="D33" s="8"/>
+      <c r="E33" s="11"/>
+      <c r="G33"/>
+      <c r="J33" s="8"/>
+      <c r="K33" s="8"/>
+      <c r="L33" s="8"/>
+      <c r="N33" s="19"/>
+      <c r="Q33" s="7"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34"/>
+      <c r="C34" s="2"/>
       <c r="D34" s="8"/>
+      <c r="G34"/>
+      <c r="J34" s="8"/>
+      <c r="K34" s="8"/>
+      <c r="L34" s="10"/>
+      <c r="Q34" s="7"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="8"/>
+      <c r="G35"/>
+      <c r="J35" s="8"/>
+      <c r="K35" s="8"/>
+      <c r="L35" s="10"/>
+      <c r="Q35" s="7"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36"/>
+      <c r="C36" s="2"/>
       <c r="D36" s="8"/>
+      <c r="G36"/>
+      <c r="J36" s="8"/>
+      <c r="K36" s="8"/>
+      <c r="L36" s="10"/>
+      <c r="N36" s="19"/>
+      <c r="Q36" s="7"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A37"/>
       <c r="C37" s="2"/>
       <c r="D37" s="8"/>
-      <c r="E37" s="3"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="3"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="N37" s="20"/>
-      <c r="O37" s="3"/>
-      <c r="P37" s="2"/>
+      <c r="E37" s="11"/>
+      <c r="G37"/>
+      <c r="J37" s="8"/>
+      <c r="K37" s="8"/>
+      <c r="L37" s="10"/>
       <c r="Q37" s="7"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
@@ -1369,21 +994,15 @@
       <c r="C38" s="2"/>
       <c r="D38" s="8"/>
       <c r="G38"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="3"/>
-      <c r="P38" s="2"/>
+      <c r="J38" s="8"/>
+      <c r="K38" s="8"/>
+      <c r="L38" s="8"/>
       <c r="Q38" s="7"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A39"/>
       <c r="C39" s="2"/>
       <c r="D39" s="8"/>
-      <c r="E39" s="3"/>
       <c r="G39"/>
       <c r="J39" s="8"/>
       <c r="K39" s="8"/>
@@ -1394,8 +1013,6 @@
       <c r="A40"/>
       <c r="C40" s="2"/>
       <c r="D40" s="8"/>
-      <c r="E40" s="3"/>
-      <c r="F40" s="9"/>
       <c r="G40"/>
       <c r="J40" s="8"/>
       <c r="K40" s="8"/>
@@ -1406,7 +1023,6 @@
       <c r="A41"/>
       <c r="C41" s="2"/>
       <c r="D41" s="8"/>
-      <c r="E41" s="3"/>
       <c r="G41"/>
       <c r="J41" s="8"/>
       <c r="K41" s="8"/>
@@ -1417,7 +1033,6 @@
       <c r="A42"/>
       <c r="C42" s="2"/>
       <c r="D42" s="8"/>
-      <c r="E42" s="3"/>
       <c r="G42"/>
       <c r="J42" s="8"/>
       <c r="K42" s="8"/>
@@ -1428,8 +1043,6 @@
       <c r="A43"/>
       <c r="C43" s="2"/>
       <c r="D43" s="8"/>
-      <c r="E43" s="3"/>
-      <c r="F43" s="9"/>
       <c r="G43"/>
       <c r="J43" s="8"/>
       <c r="K43" s="8"/>
@@ -1440,25 +1053,20 @@
       <c r="A44"/>
       <c r="C44" s="2"/>
       <c r="D44" s="8"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="9"/>
       <c r="G44"/>
       <c r="J44" s="8"/>
       <c r="K44" s="8"/>
       <c r="L44" s="8"/>
-      <c r="N44" s="3"/>
       <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A45"/>
       <c r="C45" s="2"/>
       <c r="D45" s="8"/>
-      <c r="F45" s="9"/>
       <c r="G45"/>
       <c r="J45" s="8"/>
       <c r="K45" s="8"/>
-      <c r="L45" s="10"/>
-      <c r="N45" s="21"/>
+      <c r="L45" s="8"/>
       <c r="Q45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
@@ -1468,7 +1076,7 @@
       <c r="G46"/>
       <c r="J46" s="8"/>
       <c r="K46" s="8"/>
-      <c r="L46" s="10"/>
+      <c r="L46" s="8"/>
       <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
@@ -1478,7 +1086,7 @@
       <c r="G47"/>
       <c r="J47" s="8"/>
       <c r="K47" s="8"/>
-      <c r="L47" s="10"/>
+      <c r="L47" s="8"/>
       <c r="Q47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
@@ -1488,7 +1096,7 @@
       <c r="G48"/>
       <c r="J48" s="8"/>
       <c r="K48" s="8"/>
-      <c r="L48" s="10"/>
+      <c r="L48" s="8"/>
       <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
@@ -1498,19 +1106,17 @@
       <c r="G49"/>
       <c r="J49" s="8"/>
       <c r="K49" s="8"/>
-      <c r="L49" s="10"/>
-      <c r="N49" s="21"/>
+      <c r="L49" s="8"/>
       <c r="Q49" s="7"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A50"/>
       <c r="C50" s="2"/>
       <c r="D50" s="8"/>
-      <c r="F50" s="9"/>
       <c r="G50"/>
       <c r="J50" s="8"/>
       <c r="K50" s="8"/>
-      <c r="L50" s="10"/>
+      <c r="L50" s="8"/>
       <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
@@ -1537,7 +1143,6 @@
       <c r="A53"/>
       <c r="C53" s="2"/>
       <c r="D53" s="8"/>
-      <c r="E53" s="11"/>
       <c r="G53"/>
       <c r="J53" s="8"/>
       <c r="K53" s="8"/>
@@ -1618,12 +1223,10 @@
       <c r="A61"/>
       <c r="C61" s="2"/>
       <c r="D61" s="8"/>
-      <c r="E61" s="11"/>
       <c r="G61"/>
       <c r="J61" s="8"/>
       <c r="K61" s="8"/>
       <c r="L61" s="8"/>
-      <c r="N61" s="21"/>
       <c r="Q61" s="7"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
@@ -1644,13 +1247,13 @@
       <c r="J63" s="8"/>
       <c r="K63" s="8"/>
       <c r="L63" s="8"/>
-      <c r="N63" s="21"/>
       <c r="Q63" s="7"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A64"/>
       <c r="C64" s="2"/>
       <c r="D64" s="8"/>
+      <c r="F64" s="12"/>
       <c r="G64"/>
       <c r="J64" s="8"/>
       <c r="K64" s="8"/>
@@ -1661,7 +1264,6 @@
       <c r="A65"/>
       <c r="C65" s="2"/>
       <c r="D65" s="8"/>
-      <c r="F65" s="9"/>
       <c r="G65"/>
       <c r="J65" s="8"/>
       <c r="K65" s="8"/>
@@ -1672,7 +1274,6 @@
       <c r="A66"/>
       <c r="C66" s="2"/>
       <c r="D66" s="8"/>
-      <c r="E66" s="11"/>
       <c r="G66"/>
       <c r="J66" s="8"/>
       <c r="K66" s="8"/>
@@ -1713,6 +1314,7 @@
       <c r="A70"/>
       <c r="C70" s="2"/>
       <c r="D70" s="8"/>
+      <c r="F70" s="12"/>
       <c r="G70"/>
       <c r="J70" s="8"/>
       <c r="K70" s="8"/>
@@ -1723,7 +1325,6 @@
       <c r="A71"/>
       <c r="C71" s="2"/>
       <c r="D71" s="8"/>
-      <c r="E71" s="11"/>
       <c r="G71"/>
       <c r="J71" s="8"/>
       <c r="K71" s="8"/>
@@ -1732,590 +1333,331 @@
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A72"/>
-      <c r="C72" s="2"/>
+      <c r="C72" s="13"/>
       <c r="D72" s="8"/>
-      <c r="G72"/>
-      <c r="J72" s="8"/>
-      <c r="K72" s="8"/>
-      <c r="L72" s="8"/>
+      <c r="E72" s="3"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="3"/>
+      <c r="H72" s="2"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="6"/>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6"/>
+      <c r="N72" s="18"/>
+      <c r="O72" s="3"/>
+      <c r="P72" s="2"/>
       <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A73"/>
       <c r="C73" s="2"/>
       <c r="D73" s="8"/>
+      <c r="E73" s="3"/>
       <c r="G73"/>
-      <c r="J73" s="8"/>
-      <c r="K73" s="8"/>
-      <c r="L73" s="8"/>
+      <c r="H73" s="2"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="6"/>
+      <c r="K73" s="6"/>
+      <c r="L73" s="6"/>
+      <c r="N73" s="18"/>
+      <c r="O73" s="3"/>
+      <c r="P73" s="2"/>
       <c r="Q73" s="7"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A74"/>
-      <c r="C74" s="2"/>
+      <c r="C74" s="13"/>
       <c r="D74" s="8"/>
+      <c r="E74" s="3"/>
       <c r="G74"/>
+      <c r="I74" s="5"/>
       <c r="J74" s="8"/>
       <c r="K74" s="8"/>
       <c r="L74" s="8"/>
-      <c r="N74" s="21"/>
       <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A75"/>
       <c r="C75" s="2"/>
       <c r="D75" s="8"/>
-      <c r="E75" s="11"/>
+      <c r="E75" s="3"/>
+      <c r="F75" s="9"/>
       <c r="G75"/>
+      <c r="I75" s="5"/>
       <c r="J75" s="8"/>
       <c r="K75" s="8"/>
       <c r="L75" s="8"/>
-      <c r="N75" s="21"/>
       <c r="Q75" s="7"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A76"/>
       <c r="C76" s="2"/>
       <c r="D76" s="8"/>
+      <c r="E76" s="3"/>
       <c r="G76"/>
+      <c r="I76" s="5"/>
       <c r="J76" s="8"/>
       <c r="K76" s="8"/>
-      <c r="L76" s="10"/>
+      <c r="L76" s="8"/>
       <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A77"/>
       <c r="C77" s="2"/>
       <c r="D77" s="8"/>
+      <c r="E77" s="3"/>
       <c r="G77"/>
+      <c r="I77" s="5"/>
       <c r="J77" s="8"/>
       <c r="K77" s="8"/>
-      <c r="L77" s="10"/>
+      <c r="L77" s="8"/>
       <c r="Q77" s="7"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A78"/>
       <c r="C78" s="2"/>
       <c r="D78" s="8"/>
-      <c r="G78"/>
+      <c r="E78" s="3"/>
+      <c r="F78" s="4"/>
+      <c r="G78" s="3"/>
+      <c r="I78" s="5"/>
       <c r="J78" s="8"/>
       <c r="K78" s="8"/>
-      <c r="L78" s="10"/>
-      <c r="N78" s="21"/>
+      <c r="L78" s="8"/>
+      <c r="N78" s="18"/>
+      <c r="O78" s="3"/>
       <c r="Q78" s="7"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A79"/>
       <c r="C79" s="2"/>
       <c r="D79" s="8"/>
-      <c r="E79" s="11"/>
+      <c r="E79" s="3"/>
       <c r="G79"/>
+      <c r="I79" s="5"/>
       <c r="J79" s="8"/>
       <c r="K79" s="8"/>
-      <c r="L79" s="10"/>
+      <c r="L79" s="8"/>
       <c r="Q79" s="7"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A80"/>
       <c r="C80" s="2"/>
       <c r="D80" s="8"/>
+      <c r="E80" s="3"/>
+      <c r="F80" s="9"/>
       <c r="G80"/>
+      <c r="I80" s="5"/>
       <c r="J80" s="8"/>
       <c r="K80" s="8"/>
-      <c r="L80" s="8"/>
+      <c r="L80" s="10"/>
       <c r="Q80" s="7"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81"/>
       <c r="C81" s="2"/>
       <c r="D81" s="8"/>
+      <c r="E81" s="3"/>
       <c r="G81"/>
+      <c r="I81" s="5"/>
       <c r="J81" s="8"/>
       <c r="K81" s="8"/>
-      <c r="L81" s="8"/>
+      <c r="L81" s="10"/>
       <c r="Q81" s="7"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82"/>
       <c r="C82" s="2"/>
       <c r="D82" s="8"/>
+      <c r="E82" s="3"/>
       <c r="G82"/>
+      <c r="I82" s="5"/>
       <c r="J82" s="8"/>
       <c r="K82" s="8"/>
-      <c r="L82" s="8"/>
+      <c r="L82" s="10"/>
       <c r="Q82" s="7"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83"/>
-      <c r="C83" s="2"/>
       <c r="D83" s="8"/>
-      <c r="G83"/>
-      <c r="J83" s="8"/>
-      <c r="K83" s="8"/>
-      <c r="L83" s="8"/>
-      <c r="Q83" s="7"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84"/>
-      <c r="C84" s="2"/>
       <c r="D84" s="8"/>
-      <c r="G84"/>
-      <c r="J84" s="8"/>
-      <c r="K84" s="8"/>
-      <c r="L84" s="8"/>
-      <c r="Q84" s="7"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85"/>
-      <c r="C85" s="2"/>
       <c r="D85" s="8"/>
-      <c r="G85"/>
-      <c r="J85" s="8"/>
-      <c r="K85" s="8"/>
-      <c r="L85" s="8"/>
-      <c r="Q85" s="7"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86"/>
-      <c r="C86" s="2"/>
       <c r="D86" s="8"/>
-      <c r="G86"/>
-      <c r="J86" s="8"/>
-      <c r="K86" s="8"/>
-      <c r="L86" s="8"/>
-      <c r="Q86" s="7"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87"/>
-      <c r="C87" s="2"/>
       <c r="D87" s="8"/>
-      <c r="G87"/>
-      <c r="J87" s="8"/>
-      <c r="K87" s="8"/>
-      <c r="L87" s="8"/>
-      <c r="Q87" s="7"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88"/>
-      <c r="C88" s="2"/>
       <c r="D88" s="8"/>
-      <c r="G88"/>
-      <c r="J88" s="8"/>
-      <c r="K88" s="8"/>
-      <c r="L88" s="8"/>
-      <c r="Q88" s="7"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89"/>
-      <c r="C89" s="2"/>
       <c r="D89" s="8"/>
-      <c r="G89"/>
-      <c r="J89" s="8"/>
-      <c r="K89" s="8"/>
-      <c r="L89" s="8"/>
-      <c r="Q89" s="7"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90"/>
-      <c r="C90" s="2"/>
       <c r="D90" s="8"/>
-      <c r="G90"/>
-      <c r="J90" s="8"/>
-      <c r="K90" s="8"/>
-      <c r="L90" s="8"/>
-      <c r="Q90" s="7"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91"/>
-      <c r="C91" s="2"/>
       <c r="D91" s="8"/>
-      <c r="G91"/>
-      <c r="J91" s="8"/>
-      <c r="K91" s="8"/>
-      <c r="L91" s="8"/>
-      <c r="Q91" s="7"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92"/>
-      <c r="C92" s="2"/>
       <c r="D92" s="8"/>
-      <c r="G92"/>
-      <c r="J92" s="8"/>
-      <c r="K92" s="8"/>
-      <c r="L92" s="8"/>
-      <c r="Q92" s="7"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93"/>
-      <c r="C93" s="2"/>
       <c r="D93" s="8"/>
-      <c r="G93"/>
-      <c r="J93" s="8"/>
-      <c r="K93" s="8"/>
-      <c r="L93" s="8"/>
-      <c r="Q93" s="7"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94"/>
-      <c r="C94" s="2"/>
       <c r="D94" s="8"/>
-      <c r="G94"/>
-      <c r="J94" s="8"/>
-      <c r="K94" s="8"/>
-      <c r="L94" s="8"/>
-      <c r="Q94" s="7"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95"/>
-      <c r="C95" s="2"/>
       <c r="D95" s="8"/>
-      <c r="G95"/>
-      <c r="J95" s="8"/>
-      <c r="K95" s="8"/>
-      <c r="L95" s="8"/>
-      <c r="Q95" s="7"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96"/>
-      <c r="C96" s="2"/>
       <c r="D96" s="8"/>
-      <c r="G96"/>
-      <c r="J96" s="8"/>
-      <c r="K96" s="8"/>
-      <c r="L96" s="8"/>
-      <c r="Q96" s="7"/>
-    </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A97"/>
-      <c r="C97" s="2"/>
       <c r="D97" s="8"/>
-      <c r="G97"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="Q97" s="7"/>
-    </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A98"/>
-      <c r="C98" s="2"/>
       <c r="D98" s="8"/>
-      <c r="G98"/>
-      <c r="J98" s="8"/>
-      <c r="K98" s="8"/>
-      <c r="L98" s="8"/>
-      <c r="Q98" s="7"/>
-    </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A99"/>
-      <c r="C99" s="2"/>
       <c r="D99" s="8"/>
-      <c r="G99"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="Q99" s="7"/>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A100"/>
-      <c r="C100" s="2"/>
       <c r="D100" s="8"/>
-      <c r="G100"/>
-      <c r="J100" s="8"/>
-      <c r="K100" s="8"/>
-      <c r="L100" s="8"/>
-      <c r="Q100" s="7"/>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A101"/>
-      <c r="C101" s="2"/>
       <c r="D101" s="8"/>
-      <c r="G101"/>
-      <c r="J101" s="8"/>
-      <c r="K101" s="8"/>
-      <c r="L101" s="8"/>
-      <c r="Q101" s="7"/>
-    </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A102"/>
-      <c r="C102" s="2"/>
       <c r="D102" s="8"/>
-      <c r="G102"/>
-      <c r="J102" s="8"/>
-      <c r="K102" s="8"/>
-      <c r="L102" s="8"/>
-      <c r="Q102" s="7"/>
-    </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A103"/>
-      <c r="C103" s="2"/>
       <c r="D103" s="8"/>
-      <c r="G103"/>
-      <c r="J103" s="8"/>
-      <c r="K103" s="8"/>
-      <c r="L103" s="8"/>
-      <c r="Q103" s="7"/>
-    </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A104"/>
-      <c r="C104" s="2"/>
       <c r="D104" s="8"/>
-      <c r="G104"/>
-      <c r="J104" s="8"/>
-      <c r="K104" s="8"/>
-      <c r="L104" s="8"/>
-      <c r="Q104" s="7"/>
-    </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A105"/>
-      <c r="C105" s="2"/>
       <c r="D105" s="8"/>
-      <c r="G105"/>
-      <c r="J105" s="8"/>
-      <c r="K105" s="8"/>
-      <c r="L105" s="8"/>
-      <c r="Q105" s="7"/>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A106"/>
-      <c r="C106" s="2"/>
       <c r="D106" s="8"/>
-      <c r="F106" s="12"/>
-      <c r="G106"/>
-      <c r="J106" s="8"/>
-      <c r="K106" s="8"/>
-      <c r="L106" s="8"/>
-      <c r="Q106" s="7"/>
-    </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A107"/>
-      <c r="C107" s="2"/>
       <c r="D107" s="8"/>
-      <c r="G107"/>
-      <c r="J107" s="8"/>
-      <c r="K107" s="8"/>
-      <c r="L107" s="8"/>
-      <c r="Q107" s="7"/>
-    </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A108"/>
-      <c r="C108" s="2"/>
       <c r="D108" s="8"/>
-      <c r="G108"/>
-      <c r="J108" s="8"/>
-      <c r="K108" s="8"/>
-      <c r="L108" s="8"/>
-      <c r="Q108" s="7"/>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A109"/>
-      <c r="C109" s="2"/>
       <c r="D109" s="8"/>
-      <c r="G109"/>
-      <c r="J109" s="8"/>
-      <c r="K109" s="8"/>
-      <c r="L109" s="8"/>
-      <c r="Q109" s="7"/>
-    </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A110"/>
-      <c r="C110" s="2"/>
       <c r="D110" s="8"/>
-      <c r="G110"/>
-      <c r="J110" s="8"/>
-      <c r="K110" s="8"/>
-      <c r="L110" s="8"/>
-      <c r="Q110" s="7"/>
-    </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A111"/>
-      <c r="C111" s="2"/>
       <c r="D111" s="8"/>
-      <c r="G111"/>
-      <c r="J111" s="8"/>
-      <c r="K111" s="8"/>
-      <c r="L111" s="8"/>
-      <c r="Q111" s="7"/>
-    </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A112"/>
-      <c r="C112" s="2"/>
       <c r="D112" s="8"/>
-      <c r="F112" s="12"/>
-      <c r="G112"/>
-      <c r="J112" s="8"/>
-      <c r="K112" s="8"/>
-      <c r="L112" s="8"/>
-      <c r="Q112" s="7"/>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A113"/>
-      <c r="C113" s="2"/>
       <c r="D113" s="8"/>
-      <c r="G113"/>
-      <c r="J113" s="8"/>
-      <c r="K113" s="8"/>
-      <c r="L113" s="8"/>
-      <c r="Q113" s="7"/>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A114"/>
-      <c r="C114" s="13"/>
       <c r="D114" s="8"/>
-      <c r="E114" s="3"/>
-      <c r="F114" s="4"/>
-      <c r="G114" s="3"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="5"/>
-      <c r="J114" s="6"/>
-      <c r="K114" s="6"/>
-      <c r="L114" s="6"/>
-      <c r="N114" s="20"/>
-      <c r="O114" s="3"/>
-      <c r="P114" s="2"/>
-      <c r="Q114" s="7"/>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A115"/>
-      <c r="C115" s="2"/>
       <c r="D115" s="8"/>
-      <c r="E115" s="3"/>
-      <c r="G115"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="5"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
-      <c r="N115" s="20"/>
-      <c r="O115" s="3"/>
-      <c r="P115" s="2"/>
-      <c r="Q115" s="7"/>
-    </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A116"/>
-      <c r="C116" s="13"/>
       <c r="D116" s="8"/>
-      <c r="E116" s="3"/>
-      <c r="G116"/>
-      <c r="I116" s="5"/>
-      <c r="J116" s="8"/>
-      <c r="K116" s="8"/>
-      <c r="L116" s="8"/>
-      <c r="Q116" s="7"/>
-    </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A117"/>
-      <c r="C117" s="2"/>
       <c r="D117" s="8"/>
-      <c r="E117" s="3"/>
-      <c r="F117" s="9"/>
-      <c r="G117"/>
-      <c r="I117" s="5"/>
-      <c r="J117" s="8"/>
-      <c r="K117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="Q117" s="7"/>
-    </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A118"/>
-      <c r="C118" s="2"/>
       <c r="D118" s="8"/>
-      <c r="E118" s="3"/>
-      <c r="G118"/>
-      <c r="I118" s="5"/>
-      <c r="J118" s="8"/>
-      <c r="K118" s="8"/>
-      <c r="L118" s="8"/>
-      <c r="Q118" s="7"/>
-    </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A119"/>
-      <c r="C119" s="2"/>
       <c r="D119" s="8"/>
-      <c r="E119" s="3"/>
-      <c r="G119"/>
-      <c r="I119" s="5"/>
-      <c r="J119" s="8"/>
-      <c r="K119" s="8"/>
-      <c r="L119" s="8"/>
-      <c r="Q119" s="7"/>
-    </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A120"/>
-      <c r="C120" s="2"/>
       <c r="D120" s="8"/>
-      <c r="E120" s="3"/>
-      <c r="F120" s="4"/>
-      <c r="G120" s="3"/>
-      <c r="I120" s="5"/>
-      <c r="J120" s="8"/>
-      <c r="K120" s="8"/>
-      <c r="L120" s="8"/>
-      <c r="N120" s="20"/>
-      <c r="O120" s="3"/>
-      <c r="Q120" s="7"/>
-    </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A121"/>
-      <c r="C121" s="2"/>
       <c r="D121" s="8"/>
-      <c r="E121" s="3"/>
-      <c r="G121"/>
-      <c r="I121" s="5"/>
-      <c r="J121" s="8"/>
-      <c r="K121" s="8"/>
-      <c r="L121" s="8"/>
-      <c r="Q121" s="7"/>
-    </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A122"/>
-      <c r="C122" s="2"/>
       <c r="D122" s="8"/>
-      <c r="E122" s="3"/>
-      <c r="F122" s="9"/>
-      <c r="G122"/>
-      <c r="I122" s="5"/>
-      <c r="J122" s="8"/>
-      <c r="K122" s="8"/>
-      <c r="L122" s="10"/>
-      <c r="Q122" s="7"/>
-    </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A123"/>
-      <c r="C123" s="2"/>
       <c r="D123" s="8"/>
-      <c r="E123" s="3"/>
-      <c r="G123"/>
-      <c r="I123" s="5"/>
-      <c r="J123" s="8"/>
-      <c r="K123" s="8"/>
-      <c r="L123" s="10"/>
-      <c r="Q123" s="7"/>
-    </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A124"/>
-      <c r="C124" s="2"/>
       <c r="D124" s="8"/>
-      <c r="E124" s="3"/>
-      <c r="G124"/>
-      <c r="I124" s="5"/>
-      <c r="J124" s="8"/>
-      <c r="K124" s="8"/>
-      <c r="L124" s="10"/>
-      <c r="Q124" s="7"/>
-    </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.2">
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A125"/>
       <c r="D125" s="8"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A126"/>
       <c r="D126" s="8"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A127"/>
       <c r="D127" s="8"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A128"/>
       <c r="D128" s="8"/>
     </row>
@@ -9575,293 +8917,38 @@
       <c r="A1942"/>
       <c r="D1942" s="8"/>
     </row>
-    <row r="1943" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1943"/>
-      <c r="D1943" s="8"/>
-    </row>
-    <row r="1944" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1944"/>
-      <c r="D1944" s="8"/>
-    </row>
-    <row r="1945" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1945"/>
-      <c r="D1945" s="8"/>
-    </row>
-    <row r="1946" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1946"/>
-      <c r="D1946" s="8"/>
-    </row>
-    <row r="1947" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1947"/>
-      <c r="D1947" s="8"/>
-    </row>
-    <row r="1948" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1948"/>
-      <c r="D1948" s="8"/>
-    </row>
-    <row r="1949" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1949"/>
-      <c r="D1949" s="8"/>
-    </row>
-    <row r="1950" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1950"/>
-      <c r="D1950" s="8"/>
-    </row>
-    <row r="1951" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1951"/>
-      <c r="D1951" s="8"/>
-    </row>
-    <row r="1952" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1952"/>
-      <c r="D1952" s="8"/>
-    </row>
-    <row r="1953" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1953"/>
-      <c r="D1953" s="8"/>
-    </row>
-    <row r="1954" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1954"/>
-      <c r="D1954" s="8"/>
-    </row>
-    <row r="1955" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1955"/>
-      <c r="D1955" s="8"/>
-    </row>
-    <row r="1956" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1956"/>
-      <c r="D1956" s="8"/>
-    </row>
-    <row r="1957" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1957"/>
-      <c r="D1957" s="8"/>
-    </row>
-    <row r="1958" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1958"/>
-      <c r="D1958" s="8"/>
-    </row>
-    <row r="1959" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1959"/>
-      <c r="D1959" s="8"/>
-    </row>
-    <row r="1960" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1960"/>
-      <c r="D1960" s="8"/>
-    </row>
-    <row r="1961" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1961"/>
-      <c r="D1961" s="8"/>
-    </row>
-    <row r="1962" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1962"/>
-      <c r="D1962" s="8"/>
-    </row>
-    <row r="1963" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1963"/>
-      <c r="D1963" s="8"/>
-    </row>
-    <row r="1964" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1964"/>
-      <c r="D1964" s="8"/>
-    </row>
-    <row r="1965" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1965"/>
-      <c r="D1965" s="8"/>
-    </row>
-    <row r="1966" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1966"/>
-      <c r="D1966" s="8"/>
-    </row>
-    <row r="1967" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1967"/>
-      <c r="D1967" s="8"/>
-    </row>
-    <row r="1968" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1968"/>
-      <c r="D1968" s="8"/>
-    </row>
-    <row r="1969" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1969"/>
-      <c r="D1969" s="8"/>
-    </row>
-    <row r="1970" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1970"/>
-      <c r="D1970" s="8"/>
-    </row>
-    <row r="1971" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1971"/>
-      <c r="D1971" s="8"/>
-    </row>
-    <row r="1972" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1972"/>
-      <c r="D1972" s="8"/>
-    </row>
-    <row r="1973" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1973"/>
-      <c r="D1973" s="8"/>
-    </row>
-    <row r="1974" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1974"/>
-      <c r="D1974" s="8"/>
-    </row>
-    <row r="1975" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1975"/>
-      <c r="D1975" s="8"/>
-    </row>
-    <row r="1976" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1976"/>
-      <c r="D1976" s="8"/>
-    </row>
-    <row r="1977" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1977"/>
-      <c r="D1977" s="8"/>
-    </row>
-    <row r="1978" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1978"/>
-      <c r="D1978" s="8"/>
-    </row>
-    <row r="1979" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1979"/>
-      <c r="D1979" s="8"/>
-    </row>
-    <row r="1980" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1980"/>
-      <c r="D1980" s="8"/>
-    </row>
-    <row r="1981" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1981"/>
-      <c r="D1981" s="8"/>
-    </row>
-    <row r="1982" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1982"/>
-      <c r="D1982" s="8"/>
-    </row>
-    <row r="1983" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1983"/>
-      <c r="D1983" s="8"/>
-    </row>
-    <row r="1984" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1984"/>
-      <c r="D1984" s="8"/>
-    </row>
   </sheetData>
-  <conditionalFormatting sqref="A1985:A1048576">
-    <cfRule type="duplicateValues" dxfId="39" priority="115"/>
+  <conditionalFormatting sqref="A1943:A1048576">
+    <cfRule type="duplicateValues" dxfId="10" priority="118"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E45">
-    <cfRule type="duplicateValues" dxfId="38" priority="123"/>
+  <conditionalFormatting sqref="E11">
+    <cfRule type="duplicateValues" dxfId="9" priority="125"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E53">
-    <cfRule type="duplicateValues" dxfId="37" priority="122"/>
+  <conditionalFormatting sqref="E19">
+    <cfRule type="duplicateValues" dxfId="8" priority="124"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E61">
-    <cfRule type="duplicateValues" dxfId="36" priority="121"/>
+  <conditionalFormatting sqref="E24">
+    <cfRule type="duplicateValues" dxfId="7" priority="123"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E66">
-    <cfRule type="duplicateValues" dxfId="35" priority="120"/>
+  <conditionalFormatting sqref="E29">
+    <cfRule type="duplicateValues" dxfId="6" priority="122"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E71">
-    <cfRule type="duplicateValues" dxfId="34" priority="119"/>
+  <conditionalFormatting sqref="E33">
+    <cfRule type="duplicateValues" dxfId="5" priority="121"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E75">
-    <cfRule type="duplicateValues" dxfId="33" priority="118"/>
+  <conditionalFormatting sqref="E37">
+    <cfRule type="duplicateValues" dxfId="4" priority="120"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E79">
-    <cfRule type="duplicateValues" dxfId="32" priority="117"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G38">
-    <cfRule type="duplicateValues" dxfId="31" priority="124"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="G115">
-    <cfRule type="duplicateValues" dxfId="30" priority="116"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1">
-    <cfRule type="duplicateValues" dxfId="29" priority="30"/>
+  <conditionalFormatting sqref="G73">
+    <cfRule type="duplicateValues" dxfId="3" priority="119"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="28" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="27" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5">
-    <cfRule type="duplicateValues" dxfId="25" priority="26"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7">
-    <cfRule type="duplicateValues" dxfId="23" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A8">
-    <cfRule type="duplicateValues" dxfId="22" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A9">
-    <cfRule type="duplicateValues" dxfId="21" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A10">
-    <cfRule type="duplicateValues" dxfId="20" priority="21"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A11">
-    <cfRule type="duplicateValues" dxfId="19" priority="20"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A12">
-    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A13">
-    <cfRule type="duplicateValues" dxfId="17" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A14">
-    <cfRule type="duplicateValues" dxfId="16" priority="17"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A15">
-    <cfRule type="duplicateValues" dxfId="15" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A16">
-    <cfRule type="duplicateValues" dxfId="14" priority="15"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A17">
-    <cfRule type="duplicateValues" dxfId="13" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A18">
-    <cfRule type="duplicateValues" dxfId="12" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A19">
-    <cfRule type="duplicateValues" dxfId="11" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A20">
-    <cfRule type="duplicateValues" dxfId="10" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A21">
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="duplicateValues" dxfId="8" priority="9"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A23">
-    <cfRule type="duplicateValues" dxfId="7" priority="8"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A24">
-    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A25">
-    <cfRule type="duplicateValues" dxfId="5" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A26">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A27">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A28">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A29">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A30">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/danhsachisbn.xlsx
+++ b/danhsachisbn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dominhquan/Desktop/Cdimex/cào data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D78E245-C6FA-9041-96F4-BAACDD2C0277}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332572FB-C740-6D48-9737-BE22C95885B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="600" windowWidth="19200" windowHeight="19800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10200" yWindow="660" windowWidth="19200" windowHeight="17280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,18 +23,2406 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="800">
   <si>
     <t>isbn</t>
   </si>
   <si>
-    <t>9781789894547</t>
-  </si>
-  <si>
-    <t>9781444939453</t>
-  </si>
-  <si>
-    <t>9780316381251</t>
+    <t>141338482</t>
+  </si>
+  <si>
+    <t>358451221</t>
+  </si>
+  <si>
+    <t>593708245</t>
+  </si>
+  <si>
+    <t>1100010033</t>
+  </si>
+  <si>
+    <t>1300010015</t>
+  </si>
+  <si>
+    <t>1300010072</t>
+  </si>
+  <si>
+    <t>1300010073</t>
+  </si>
+  <si>
+    <t>1400010001</t>
+  </si>
+  <si>
+    <t>1400010031</t>
+  </si>
+  <si>
+    <t>1400010036</t>
+  </si>
+  <si>
+    <t>1400010044</t>
+  </si>
+  <si>
+    <t>1400010045</t>
+  </si>
+  <si>
+    <t>1400010057</t>
+  </si>
+  <si>
+    <t>1400010058</t>
+  </si>
+  <si>
+    <t>1400010060</t>
+  </si>
+  <si>
+    <t>1400010061</t>
+  </si>
+  <si>
+    <t>1400010064</t>
+  </si>
+  <si>
+    <t>1400010065</t>
+  </si>
+  <si>
+    <t>1400010139</t>
+  </si>
+  <si>
+    <t>1400710001</t>
+  </si>
+  <si>
+    <t>1400710002</t>
+  </si>
+  <si>
+    <t>1400710003</t>
+  </si>
+  <si>
+    <t>1400710004</t>
+  </si>
+  <si>
+    <t>1400710005</t>
+  </si>
+  <si>
+    <t>1402140011</t>
+  </si>
+  <si>
+    <t>1402140012</t>
+  </si>
+  <si>
+    <t>1402140013</t>
+  </si>
+  <si>
+    <t>1402140014</t>
+  </si>
+  <si>
+    <t>1402140015</t>
+  </si>
+  <si>
+    <t>1402140016</t>
+  </si>
+  <si>
+    <t>1402140017</t>
+  </si>
+  <si>
+    <t>1402140018</t>
+  </si>
+  <si>
+    <t>1402140019</t>
+  </si>
+  <si>
+    <t>1402140020</t>
+  </si>
+  <si>
+    <t>1500010014</t>
+  </si>
+  <si>
+    <t>1500010017</t>
+  </si>
+  <si>
+    <t>1500010052</t>
+  </si>
+  <si>
+    <t>1500010060</t>
+  </si>
+  <si>
+    <t>1500010061</t>
+  </si>
+  <si>
+    <t>1500010065</t>
+  </si>
+  <si>
+    <t>1500010098</t>
+  </si>
+  <si>
+    <t>1507640002</t>
+  </si>
+  <si>
+    <t>1507640003</t>
+  </si>
+  <si>
+    <t>1507640009</t>
+  </si>
+  <si>
+    <t>1507640010</t>
+  </si>
+  <si>
+    <t>1507640011</t>
+  </si>
+  <si>
+    <t>1507640012</t>
+  </si>
+  <si>
+    <t>2308770001</t>
+  </si>
+  <si>
+    <t>2308770002</t>
+  </si>
+  <si>
+    <t>2308770003</t>
+  </si>
+  <si>
+    <t>2308770004</t>
+  </si>
+  <si>
+    <t>2308790001</t>
+  </si>
+  <si>
+    <t>2308790002</t>
+  </si>
+  <si>
+    <t>2308790003</t>
+  </si>
+  <si>
+    <t>2309190001</t>
+  </si>
+  <si>
+    <t>2309190002</t>
+  </si>
+  <si>
+    <t>2309190003</t>
+  </si>
+  <si>
+    <t>2309190005</t>
+  </si>
+  <si>
+    <t>2400010004</t>
+  </si>
+  <si>
+    <t>2400010047</t>
+  </si>
+  <si>
+    <t>2400010048</t>
+  </si>
+  <si>
+    <t>2400010064</t>
+  </si>
+  <si>
+    <t>2400010072</t>
+  </si>
+  <si>
+    <t>2400010085</t>
+  </si>
+  <si>
+    <t>2400010097</t>
+  </si>
+  <si>
+    <t>2402950001</t>
+  </si>
+  <si>
+    <t>2402950002</t>
+  </si>
+  <si>
+    <t>2402950003</t>
+  </si>
+  <si>
+    <t>2402950004</t>
+  </si>
+  <si>
+    <t>2402950005</t>
+  </si>
+  <si>
+    <t>2402950006</t>
+  </si>
+  <si>
+    <t>2402950007</t>
+  </si>
+  <si>
+    <t>2402950008</t>
+  </si>
+  <si>
+    <t>2402950009</t>
+  </si>
+  <si>
+    <t>2402950010</t>
+  </si>
+  <si>
+    <t>2403150001</t>
+  </si>
+  <si>
+    <t>2403150003</t>
+  </si>
+  <si>
+    <t>2403150005</t>
+  </si>
+  <si>
+    <t>2403150006</t>
+  </si>
+  <si>
+    <t>2403150007</t>
+  </si>
+  <si>
+    <t>2403150009</t>
+  </si>
+  <si>
+    <t>2403150011</t>
+  </si>
+  <si>
+    <t>2403150013</t>
+  </si>
+  <si>
+    <t>2403150014</t>
+  </si>
+  <si>
+    <t>2403150015</t>
+  </si>
+  <si>
+    <t>2403150016</t>
+  </si>
+  <si>
+    <t>2406970001</t>
+  </si>
+  <si>
+    <t>2406970005</t>
+  </si>
+  <si>
+    <t>2407590001</t>
+  </si>
+  <si>
+    <t>2407590002</t>
+  </si>
+  <si>
+    <t>2407590003</t>
+  </si>
+  <si>
+    <t>2407590005</t>
+  </si>
+  <si>
+    <t>2408490001</t>
+  </si>
+  <si>
+    <t>2408490002</t>
+  </si>
+  <si>
+    <t>2408490003</t>
+  </si>
+  <si>
+    <t>2408490004</t>
+  </si>
+  <si>
+    <t>2408490005</t>
+  </si>
+  <si>
+    <t>2409740003</t>
+  </si>
+  <si>
+    <t>2409740004</t>
+  </si>
+  <si>
+    <t>2409740010</t>
+  </si>
+  <si>
+    <t>2409740013</t>
+  </si>
+  <si>
+    <t>2500010018</t>
+  </si>
+  <si>
+    <t>2500010019</t>
+  </si>
+  <si>
+    <t>5212414310001</t>
+  </si>
+  <si>
+    <t>5212414310002</t>
+  </si>
+  <si>
+    <t>5212414310003</t>
+  </si>
+  <si>
+    <t>5212414310004</t>
+  </si>
+  <si>
+    <t>5212414310005</t>
+  </si>
+  <si>
+    <t>5212414750004</t>
+  </si>
+  <si>
+    <t>5212414750006</t>
+  </si>
+  <si>
+    <t>5212414750007</t>
+  </si>
+  <si>
+    <t>5212414750008</t>
+  </si>
+  <si>
+    <t>5212414790002</t>
+  </si>
+  <si>
+    <t>5212414790003</t>
+  </si>
+  <si>
+    <t>5212414790004</t>
+  </si>
+  <si>
+    <t>5212414840001</t>
+  </si>
+  <si>
+    <t>5212414840002</t>
+  </si>
+  <si>
+    <t>5212414840003</t>
+  </si>
+  <si>
+    <t>5241418780002</t>
+  </si>
+  <si>
+    <t>5241518760001</t>
+  </si>
+  <si>
+    <t>5242418230001</t>
+  </si>
+  <si>
+    <t>5242418230002</t>
+  </si>
+  <si>
+    <t>5242418230003</t>
+  </si>
+  <si>
+    <t>5242418230005</t>
+  </si>
+  <si>
+    <t>5242418230006</t>
+  </si>
+  <si>
+    <t>5242418230007</t>
+  </si>
+  <si>
+    <t>5242418230008</t>
+  </si>
+  <si>
+    <t>5242418230009</t>
+  </si>
+  <si>
+    <t>5242418230010</t>
+  </si>
+  <si>
+    <t>5242418750100</t>
+  </si>
+  <si>
+    <t>5251318790001</t>
+  </si>
+  <si>
+    <t>5251318790002</t>
+  </si>
+  <si>
+    <t>5251318790003</t>
+  </si>
+  <si>
+    <t>5251318790004</t>
+  </si>
+  <si>
+    <t>5251518760001</t>
+  </si>
+  <si>
+    <t>5252319900001</t>
+  </si>
+  <si>
+    <t>5252319900002</t>
+  </si>
+  <si>
+    <t>5252319900003</t>
+  </si>
+  <si>
+    <t>5252319900004</t>
+  </si>
+  <si>
+    <t>5252419070001</t>
+  </si>
+  <si>
+    <t>5252419070002</t>
+  </si>
+  <si>
+    <t>5252419070003</t>
+  </si>
+  <si>
+    <t>5252419420001</t>
+  </si>
+  <si>
+    <t>5252419420002</t>
+  </si>
+  <si>
+    <t>5252419420003</t>
+  </si>
+  <si>
+    <t>5252419420004</t>
+  </si>
+  <si>
+    <t>5252419420005</t>
+  </si>
+  <si>
+    <t>5252419420006</t>
+  </si>
+  <si>
+    <t>5252419420007</t>
+  </si>
+  <si>
+    <t>5252419420008</t>
+  </si>
+  <si>
+    <t>5252419420009</t>
+  </si>
+  <si>
+    <t>5252419420010</t>
+  </si>
+  <si>
+    <t>5252419490002</t>
+  </si>
+  <si>
+    <t>5252419490003</t>
+  </si>
+  <si>
+    <t>5252419490004</t>
+  </si>
+  <si>
+    <t>5252419490005</t>
+  </si>
+  <si>
+    <t>5252419490006</t>
+  </si>
+  <si>
+    <t>5252419490007</t>
+  </si>
+  <si>
+    <t>5252419490008</t>
+  </si>
+  <si>
+    <t>5252419490009</t>
+  </si>
+  <si>
+    <t>5252419510001</t>
+  </si>
+  <si>
+    <t>5252419510002</t>
+  </si>
+  <si>
+    <t>5252419510003</t>
+  </si>
+  <si>
+    <t>5252419510004</t>
+  </si>
+  <si>
+    <t>5252419520001</t>
+  </si>
+  <si>
+    <t>5252419520002</t>
+  </si>
+  <si>
+    <t>5252419840001</t>
+  </si>
+  <si>
+    <t>5252419840002</t>
+  </si>
+  <si>
+    <t>5252419840003</t>
+  </si>
+  <si>
+    <t>5252419840004</t>
+  </si>
+  <si>
+    <t>5252419840005</t>
+  </si>
+  <si>
+    <t>6222414700001</t>
+  </si>
+  <si>
+    <t>6232314420001</t>
+  </si>
+  <si>
+    <t>6232314420002</t>
+  </si>
+  <si>
+    <t>6232314420003</t>
+  </si>
+  <si>
+    <t>6232314420004</t>
+  </si>
+  <si>
+    <t>6232314420005</t>
+  </si>
+  <si>
+    <t>6232314420006</t>
+  </si>
+  <si>
+    <t>6232413360006</t>
+  </si>
+  <si>
+    <t>6232413360007</t>
+  </si>
+  <si>
+    <t>6232413360008</t>
+  </si>
+  <si>
+    <t>6232413360009</t>
+  </si>
+  <si>
+    <t>6232413360010</t>
+  </si>
+  <si>
+    <t>6232413360011</t>
+  </si>
+  <si>
+    <t>6232413360012</t>
+  </si>
+  <si>
+    <t>6232413360013</t>
+  </si>
+  <si>
+    <t>6232413360014</t>
+  </si>
+  <si>
+    <t>6232413360015</t>
+  </si>
+  <si>
+    <t>6232413360016</t>
+  </si>
+  <si>
+    <t>6232413360017</t>
+  </si>
+  <si>
+    <t>6232413970001</t>
+  </si>
+  <si>
+    <t>6232413970002</t>
+  </si>
+  <si>
+    <t>6232413970003</t>
+  </si>
+  <si>
+    <t>6232413970004</t>
+  </si>
+  <si>
+    <t>6232413970005</t>
+  </si>
+  <si>
+    <t>6232413970006</t>
+  </si>
+  <si>
+    <t>6232414700004</t>
+  </si>
+  <si>
+    <t>6232414700005</t>
+  </si>
+  <si>
+    <t>6242413360001</t>
+  </si>
+  <si>
+    <t>6242413360002</t>
+  </si>
+  <si>
+    <t>6242413360003</t>
+  </si>
+  <si>
+    <t>6242413360004</t>
+  </si>
+  <si>
+    <t>6242413360005</t>
+  </si>
+  <si>
+    <t>6242414700003</t>
+  </si>
+  <si>
+    <t>6251418780001</t>
+  </si>
+  <si>
+    <t>6251418780003</t>
+  </si>
+  <si>
+    <t>8934970000000</t>
+  </si>
+  <si>
+    <t>8934974201168</t>
+  </si>
+  <si>
+    <t>8934974201175</t>
+  </si>
+  <si>
+    <t>8934974201182</t>
+  </si>
+  <si>
+    <t>8934974201199</t>
+  </si>
+  <si>
+    <t>8934974201205</t>
+  </si>
+  <si>
+    <t>8934974201212</t>
+  </si>
+  <si>
+    <t>8934974201229</t>
+  </si>
+  <si>
+    <t>8934974202523</t>
+  </si>
+  <si>
+    <t>8934974202530</t>
+  </si>
+  <si>
+    <t>8934974202547</t>
+  </si>
+  <si>
+    <t>8934974202554</t>
+  </si>
+  <si>
+    <t>8934974202561</t>
+  </si>
+  <si>
+    <t>8934974202578</t>
+  </si>
+  <si>
+    <t>8934974202585</t>
+  </si>
+  <si>
+    <t>8934974202592</t>
+  </si>
+  <si>
+    <t>8934974202608</t>
+  </si>
+  <si>
+    <t>8934974208747</t>
+  </si>
+  <si>
+    <t>8934974208754</t>
+  </si>
+  <si>
+    <t>8934974208761</t>
+  </si>
+  <si>
+    <t>8934974208778</t>
+  </si>
+  <si>
+    <t>8934974208785</t>
+  </si>
+  <si>
+    <t>8934974208792</t>
+  </si>
+  <si>
+    <t>8934974208808</t>
+  </si>
+  <si>
+    <t>8934974208815</t>
+  </si>
+  <si>
+    <t>8935200000000</t>
+  </si>
+  <si>
+    <t>8935210000000</t>
+  </si>
+  <si>
+    <t>8935210302052</t>
+  </si>
+  <si>
+    <t>8935210302069</t>
+  </si>
+  <si>
+    <t>8935210302076</t>
+  </si>
+  <si>
+    <t>8935210275448</t>
+  </si>
+  <si>
+    <t>8935210275479</t>
+  </si>
+  <si>
+    <t>8935210275455</t>
+  </si>
+  <si>
+    <t>8935210275462</t>
+  </si>
+  <si>
+    <t>8935210307231</t>
+  </si>
+  <si>
+    <t>8935210251954</t>
+  </si>
+  <si>
+    <t>8935210251961</t>
+  </si>
+  <si>
+    <t>8935210307309</t>
+  </si>
+  <si>
+    <t>8935210307224</t>
+  </si>
+  <si>
+    <t>8935210274564</t>
+  </si>
+  <si>
+    <t>8935210296351</t>
+  </si>
+  <si>
+    <t>8935210302083</t>
+  </si>
+  <si>
+    <t>8935210302090</t>
+  </si>
+  <si>
+    <t>8935210302106</t>
+  </si>
+  <si>
+    <t>8935210302113</t>
+  </si>
+  <si>
+    <t>8935210302120</t>
+  </si>
+  <si>
+    <t>8935212355704</t>
+  </si>
+  <si>
+    <t>8935212355698</t>
+  </si>
+  <si>
+    <t>8935212355711</t>
+  </si>
+  <si>
+    <t>8935210307248</t>
+  </si>
+  <si>
+    <t>8935210302137</t>
+  </si>
+  <si>
+    <t>8935210307286</t>
+  </si>
+  <si>
+    <t>8935210307262</t>
+  </si>
+  <si>
+    <t>8935210307293</t>
+  </si>
+  <si>
+    <t>8935210302144</t>
+  </si>
+  <si>
+    <t>8935212371964</t>
+  </si>
+  <si>
+    <t>8935212367233</t>
+  </si>
+  <si>
+    <t>8935210307255</t>
+  </si>
+  <si>
+    <t>8935210306654</t>
+  </si>
+  <si>
+    <t>8935210307033</t>
+  </si>
+  <si>
+    <t>8935210307040</t>
+  </si>
+  <si>
+    <t>8935210307057</t>
+  </si>
+  <si>
+    <t>8935210307064</t>
+  </si>
+  <si>
+    <t>8935212333764</t>
+  </si>
+  <si>
+    <t>8935212335775</t>
+  </si>
+  <si>
+    <t>8935212335782</t>
+  </si>
+  <si>
+    <t>8935212335843</t>
+  </si>
+  <si>
+    <t>8935212338462</t>
+  </si>
+  <si>
+    <t>8935212338479</t>
+  </si>
+  <si>
+    <t>8935212338493</t>
+  </si>
+  <si>
+    <t>8935212338615</t>
+  </si>
+  <si>
+    <t>8935212338622</t>
+  </si>
+  <si>
+    <t>8935212338639</t>
+  </si>
+  <si>
+    <t>8935212338646</t>
+  </si>
+  <si>
+    <t>8935212338653</t>
+  </si>
+  <si>
+    <t>8935212338660</t>
+  </si>
+  <si>
+    <t>8935212338677</t>
+  </si>
+  <si>
+    <t>8935212338684</t>
+  </si>
+  <si>
+    <t>8935212338691</t>
+  </si>
+  <si>
+    <t>8935212342513</t>
+  </si>
+  <si>
+    <t>8935212342520</t>
+  </si>
+  <si>
+    <t>8935212342544</t>
+  </si>
+  <si>
+    <t>8935212342551</t>
+  </si>
+  <si>
+    <t>8935212342575</t>
+  </si>
+  <si>
+    <t>8935212342582</t>
+  </si>
+  <si>
+    <t>8935212342599</t>
+  </si>
+  <si>
+    <t>8935212342605</t>
+  </si>
+  <si>
+    <t>8935212342612</t>
+  </si>
+  <si>
+    <t>8935212342629</t>
+  </si>
+  <si>
+    <t>8935212342636</t>
+  </si>
+  <si>
+    <t>8935212342643</t>
+  </si>
+  <si>
+    <t>8935212342650</t>
+  </si>
+  <si>
+    <t>8935212342667</t>
+  </si>
+  <si>
+    <t>8935212342674</t>
+  </si>
+  <si>
+    <t>8935212342681</t>
+  </si>
+  <si>
+    <t>8935212343992</t>
+  </si>
+  <si>
+    <t>8935212344012</t>
+  </si>
+  <si>
+    <t>8935212346108</t>
+  </si>
+  <si>
+    <t>8935212347297</t>
+  </si>
+  <si>
+    <t>8935212348478</t>
+  </si>
+  <si>
+    <t>8935212348485</t>
+  </si>
+  <si>
+    <t>8935212348492</t>
+  </si>
+  <si>
+    <t>8935212350129</t>
+  </si>
+  <si>
+    <t>8935212350136</t>
+  </si>
+  <si>
+    <t>8935212351836</t>
+  </si>
+  <si>
+    <t>8935212351843</t>
+  </si>
+  <si>
+    <t>8935212351911</t>
+  </si>
+  <si>
+    <t>8935212352659</t>
+  </si>
+  <si>
+    <t>8935212352666</t>
+  </si>
+  <si>
+    <t>8935212353212</t>
+  </si>
+  <si>
+    <t>8935212353229</t>
+  </si>
+  <si>
+    <t>8935212353236</t>
+  </si>
+  <si>
+    <t>8935212353243</t>
+  </si>
+  <si>
+    <t>8935212353274</t>
+  </si>
+  <si>
+    <t>8935212353281</t>
+  </si>
+  <si>
+    <t>8935212353298</t>
+  </si>
+  <si>
+    <t>8935212353656</t>
+  </si>
+  <si>
+    <t>8935212353663</t>
+  </si>
+  <si>
+    <t>8935212354561</t>
+  </si>
+  <si>
+    <t>8935212354578</t>
+  </si>
+  <si>
+    <t>8935212354585</t>
+  </si>
+  <si>
+    <t>8935212354592</t>
+  </si>
+  <si>
+    <t>8935212354608</t>
+  </si>
+  <si>
+    <t>8935212354615</t>
+  </si>
+  <si>
+    <t>8935212354622</t>
+  </si>
+  <si>
+    <t>8935212354639</t>
+  </si>
+  <si>
+    <t>8935212357050</t>
+  </si>
+  <si>
+    <t>8935212357142</t>
+  </si>
+  <si>
+    <t>8935212357159</t>
+  </si>
+  <si>
+    <t>8935212357166</t>
+  </si>
+  <si>
+    <t>8935212357173</t>
+  </si>
+  <si>
+    <t>8935212357456</t>
+  </si>
+  <si>
+    <t>8935212357470</t>
+  </si>
+  <si>
+    <t>8935212358354</t>
+  </si>
+  <si>
+    <t>8935212358361</t>
+  </si>
+  <si>
+    <t>8935212358705</t>
+  </si>
+  <si>
+    <t>8935212359191</t>
+  </si>
+  <si>
+    <t>8935212359207</t>
+  </si>
+  <si>
+    <t>8935212359214</t>
+  </si>
+  <si>
+    <t>8935212359221</t>
+  </si>
+  <si>
+    <t>8935212359238</t>
+  </si>
+  <si>
+    <t>8935212359245</t>
+  </si>
+  <si>
+    <t>8935212359252</t>
+  </si>
+  <si>
+    <t>8935212359269</t>
+  </si>
+  <si>
+    <t>8935212360456</t>
+  </si>
+  <si>
+    <t>8935212360463</t>
+  </si>
+  <si>
+    <t>8935212360470</t>
+  </si>
+  <si>
+    <t>8935212360487</t>
+  </si>
+  <si>
+    <t>8935212360494</t>
+  </si>
+  <si>
+    <t>8935212360500</t>
+  </si>
+  <si>
+    <t>8935212360517</t>
+  </si>
+  <si>
+    <t>8935212360524</t>
+  </si>
+  <si>
+    <t>8935212360531</t>
+  </si>
+  <si>
+    <t>8935212360548</t>
+  </si>
+  <si>
+    <t>8935212360555</t>
+  </si>
+  <si>
+    <t>8935212360609</t>
+  </si>
+  <si>
+    <t>8935212361194</t>
+  </si>
+  <si>
+    <t>8935212362108</t>
+  </si>
+  <si>
+    <t>8935212362115</t>
+  </si>
+  <si>
+    <t>8935212362528</t>
+  </si>
+  <si>
+    <t>8935212363501</t>
+  </si>
+  <si>
+    <t>8935212363518</t>
+  </si>
+  <si>
+    <t>8935212363525</t>
+  </si>
+  <si>
+    <t>8935212363815</t>
+  </si>
+  <si>
+    <t>8935212363822</t>
+  </si>
+  <si>
+    <t>8935212363839</t>
+  </si>
+  <si>
+    <t>8935212363846</t>
+  </si>
+  <si>
+    <t>8935212364140</t>
+  </si>
+  <si>
+    <t>8935212364157</t>
+  </si>
+  <si>
+    <t>8935212364164</t>
+  </si>
+  <si>
+    <t>8935212364171</t>
+  </si>
+  <si>
+    <t>8935212364188</t>
+  </si>
+  <si>
+    <t>8935212364195</t>
+  </si>
+  <si>
+    <t>8935212364201</t>
+  </si>
+  <si>
+    <t>8935212364973</t>
+  </si>
+  <si>
+    <t>8935212364980</t>
+  </si>
+  <si>
+    <t>8935212364997</t>
+  </si>
+  <si>
+    <t>8935212365000</t>
+  </si>
+  <si>
+    <t>8935212365017</t>
+  </si>
+  <si>
+    <t>8935212365598</t>
+  </si>
+  <si>
+    <t>8935212365604</t>
+  </si>
+  <si>
+    <t>8935212365611</t>
+  </si>
+  <si>
+    <t>8935212365628</t>
+  </si>
+  <si>
+    <t>8935212366700</t>
+  </si>
+  <si>
+    <t>8935212366717</t>
+  </si>
+  <si>
+    <t>8935212366724</t>
+  </si>
+  <si>
+    <t>8935212366731</t>
+  </si>
+  <si>
+    <t>8935212366847</t>
+  </si>
+  <si>
+    <t>8935212366854</t>
+  </si>
+  <si>
+    <t>8935212366861</t>
+  </si>
+  <si>
+    <t>8935212367363</t>
+  </si>
+  <si>
+    <t>8935212367370</t>
+  </si>
+  <si>
+    <t>8935212367387</t>
+  </si>
+  <si>
+    <t>8935212368001</t>
+  </si>
+  <si>
+    <t>8935212368018</t>
+  </si>
+  <si>
+    <t>8935212368025</t>
+  </si>
+  <si>
+    <t>8935212368032</t>
+  </si>
+  <si>
+    <t>8935212368049</t>
+  </si>
+  <si>
+    <t>8935212368056</t>
+  </si>
+  <si>
+    <t>8935212368186</t>
+  </si>
+  <si>
+    <t>8935212368193</t>
+  </si>
+  <si>
+    <t>8935212368544</t>
+  </si>
+  <si>
+    <t>8935212368667</t>
+  </si>
+  <si>
+    <t>8935212368674</t>
+  </si>
+  <si>
+    <t>8935212368681</t>
+  </si>
+  <si>
+    <t>8935212368698</t>
+  </si>
+  <si>
+    <t>8935212368704</t>
+  </si>
+  <si>
+    <t>8935212368711</t>
+  </si>
+  <si>
+    <t>8935212368728</t>
+  </si>
+  <si>
+    <t>8935212368735</t>
+  </si>
+  <si>
+    <t>8935212368742</t>
+  </si>
+  <si>
+    <t>8935212368759</t>
+  </si>
+  <si>
+    <t>8935212370066</t>
+  </si>
+  <si>
+    <t>8935212370073</t>
+  </si>
+  <si>
+    <t>8935212370080</t>
+  </si>
+  <si>
+    <t>8935212370097</t>
+  </si>
+  <si>
+    <t>8935212370103</t>
+  </si>
+  <si>
+    <t>8935212370110</t>
+  </si>
+  <si>
+    <t>8935212370141</t>
+  </si>
+  <si>
+    <t>8935212370158</t>
+  </si>
+  <si>
+    <t>8935212370196</t>
+  </si>
+  <si>
+    <t>8935212370202</t>
+  </si>
+  <si>
+    <t>8935212370219</t>
+  </si>
+  <si>
+    <t>8935212370226</t>
+  </si>
+  <si>
+    <t>8935212371124</t>
+  </si>
+  <si>
+    <t>8935212371131</t>
+  </si>
+  <si>
+    <t>8935212371148</t>
+  </si>
+  <si>
+    <t>8935212371155</t>
+  </si>
+  <si>
+    <t>8935212371285</t>
+  </si>
+  <si>
+    <t>8935212371834</t>
+  </si>
+  <si>
+    <t>8935212371841</t>
+  </si>
+  <si>
+    <t>8935212371858</t>
+  </si>
+  <si>
+    <t>8935212371865</t>
+  </si>
+  <si>
+    <t>8935212371872</t>
+  </si>
+  <si>
+    <t>8935212372138</t>
+  </si>
+  <si>
+    <t>8935212372145</t>
+  </si>
+  <si>
+    <t>8935212372251</t>
+  </si>
+  <si>
+    <t>8935212372268</t>
+  </si>
+  <si>
+    <t>8935212372275</t>
+  </si>
+  <si>
+    <t>8935212372282</t>
+  </si>
+  <si>
+    <t>8935212372299</t>
+  </si>
+  <si>
+    <t>8935212372398</t>
+  </si>
+  <si>
+    <t>8935212372947</t>
+  </si>
+  <si>
+    <t>8935212372954</t>
+  </si>
+  <si>
+    <t>8935212373814</t>
+  </si>
+  <si>
+    <t>8935212373821</t>
+  </si>
+  <si>
+    <t>8935212373838</t>
+  </si>
+  <si>
+    <t>8935212373845</t>
+  </si>
+  <si>
+    <t>8935212374118</t>
+  </si>
+  <si>
+    <t>8935212374125</t>
+  </si>
+  <si>
+    <t>8935212374132</t>
+  </si>
+  <si>
+    <t>8935212374149</t>
+  </si>
+  <si>
+    <t>8935212374156</t>
+  </si>
+  <si>
+    <t>8935212374170</t>
+  </si>
+  <si>
+    <t>8935212374187</t>
+  </si>
+  <si>
+    <t>8935212374194</t>
+  </si>
+  <si>
+    <t>8935212374200</t>
+  </si>
+  <si>
+    <t>8935212374217</t>
+  </si>
+  <si>
+    <t>8935212374224</t>
+  </si>
+  <si>
+    <t>8935212374231</t>
+  </si>
+  <si>
+    <t>8935212374835</t>
+  </si>
+  <si>
+    <t>8935235238220</t>
+  </si>
+  <si>
+    <t>8935235238886</t>
+  </si>
+  <si>
+    <t>8935235238893</t>
+  </si>
+  <si>
+    <t>8935235238909</t>
+  </si>
+  <si>
+    <t>8935235238916</t>
+  </si>
+  <si>
+    <t>8935235238923</t>
+  </si>
+  <si>
+    <t>8935235238930</t>
+  </si>
+  <si>
+    <t>8935235240339</t>
+  </si>
+  <si>
+    <t>8935240000000</t>
+  </si>
+  <si>
+    <t>8935235219144</t>
+  </si>
+  <si>
+    <t>8935235236837</t>
+  </si>
+  <si>
+    <t>8935244860863</t>
+  </si>
+  <si>
+    <t>8935235229938</t>
+  </si>
+  <si>
+    <t>8935244893687</t>
+  </si>
+  <si>
+    <t>8935244822359</t>
+  </si>
+  <si>
+    <t>8935244822427</t>
+  </si>
+  <si>
+    <t>8935244839180</t>
+  </si>
+  <si>
+    <t>8935244839203</t>
+  </si>
+  <si>
+    <t>8935244839227</t>
+  </si>
+  <si>
+    <t>8935244854886</t>
+  </si>
+  <si>
+    <t>8935244854893</t>
+  </si>
+  <si>
+    <t>8935244854916</t>
+  </si>
+  <si>
+    <t>8935244854923</t>
+  </si>
+  <si>
+    <t>8935244868975</t>
+  </si>
+  <si>
+    <t>8935244874624</t>
+  </si>
+  <si>
+    <t>8935244874631</t>
+  </si>
+  <si>
+    <t>8935244874648</t>
+  </si>
+  <si>
+    <t>8935244874655</t>
+  </si>
+  <si>
+    <t>8935244874662</t>
+  </si>
+  <si>
+    <t>8935244882247</t>
+  </si>
+  <si>
+    <t>8935244882254</t>
+  </si>
+  <si>
+    <t>8935244882261</t>
+  </si>
+  <si>
+    <t>8935244882278</t>
+  </si>
+  <si>
+    <t>8935244882285</t>
+  </si>
+  <si>
+    <t>8935330000000</t>
+  </si>
+  <si>
+    <t>8935350000000</t>
+  </si>
+  <si>
+    <t>8935352601693</t>
+  </si>
+  <si>
+    <t>8935352601709</t>
+  </si>
+  <si>
+    <t>8935352601716</t>
+  </si>
+  <si>
+    <t>8935352601723</t>
+  </si>
+  <si>
+    <t>8935352601754</t>
+  </si>
+  <si>
+    <t>8935352612019</t>
+  </si>
+  <si>
+    <t>8935352612026</t>
+  </si>
+  <si>
+    <t>8935352612033</t>
+  </si>
+  <si>
+    <t>8935352612040</t>
+  </si>
+  <si>
+    <t>8935352614341</t>
+  </si>
+  <si>
+    <t>8935352614358</t>
+  </si>
+  <si>
+    <t>8935352614372</t>
+  </si>
+  <si>
+    <t>8935352614389</t>
+  </si>
+  <si>
+    <t>8935352614396</t>
+  </si>
+  <si>
+    <t>8935352614402</t>
+  </si>
+  <si>
+    <t>8935352614419</t>
+  </si>
+  <si>
+    <t>8935352614426</t>
+  </si>
+  <si>
+    <t>8935352615218</t>
+  </si>
+  <si>
+    <t>8935352615225</t>
+  </si>
+  <si>
+    <t>8935352615232</t>
+  </si>
+  <si>
+    <t>8935352615928</t>
+  </si>
+  <si>
+    <t>8935352615959</t>
+  </si>
+  <si>
+    <t>8935352615973</t>
+  </si>
+  <si>
+    <t>8935352615980</t>
+  </si>
+  <si>
+    <t>8935352616000</t>
+  </si>
+  <si>
+    <t>8935352616017</t>
+  </si>
+  <si>
+    <t>8935352617816</t>
+  </si>
+  <si>
+    <t>8935352617823</t>
+  </si>
+  <si>
+    <t>8935352617830</t>
+  </si>
+  <si>
+    <t>8935352617847</t>
+  </si>
+  <si>
+    <t>8936160000000</t>
+  </si>
+  <si>
+    <t>8936173840421</t>
+  </si>
+  <si>
+    <t>8936173840544</t>
+  </si>
+  <si>
+    <t>8936173840551</t>
+  </si>
+  <si>
+    <t>8936173840988</t>
+  </si>
+  <si>
+    <t>8936173841008</t>
+  </si>
+  <si>
+    <t>8936173841015</t>
+  </si>
+  <si>
+    <t>8936173841022</t>
+  </si>
+  <si>
+    <t>8936173841039</t>
+  </si>
+  <si>
+    <t>8936173841602</t>
+  </si>
+  <si>
+    <t>8936173841619</t>
+  </si>
+  <si>
+    <t>8936173841633</t>
+  </si>
+  <si>
+    <t>8936173841640</t>
+  </si>
+  <si>
+    <t>8936173841657</t>
+  </si>
+  <si>
+    <t>8936173841664</t>
+  </si>
+  <si>
+    <t>8936173841671</t>
+  </si>
+  <si>
+    <t>8936173841701</t>
+  </si>
+  <si>
+    <t>8936173841725</t>
+  </si>
+  <si>
+    <t>8936173841732</t>
+  </si>
+  <si>
+    <t>8936173841749</t>
+  </si>
+  <si>
+    <t>8936173841923</t>
+  </si>
+  <si>
+    <t>8936173841930</t>
+  </si>
+  <si>
+    <t>8936173841947</t>
+  </si>
+  <si>
+    <t>8936173842074</t>
+  </si>
+  <si>
+    <t>8936173842081</t>
+  </si>
+  <si>
+    <t>8936173842098</t>
+  </si>
+  <si>
+    <t>8936173842104</t>
+  </si>
+  <si>
+    <t>8936210000000</t>
+  </si>
+  <si>
+    <t>8936218410244</t>
+  </si>
+  <si>
+    <t>8936218410299</t>
+  </si>
+  <si>
+    <t>8936218410428</t>
+  </si>
+  <si>
+    <t>8936218410435</t>
+  </si>
+  <si>
+    <t>8936218410442</t>
+  </si>
+  <si>
+    <t>8936218410459</t>
+  </si>
+  <si>
+    <t>8938532871343</t>
+  </si>
+  <si>
+    <t>8938532871350</t>
+  </si>
+  <si>
+    <t>8938532871367</t>
+  </si>
+  <si>
+    <t>8938532871497</t>
+  </si>
+  <si>
+    <t>8938532871503</t>
+  </si>
+  <si>
+    <t>8938532871510</t>
+  </si>
+  <si>
+    <t>8938532871527</t>
+  </si>
+  <si>
+    <t>8938540000000</t>
+  </si>
+  <si>
+    <t>9780007150342</t>
+  </si>
+  <si>
+    <t>9780007988860</t>
+  </si>
+  <si>
+    <t>9780008280581</t>
+  </si>
+  <si>
+    <t>9780062381927</t>
+  </si>
+  <si>
+    <t>9780064432801</t>
+  </si>
+  <si>
+    <t>9780141363752</t>
+  </si>
+  <si>
+    <t>9780141383514</t>
+  </si>
+  <si>
+    <t>9780241294567</t>
+  </si>
+  <si>
+    <t>9780241351826</t>
+  </si>
+  <si>
+    <t>9780241375853</t>
+  </si>
+  <si>
+    <t>9780241379097</t>
+  </si>
+  <si>
+    <t>9780241379158</t>
+  </si>
+  <si>
+    <t>9780241502358</t>
+  </si>
+  <si>
+    <t>9780241563861</t>
+  </si>
+  <si>
+    <t>9780241564189</t>
+  </si>
+  <si>
+    <t>9780241609866</t>
+  </si>
+  <si>
+    <t>9780241648926</t>
+  </si>
+  <si>
+    <t>9780241660423</t>
+  </si>
+  <si>
+    <t>9780241669518</t>
+  </si>
+  <si>
+    <t>9780241669693</t>
+  </si>
+  <si>
+    <t>9780241669853</t>
+  </si>
+  <si>
+    <t>9780241680810</t>
+  </si>
+  <si>
+    <t>9780241714768</t>
+  </si>
+  <si>
+    <t>9780307960306</t>
+  </si>
+  <si>
+    <t>9780312518516</t>
+  </si>
+  <si>
+    <t>9780316070409</t>
+  </si>
+  <si>
+    <t>9780316452144</t>
+  </si>
+  <si>
+    <t>9780375826320</t>
+  </si>
+  <si>
+    <t>9780375858130</t>
+  </si>
+  <si>
+    <t>9780399226908</t>
+  </si>
+  <si>
+    <t>9780399240461</t>
+  </si>
+  <si>
+    <t>9780553521016</t>
+  </si>
+  <si>
+    <t>9780593176757</t>
+  </si>
+  <si>
+    <t>9780593223932</t>
+  </si>
+  <si>
+    <t>9780593528600</t>
+  </si>
+  <si>
+    <t>9780593750636</t>
+  </si>
+  <si>
+    <t>9780593887943</t>
+  </si>
+  <si>
+    <t>9780618956746</t>
+  </si>
+  <si>
+    <t>9780655228400</t>
+  </si>
+  <si>
+    <t>9780655228417</t>
+  </si>
+  <si>
+    <t>9780655228431</t>
+  </si>
+  <si>
+    <t>9780655228653</t>
+  </si>
+  <si>
+    <t>9780655232698</t>
+  </si>
+  <si>
+    <t>9780655233541</t>
+  </si>
+  <si>
+    <t>9780655234128</t>
+  </si>
+  <si>
+    <t>9780655235811</t>
+  </si>
+  <si>
+    <t>9780655237235</t>
+  </si>
+  <si>
+    <t>9780660000000</t>
+  </si>
+  <si>
+    <t>9780694011476</t>
+  </si>
+  <si>
+    <t>9780694013012</t>
+  </si>
+  <si>
+    <t>9780698115637</t>
+  </si>
+  <si>
+    <t>9780709728801</t>
+  </si>
+  <si>
+    <t>9780744536348</t>
+  </si>
+  <si>
+    <t>9780744547016</t>
+  </si>
+  <si>
+    <t>9780747599906</t>
+  </si>
+  <si>
+    <t>9780763695194</t>
+  </si>
+  <si>
+    <t>9780769658681</t>
+  </si>
+  <si>
+    <t>9780805013153</t>
+  </si>
+  <si>
+    <t>9780805047905</t>
+  </si>
+  <si>
+    <t>9780805053883</t>
+  </si>
+  <si>
+    <t>9780823410255</t>
+  </si>
+  <si>
+    <t>9780859531238</t>
+  </si>
+  <si>
+    <t>9780943990033</t>
+  </si>
+  <si>
+    <t>9781107549098</t>
+  </si>
+  <si>
+    <t>9781107549241</t>
+  </si>
+  <si>
+    <t>9781107549364</t>
+  </si>
+  <si>
+    <t>9781107549494</t>
+  </si>
+  <si>
+    <t>9781107549579</t>
+  </si>
+  <si>
+    <t>9781107549630</t>
+  </si>
+  <si>
+    <t>9781107549739</t>
+  </si>
+  <si>
+    <t>9781107549876</t>
+  </si>
+  <si>
+    <t>9781107549937</t>
+  </si>
+  <si>
+    <t>9781107549968</t>
+  </si>
+  <si>
+    <t>9781107550001</t>
+  </si>
+  <si>
+    <t>9781107550063</t>
+  </si>
+  <si>
+    <t>9781107550216</t>
+  </si>
+  <si>
+    <t>9781107550704</t>
+  </si>
+  <si>
+    <t>9781107560321</t>
+  </si>
+  <si>
+    <t>9781107575721</t>
+  </si>
+  <si>
+    <t>9781107575783</t>
+  </si>
+  <si>
+    <t>9781107575820</t>
+  </si>
+  <si>
+    <t>9781107575844</t>
+  </si>
+  <si>
+    <t>9781107575943</t>
+  </si>
+  <si>
+    <t>9781107575974</t>
+  </si>
+  <si>
+    <t>9781107576766</t>
+  </si>
+  <si>
+    <t>9781107576797</t>
+  </si>
+  <si>
+    <t>9781108400664</t>
+  </si>
+  <si>
+    <t>9781108400695</t>
+  </si>
+  <si>
+    <t>9781108400725</t>
+  </si>
+  <si>
+    <t>9781108400770</t>
+  </si>
+  <si>
+    <t>9781108401913</t>
+  </si>
+  <si>
+    <t>9781108405669</t>
+  </si>
+  <si>
+    <t>9781108405690</t>
+  </si>
+  <si>
+    <t>9781108408158</t>
+  </si>
+  <si>
+    <t>9781108410793</t>
+  </si>
+  <si>
+    <t>9781108435376</t>
+  </si>
+  <si>
+    <t>9781108439619</t>
+  </si>
+  <si>
+    <t>9781108439633</t>
+  </si>
+  <si>
+    <t>9781108439640</t>
+  </si>
+  <si>
+    <t>9781108439671</t>
+  </si>
+  <si>
+    <t>9781108439718</t>
+  </si>
+  <si>
+    <t>9781108439725</t>
+  </si>
+  <si>
+    <t>9781316500781</t>
+  </si>
+  <si>
+    <t>9781316500811</t>
+  </si>
+  <si>
+    <t>9781316503089</t>
+  </si>
+  <si>
+    <t>9781316503102</t>
+  </si>
+  <si>
+    <t>9781316503133</t>
+  </si>
+  <si>
+    <t>9781316503157</t>
+  </si>
+  <si>
+    <t>9781316503188</t>
+  </si>
+  <si>
+    <t>9781316503201</t>
+  </si>
+  <si>
+    <t>9781316503225</t>
+  </si>
+  <si>
+    <t>9781316600696</t>
+  </si>
+  <si>
+    <t>9781316600719</t>
+  </si>
+  <si>
+    <t>9781316600733</t>
+  </si>
+  <si>
+    <t>9781316600788</t>
+  </si>
+  <si>
+    <t>9781316600825</t>
+  </si>
+  <si>
+    <t>9781316600849</t>
+  </si>
+  <si>
+    <t>9781316600863</t>
+  </si>
+  <si>
+    <t>9781316605684</t>
+  </si>
+  <si>
+    <t>9781316605769</t>
+  </si>
+  <si>
+    <t>9781316605790</t>
+  </si>
+  <si>
+    <t>9781316605820</t>
+  </si>
+  <si>
+    <t>9781316608104</t>
+  </si>
+  <si>
+    <t>9781316608111</t>
+  </si>
+  <si>
+    <t>9781405336802</t>
+  </si>
+  <si>
+    <t>9781405392570</t>
+  </si>
+  <si>
+    <t>9781406373660</t>
+  </si>
+  <si>
+    <t>9781407170718</t>
+  </si>
+  <si>
+    <t>9781408331606</t>
+  </si>
+  <si>
+    <t>9781408361795</t>
+  </si>
+  <si>
+    <t>9781409376019</t>
+  </si>
+  <si>
+    <t>9781409563938</t>
+  </si>
+  <si>
+    <t>9781416979173</t>
+  </si>
+  <si>
+    <t>9781420000000</t>
+  </si>
+  <si>
+    <t>9781442450707</t>
+  </si>
+  <si>
+    <t>9781442458420</t>
+  </si>
+  <si>
+    <t>9781444918151</t>
+  </si>
+  <si>
+    <t>9781474823388</t>
+  </si>
+  <si>
+    <t>9781474823425</t>
+  </si>
+  <si>
+    <t>9781474823517</t>
+  </si>
+  <si>
+    <t>9781474943611</t>
+  </si>
+  <si>
+    <t>9781474952965</t>
+  </si>
+  <si>
+    <t>9781474959049</t>
+  </si>
+  <si>
+    <t>9781474969635</t>
+  </si>
+  <si>
+    <t>9781474986939</t>
+  </si>
+  <si>
+    <t>9781474989466</t>
+  </si>
+  <si>
+    <t>9781474991537</t>
+  </si>
+  <si>
+    <t>9781474999625</t>
+  </si>
+  <si>
+    <t>9781474999632</t>
+  </si>
+  <si>
+    <t>9781481472494</t>
+  </si>
+  <si>
+    <t>9781503773424</t>
+  </si>
+  <si>
+    <t>9781503774353</t>
+  </si>
+  <si>
+    <t>9781523515967</t>
+  </si>
+  <si>
+    <t>9781523515974</t>
+  </si>
+  <si>
+    <t>9781524792688</t>
+  </si>
+  <si>
+    <t>9781527008595</t>
+  </si>
+  <si>
+    <t>9781529051407</t>
+  </si>
+  <si>
+    <t>9781529056945</t>
+  </si>
+  <si>
+    <t>9781529072532</t>
+  </si>
+  <si>
+    <t>9781529083392</t>
+  </si>
+  <si>
+    <t>9781529084634</t>
+  </si>
+  <si>
+    <t>9781577681786</t>
+  </si>
+  <si>
+    <t>9781577681984</t>
+  </si>
+  <si>
+    <t>9781627797238</t>
+  </si>
+  <si>
+    <t>9781760524333</t>
+  </si>
+  <si>
+    <t>9781785989087</t>
+  </si>
+  <si>
+    <t>9781786289452</t>
+  </si>
+  <si>
+    <t>9781787419209</t>
+  </si>
+  <si>
+    <t>9781789891157</t>
+  </si>
+  <si>
+    <t>9781789899184</t>
+  </si>
+  <si>
+    <t>9781800582828</t>
+  </si>
+  <si>
+    <t>9781800780910</t>
+  </si>
+  <si>
+    <t>9781801052740</t>
+  </si>
+  <si>
+    <t>9781801312431</t>
+  </si>
+  <si>
+    <t>9781801313155</t>
+  </si>
+  <si>
+    <t>9781803372396</t>
+  </si>
+  <si>
+    <t>9781803685311</t>
+  </si>
+  <si>
+    <t>9781805444640</t>
+  </si>
+  <si>
+    <t>9781805444695</t>
+  </si>
+  <si>
+    <t>9781836422075</t>
+  </si>
+  <si>
+    <t>9781836429944</t>
+  </si>
+  <si>
+    <t>9781838993238</t>
+  </si>
+  <si>
+    <t>9781838993313</t>
+  </si>
+  <si>
+    <t>9781838993467</t>
+  </si>
+  <si>
+    <t>9781838993665</t>
+  </si>
+  <si>
+    <t>9781838993733</t>
+  </si>
+  <si>
+    <t>9781838993740</t>
+  </si>
+  <si>
+    <t>9781839034732</t>
+  </si>
+  <si>
+    <t>9781839238987</t>
+  </si>
+  <si>
+    <t>9781839238994</t>
+  </si>
+  <si>
+    <t>9781923168367</t>
+  </si>
+  <si>
+    <t>9786040000000</t>
+  </si>
+  <si>
+    <t>9786040269539</t>
+  </si>
+  <si>
+    <t>9786044435077</t>
+  </si>
+  <si>
+    <t>9786044435084</t>
+  </si>
+  <si>
+    <t>9786044435060</t>
+  </si>
+  <si>
+    <t>9786044413532</t>
+  </si>
+  <si>
+    <t>9786044413556</t>
+  </si>
+  <si>
+    <t>9786044413449</t>
+  </si>
+  <si>
+    <t>9786040170897</t>
+  </si>
+  <si>
+    <t>9786044435015</t>
+  </si>
+  <si>
+    <t>9786044413563</t>
+  </si>
+  <si>
+    <t>9786040375742</t>
+  </si>
+  <si>
+    <t>9786042393577</t>
+  </si>
+  <si>
+    <t>9786042393584</t>
+  </si>
+  <si>
+    <t>9786042393591</t>
+  </si>
+  <si>
+    <t>9786042393607</t>
+  </si>
+  <si>
+    <t>9786042393614</t>
+  </si>
+  <si>
+    <t>9786050000000</t>
+  </si>
+  <si>
+    <t>9788830329645</t>
+  </si>
+  <si>
+    <t>9789350892596</t>
+  </si>
+  <si>
+    <t>9789350892619</t>
+  </si>
+  <si>
+    <t>9789350892626</t>
+  </si>
+  <si>
+    <t>9789464765212</t>
+  </si>
+  <si>
+    <t>9789811400254</t>
+  </si>
+  <si>
+    <t>89352000000000000</t>
+  </si>
+  <si>
+    <t>9780007988877</t>
+  </si>
+  <si>
+    <t>9780007988884</t>
+  </si>
+  <si>
+    <t>9780007988891</t>
+  </si>
+  <si>
+    <t>9781634400824</t>
+  </si>
+  <si>
+    <t>9781789893250</t>
+  </si>
+  <si>
+    <t>CB415080001</t>
+  </si>
+  <si>
+    <t>CB415090001</t>
+  </si>
+  <si>
+    <t>CB518900001</t>
   </si>
 </sst>
 </file>
@@ -44,7 +2432,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -118,13 +2506,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -134,27 +2515,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -204,9 +2570,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma 7" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -220,27 +2584,7 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -320,7 +2664,27 @@
         <color rgb="FF9C0006"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
@@ -646,7 +3010,9 @@
       <c r="D4" s="8"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A5"/>
+      <c r="A5" s="21" t="s">
+        <v>4</v>
+      </c>
       <c r="C5" s="2"/>
       <c r="D5" s="8"/>
       <c r="G5"/>
@@ -656,7 +3022,9 @@
       <c r="Q5" s="7"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A6"/>
+      <c r="A6" s="21" t="s">
+        <v>5</v>
+      </c>
       <c r="C6" s="2"/>
       <c r="D6" s="8"/>
       <c r="G6"/>
@@ -666,7 +3034,9 @@
       <c r="Q6" s="7"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7"/>
+      <c r="A7" s="21" t="s">
+        <v>6</v>
+      </c>
       <c r="C7" s="2"/>
       <c r="D7" s="8"/>
       <c r="G7"/>
@@ -677,7 +3047,9 @@
       <c r="Q7" s="7"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A8"/>
+      <c r="A8" s="21" t="s">
+        <v>7</v>
+      </c>
       <c r="C8" s="2"/>
       <c r="D8" s="8"/>
       <c r="F8" s="9"/>
@@ -688,7 +3060,9 @@
       <c r="Q8" s="7"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A9"/>
+      <c r="A9" s="21" t="s">
+        <v>8</v>
+      </c>
       <c r="C9" s="2"/>
       <c r="D9" s="8"/>
       <c r="G9"/>
@@ -698,7 +3072,9 @@
       <c r="Q9" s="7"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A10"/>
+      <c r="A10" s="21" t="s">
+        <v>9</v>
+      </c>
       <c r="C10" s="2"/>
       <c r="D10" s="8"/>
       <c r="G10"/>
@@ -708,7 +3084,9 @@
       <c r="Q10" s="7"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A11"/>
+      <c r="A11" s="21" t="s">
+        <v>10</v>
+      </c>
       <c r="C11" s="2"/>
       <c r="D11" s="8"/>
       <c r="E11" s="11"/>
@@ -719,7 +3097,9 @@
       <c r="Q11" s="7"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A12"/>
+      <c r="A12" s="21" t="s">
+        <v>11</v>
+      </c>
       <c r="C12" s="2"/>
       <c r="D12" s="8"/>
       <c r="G12"/>
@@ -729,7 +3109,9 @@
       <c r="Q12" s="7"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13"/>
+      <c r="A13" s="21" t="s">
+        <v>12</v>
+      </c>
       <c r="C13" s="2"/>
       <c r="D13" s="8"/>
       <c r="G13"/>
@@ -739,7 +3121,9 @@
       <c r="Q13" s="7"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A14"/>
+      <c r="A14" s="21" t="s">
+        <v>13</v>
+      </c>
       <c r="C14" s="2"/>
       <c r="D14" s="8"/>
       <c r="G14"/>
@@ -749,7 +3133,9 @@
       <c r="Q14" s="7"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A15"/>
+      <c r="A15" s="21" t="s">
+        <v>14</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="8"/>
       <c r="G15"/>
@@ -759,7 +3145,9 @@
       <c r="Q15" s="7"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A16"/>
+      <c r="A16" s="21" t="s">
+        <v>15</v>
+      </c>
       <c r="C16" s="2"/>
       <c r="D16" s="8"/>
       <c r="G16"/>
@@ -769,7 +3157,9 @@
       <c r="Q16" s="7"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A17"/>
+      <c r="A17" s="21" t="s">
+        <v>16</v>
+      </c>
       <c r="C17" s="2"/>
       <c r="D17" s="8"/>
       <c r="G17"/>
@@ -779,7 +3169,9 @@
       <c r="Q17" s="7"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A18"/>
+      <c r="A18" s="21" t="s">
+        <v>17</v>
+      </c>
       <c r="C18" s="2"/>
       <c r="D18" s="8"/>
       <c r="G18"/>
@@ -789,7 +3181,9 @@
       <c r="Q18" s="7"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19"/>
+      <c r="A19" s="21" t="s">
+        <v>18</v>
+      </c>
       <c r="C19" s="2"/>
       <c r="D19" s="8"/>
       <c r="E19" s="11"/>
@@ -801,7 +3195,9 @@
       <c r="Q19" s="7"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A20"/>
+      <c r="A20" s="21" t="s">
+        <v>19</v>
+      </c>
       <c r="C20" s="2"/>
       <c r="D20" s="8"/>
       <c r="G20"/>
@@ -811,7 +3207,9 @@
       <c r="Q20" s="7"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A21"/>
+      <c r="A21" s="21" t="s">
+        <v>20</v>
+      </c>
       <c r="C21" s="2"/>
       <c r="D21" s="8"/>
       <c r="G21"/>
@@ -822,7 +3220,9 @@
       <c r="Q21" s="7"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A22"/>
+      <c r="A22" s="21" t="s">
+        <v>21</v>
+      </c>
       <c r="C22" s="2"/>
       <c r="D22" s="8"/>
       <c r="G22"/>
@@ -832,7 +3232,9 @@
       <c r="Q22" s="7"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A23"/>
+      <c r="A23" s="21" t="s">
+        <v>22</v>
+      </c>
       <c r="C23" s="2"/>
       <c r="D23" s="8"/>
       <c r="F23" s="9"/>
@@ -843,7 +3245,9 @@
       <c r="Q23" s="7"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A24"/>
+      <c r="A24" s="21" t="s">
+        <v>23</v>
+      </c>
       <c r="C24" s="2"/>
       <c r="D24" s="8"/>
       <c r="E24" s="11"/>
@@ -854,7 +3258,9 @@
       <c r="Q24" s="7"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A25"/>
+      <c r="A25" s="21" t="s">
+        <v>24</v>
+      </c>
       <c r="C25" s="2"/>
       <c r="D25" s="8"/>
       <c r="G25"/>
@@ -864,7 +3270,9 @@
       <c r="Q25" s="7"/>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A26"/>
+      <c r="A26" s="21" t="s">
+        <v>25</v>
+      </c>
       <c r="C26" s="2"/>
       <c r="D26" s="8"/>
       <c r="G26"/>
@@ -874,7 +3282,9 @@
       <c r="Q26" s="7"/>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A27"/>
+      <c r="A27" s="21" t="s">
+        <v>26</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="8"/>
       <c r="G27"/>
@@ -884,7 +3294,9 @@
       <c r="Q27" s="7"/>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A28"/>
+      <c r="A28" s="21" t="s">
+        <v>27</v>
+      </c>
       <c r="C28" s="2"/>
       <c r="D28" s="8"/>
       <c r="G28"/>
@@ -894,7 +3306,9 @@
       <c r="Q28" s="7"/>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A29"/>
+      <c r="A29" s="21" t="s">
+        <v>28</v>
+      </c>
       <c r="C29" s="2"/>
       <c r="D29" s="8"/>
       <c r="E29" s="11"/>
@@ -905,7 +3319,9 @@
       <c r="Q29" s="7"/>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A30"/>
+      <c r="A30" s="21" t="s">
+        <v>29</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="8"/>
       <c r="G30"/>
@@ -915,7 +3331,9 @@
       <c r="Q30" s="7"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A31"/>
+      <c r="A31" s="21" t="s">
+        <v>30</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="8"/>
       <c r="G31"/>
@@ -925,7 +3343,9 @@
       <c r="Q31" s="7"/>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32"/>
+      <c r="A32" s="21" t="s">
+        <v>31</v>
+      </c>
       <c r="C32" s="2"/>
       <c r="D32" s="8"/>
       <c r="G32"/>
@@ -936,7 +3356,9 @@
       <c r="Q32" s="7"/>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A33"/>
+      <c r="A33" s="21" t="s">
+        <v>32</v>
+      </c>
       <c r="C33" s="2"/>
       <c r="D33" s="8"/>
       <c r="E33" s="11"/>
@@ -948,7 +3370,9 @@
       <c r="Q33" s="7"/>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A34"/>
+      <c r="A34" s="21" t="s">
+        <v>33</v>
+      </c>
       <c r="C34" s="2"/>
       <c r="D34" s="8"/>
       <c r="G34"/>
@@ -958,7 +3382,9 @@
       <c r="Q34" s="7"/>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A35"/>
+      <c r="A35" s="21" t="s">
+        <v>34</v>
+      </c>
       <c r="C35" s="2"/>
       <c r="D35" s="8"/>
       <c r="G35"/>
@@ -968,7 +3394,9 @@
       <c r="Q35" s="7"/>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A36"/>
+      <c r="A36" s="21" t="s">
+        <v>35</v>
+      </c>
       <c r="C36" s="2"/>
       <c r="D36" s="8"/>
       <c r="G36"/>
@@ -979,7 +3407,9 @@
       <c r="Q36" s="7"/>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A37"/>
+      <c r="A37" s="21" t="s">
+        <v>36</v>
+      </c>
       <c r="C37" s="2"/>
       <c r="D37" s="8"/>
       <c r="E37" s="11"/>
@@ -990,7 +3420,9 @@
       <c r="Q37" s="7"/>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A38"/>
+      <c r="A38" s="21" t="s">
+        <v>37</v>
+      </c>
       <c r="C38" s="2"/>
       <c r="D38" s="8"/>
       <c r="G38"/>
@@ -1000,7 +3432,9 @@
       <c r="Q38" s="7"/>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A39"/>
+      <c r="A39" s="21" t="s">
+        <v>38</v>
+      </c>
       <c r="C39" s="2"/>
       <c r="D39" s="8"/>
       <c r="G39"/>
@@ -1010,7 +3444,9 @@
       <c r="Q39" s="7"/>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A40"/>
+      <c r="A40" s="21" t="s">
+        <v>39</v>
+      </c>
       <c r="C40" s="2"/>
       <c r="D40" s="8"/>
       <c r="G40"/>
@@ -1020,7 +3456,9 @@
       <c r="Q40" s="7"/>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A41"/>
+      <c r="A41" s="21" t="s">
+        <v>40</v>
+      </c>
       <c r="C41" s="2"/>
       <c r="D41" s="8"/>
       <c r="G41"/>
@@ -1030,7 +3468,9 @@
       <c r="Q41" s="7"/>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A42"/>
+      <c r="A42" s="21" t="s">
+        <v>41</v>
+      </c>
       <c r="C42" s="2"/>
       <c r="D42" s="8"/>
       <c r="G42"/>
@@ -1040,7 +3480,9 @@
       <c r="Q42" s="7"/>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A43"/>
+      <c r="A43" s="21" t="s">
+        <v>42</v>
+      </c>
       <c r="C43" s="2"/>
       <c r="D43" s="8"/>
       <c r="G43"/>
@@ -1050,7 +3492,9 @@
       <c r="Q43" s="7"/>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A44"/>
+      <c r="A44" s="21" t="s">
+        <v>43</v>
+      </c>
       <c r="C44" s="2"/>
       <c r="D44" s="8"/>
       <c r="G44"/>
@@ -1060,7 +3504,9 @@
       <c r="Q44" s="7"/>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A45"/>
+      <c r="A45" s="21" t="s">
+        <v>44</v>
+      </c>
       <c r="C45" s="2"/>
       <c r="D45" s="8"/>
       <c r="G45"/>
@@ -1070,7 +3516,9 @@
       <c r="Q45" s="7"/>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A46"/>
+      <c r="A46" s="21" t="s">
+        <v>45</v>
+      </c>
       <c r="C46" s="2"/>
       <c r="D46" s="8"/>
       <c r="G46"/>
@@ -1080,7 +3528,9 @@
       <c r="Q46" s="7"/>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A47"/>
+      <c r="A47" s="21" t="s">
+        <v>46</v>
+      </c>
       <c r="C47" s="2"/>
       <c r="D47" s="8"/>
       <c r="G47"/>
@@ -1090,7 +3540,9 @@
       <c r="Q47" s="7"/>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A48"/>
+      <c r="A48" s="21" t="s">
+        <v>47</v>
+      </c>
       <c r="C48" s="2"/>
       <c r="D48" s="8"/>
       <c r="G48"/>
@@ -1100,7 +3552,9 @@
       <c r="Q48" s="7"/>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A49"/>
+      <c r="A49" s="21" t="s">
+        <v>48</v>
+      </c>
       <c r="C49" s="2"/>
       <c r="D49" s="8"/>
       <c r="G49"/>
@@ -1110,7 +3564,9 @@
       <c r="Q49" s="7"/>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A50"/>
+      <c r="A50" s="21" t="s">
+        <v>49</v>
+      </c>
       <c r="C50" s="2"/>
       <c r="D50" s="8"/>
       <c r="G50"/>
@@ -1120,7 +3576,9 @@
       <c r="Q50" s="7"/>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A51"/>
+      <c r="A51" s="21" t="s">
+        <v>50</v>
+      </c>
       <c r="C51" s="2"/>
       <c r="D51" s="8"/>
       <c r="G51"/>
@@ -1130,7 +3588,9 @@
       <c r="Q51" s="7"/>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A52"/>
+      <c r="A52" s="21" t="s">
+        <v>51</v>
+      </c>
       <c r="C52" s="2"/>
       <c r="D52" s="8"/>
       <c r="G52"/>
@@ -1140,7 +3600,9 @@
       <c r="Q52" s="7"/>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A53"/>
+      <c r="A53" s="21" t="s">
+        <v>52</v>
+      </c>
       <c r="C53" s="2"/>
       <c r="D53" s="8"/>
       <c r="G53"/>
@@ -1150,7 +3612,9 @@
       <c r="Q53" s="7"/>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A54"/>
+      <c r="A54" s="21" t="s">
+        <v>53</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="8"/>
       <c r="G54"/>
@@ -1160,7 +3624,9 @@
       <c r="Q54" s="7"/>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A55"/>
+      <c r="A55" s="21" t="s">
+        <v>54</v>
+      </c>
       <c r="C55" s="2"/>
       <c r="D55" s="8"/>
       <c r="G55"/>
@@ -1170,7 +3636,9 @@
       <c r="Q55" s="7"/>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A56"/>
+      <c r="A56" s="21" t="s">
+        <v>55</v>
+      </c>
       <c r="C56" s="2"/>
       <c r="D56" s="8"/>
       <c r="G56"/>
@@ -1180,7 +3648,9 @@
       <c r="Q56" s="7"/>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A57"/>
+      <c r="A57" s="21" t="s">
+        <v>56</v>
+      </c>
       <c r="C57" s="2"/>
       <c r="D57" s="8"/>
       <c r="G57"/>
@@ -1190,7 +3660,9 @@
       <c r="Q57" s="7"/>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A58"/>
+      <c r="A58" s="21" t="s">
+        <v>57</v>
+      </c>
       <c r="C58" s="2"/>
       <c r="D58" s="8"/>
       <c r="G58"/>
@@ -1200,7 +3672,9 @@
       <c r="Q58" s="7"/>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A59"/>
+      <c r="A59" s="21" t="s">
+        <v>58</v>
+      </c>
       <c r="C59" s="2"/>
       <c r="D59" s="8"/>
       <c r="G59"/>
@@ -1210,7 +3684,9 @@
       <c r="Q59" s="7"/>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A60"/>
+      <c r="A60" s="21" t="s">
+        <v>59</v>
+      </c>
       <c r="C60" s="2"/>
       <c r="D60" s="8"/>
       <c r="G60"/>
@@ -1220,7 +3696,9 @@
       <c r="Q60" s="7"/>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A61"/>
+      <c r="A61" s="21" t="s">
+        <v>60</v>
+      </c>
       <c r="C61" s="2"/>
       <c r="D61" s="8"/>
       <c r="G61"/>
@@ -1230,7 +3708,9 @@
       <c r="Q61" s="7"/>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A62"/>
+      <c r="A62" s="21" t="s">
+        <v>61</v>
+      </c>
       <c r="C62" s="2"/>
       <c r="D62" s="8"/>
       <c r="G62"/>
@@ -1240,7 +3720,9 @@
       <c r="Q62" s="7"/>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A63"/>
+      <c r="A63" s="21" t="s">
+        <v>62</v>
+      </c>
       <c r="C63" s="2"/>
       <c r="D63" s="8"/>
       <c r="G63"/>
@@ -1250,7 +3732,9 @@
       <c r="Q63" s="7"/>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A64"/>
+      <c r="A64" s="21" t="s">
+        <v>63</v>
+      </c>
       <c r="C64" s="2"/>
       <c r="D64" s="8"/>
       <c r="F64" s="12"/>
@@ -1261,7 +3745,9 @@
       <c r="Q64" s="7"/>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A65"/>
+      <c r="A65" s="21" t="s">
+        <v>64</v>
+      </c>
       <c r="C65" s="2"/>
       <c r="D65" s="8"/>
       <c r="G65"/>
@@ -1271,7 +3757,9 @@
       <c r="Q65" s="7"/>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A66"/>
+      <c r="A66" s="21" t="s">
+        <v>65</v>
+      </c>
       <c r="C66" s="2"/>
       <c r="D66" s="8"/>
       <c r="G66"/>
@@ -1281,7 +3769,9 @@
       <c r="Q66" s="7"/>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A67"/>
+      <c r="A67" s="21" t="s">
+        <v>66</v>
+      </c>
       <c r="C67" s="2"/>
       <c r="D67" s="8"/>
       <c r="G67"/>
@@ -1291,7 +3781,9 @@
       <c r="Q67" s="7"/>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A68"/>
+      <c r="A68" s="21" t="s">
+        <v>67</v>
+      </c>
       <c r="C68" s="2"/>
       <c r="D68" s="8"/>
       <c r="G68"/>
@@ -1301,7 +3793,9 @@
       <c r="Q68" s="7"/>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A69"/>
+      <c r="A69" s="21" t="s">
+        <v>68</v>
+      </c>
       <c r="C69" s="2"/>
       <c r="D69" s="8"/>
       <c r="G69"/>
@@ -1311,7 +3805,9 @@
       <c r="Q69" s="7"/>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A70"/>
+      <c r="A70" s="21" t="s">
+        <v>69</v>
+      </c>
       <c r="C70" s="2"/>
       <c r="D70" s="8"/>
       <c r="F70" s="12"/>
@@ -1322,7 +3818,9 @@
       <c r="Q70" s="7"/>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A71"/>
+      <c r="A71" s="21" t="s">
+        <v>70</v>
+      </c>
       <c r="C71" s="2"/>
       <c r="D71" s="8"/>
       <c r="G71"/>
@@ -1332,7 +3830,9 @@
       <c r="Q71" s="7"/>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A72"/>
+      <c r="A72" s="21" t="s">
+        <v>71</v>
+      </c>
       <c r="C72" s="13"/>
       <c r="D72" s="8"/>
       <c r="E72" s="3"/>
@@ -1349,7 +3849,9 @@
       <c r="Q72" s="7"/>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A73"/>
+      <c r="A73" s="21" t="s">
+        <v>72</v>
+      </c>
       <c r="C73" s="2"/>
       <c r="D73" s="8"/>
       <c r="E73" s="3"/>
@@ -1365,7 +3867,9 @@
       <c r="Q73" s="7"/>
     </row>
     <row r="74" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A74"/>
+      <c r="A74" s="21" t="s">
+        <v>73</v>
+      </c>
       <c r="C74" s="13"/>
       <c r="D74" s="8"/>
       <c r="E74" s="3"/>
@@ -1377,7 +3881,9 @@
       <c r="Q74" s="7"/>
     </row>
     <row r="75" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A75"/>
+      <c r="A75" s="21" t="s">
+        <v>74</v>
+      </c>
       <c r="C75" s="2"/>
       <c r="D75" s="8"/>
       <c r="E75" s="3"/>
@@ -1390,7 +3896,9 @@
       <c r="Q75" s="7"/>
     </row>
     <row r="76" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A76"/>
+      <c r="A76" s="21" t="s">
+        <v>75</v>
+      </c>
       <c r="C76" s="2"/>
       <c r="D76" s="8"/>
       <c r="E76" s="3"/>
@@ -1402,7 +3910,9 @@
       <c r="Q76" s="7"/>
     </row>
     <row r="77" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A77"/>
+      <c r="A77" s="21" t="s">
+        <v>76</v>
+      </c>
       <c r="C77" s="2"/>
       <c r="D77" s="8"/>
       <c r="E77" s="3"/>
@@ -1414,7 +3924,9 @@
       <c r="Q77" s="7"/>
     </row>
     <row r="78" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A78"/>
+      <c r="A78" s="21" t="s">
+        <v>77</v>
+      </c>
       <c r="C78" s="2"/>
       <c r="D78" s="8"/>
       <c r="E78" s="3"/>
@@ -1429,7 +3941,9 @@
       <c r="Q78" s="7"/>
     </row>
     <row r="79" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A79"/>
+      <c r="A79" s="21" t="s">
+        <v>78</v>
+      </c>
       <c r="C79" s="2"/>
       <c r="D79" s="8"/>
       <c r="E79" s="3"/>
@@ -1441,7 +3955,9 @@
       <c r="Q79" s="7"/>
     </row>
     <row r="80" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A80"/>
+      <c r="A80" s="21" t="s">
+        <v>79</v>
+      </c>
       <c r="C80" s="2"/>
       <c r="D80" s="8"/>
       <c r="E80" s="3"/>
@@ -1454,7 +3970,9 @@
       <c r="Q80" s="7"/>
     </row>
     <row r="81" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A81"/>
+      <c r="A81" s="21" t="s">
+        <v>80</v>
+      </c>
       <c r="C81" s="2"/>
       <c r="D81" s="8"/>
       <c r="E81" s="3"/>
@@ -1466,7 +3984,9 @@
       <c r="Q81" s="7"/>
     </row>
     <row r="82" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A82"/>
+      <c r="A82" s="21" t="s">
+        <v>81</v>
+      </c>
       <c r="C82" s="2"/>
       <c r="D82" s="8"/>
       <c r="E82" s="3"/>
@@ -1478,2903 +3998,4353 @@
       <c r="Q82" s="7"/>
     </row>
     <row r="83" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A83"/>
+      <c r="A83" s="21" t="s">
+        <v>82</v>
+      </c>
       <c r="D83" s="8"/>
     </row>
     <row r="84" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A84"/>
+      <c r="A84" s="21" t="s">
+        <v>83</v>
+      </c>
       <c r="D84" s="8"/>
     </row>
     <row r="85" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A85"/>
+      <c r="A85" s="21" t="s">
+        <v>84</v>
+      </c>
       <c r="D85" s="8"/>
     </row>
     <row r="86" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A86"/>
+      <c r="A86" s="21" t="s">
+        <v>85</v>
+      </c>
       <c r="D86" s="8"/>
     </row>
     <row r="87" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A87"/>
+      <c r="A87" s="21" t="s">
+        <v>86</v>
+      </c>
       <c r="D87" s="8"/>
     </row>
     <row r="88" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A88"/>
+      <c r="A88" s="21" t="s">
+        <v>87</v>
+      </c>
       <c r="D88" s="8"/>
     </row>
     <row r="89" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A89"/>
+      <c r="A89" s="21" t="s">
+        <v>88</v>
+      </c>
       <c r="D89" s="8"/>
     </row>
     <row r="90" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A90"/>
+      <c r="A90" s="21" t="s">
+        <v>89</v>
+      </c>
       <c r="D90" s="8"/>
     </row>
     <row r="91" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A91"/>
+      <c r="A91" s="21" t="s">
+        <v>90</v>
+      </c>
       <c r="D91" s="8"/>
     </row>
     <row r="92" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A92"/>
+      <c r="A92" s="21" t="s">
+        <v>91</v>
+      </c>
       <c r="D92" s="8"/>
     </row>
     <row r="93" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A93"/>
+      <c r="A93" s="21" t="s">
+        <v>92</v>
+      </c>
       <c r="D93" s="8"/>
     </row>
     <row r="94" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A94"/>
+      <c r="A94" s="21" t="s">
+        <v>93</v>
+      </c>
       <c r="D94" s="8"/>
     </row>
     <row r="95" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A95"/>
+      <c r="A95" s="21" t="s">
+        <v>94</v>
+      </c>
       <c r="D95" s="8"/>
     </row>
     <row r="96" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A96"/>
+      <c r="A96" s="21" t="s">
+        <v>95</v>
+      </c>
       <c r="D96" s="8"/>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97"/>
+      <c r="A97" s="21" t="s">
+        <v>96</v>
+      </c>
       <c r="D97" s="8"/>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98"/>
+      <c r="A98" s="21" t="s">
+        <v>97</v>
+      </c>
       <c r="D98" s="8"/>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99"/>
+      <c r="A99" s="21" t="s">
+        <v>98</v>
+      </c>
       <c r="D99" s="8"/>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100"/>
+      <c r="A100" s="21" t="s">
+        <v>99</v>
+      </c>
       <c r="D100" s="8"/>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101"/>
+      <c r="A101" s="21" t="s">
+        <v>100</v>
+      </c>
       <c r="D101" s="8"/>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102"/>
+      <c r="A102" s="21" t="s">
+        <v>101</v>
+      </c>
       <c r="D102" s="8"/>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103"/>
+      <c r="A103" s="21" t="s">
+        <v>102</v>
+      </c>
       <c r="D103" s="8"/>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104"/>
+      <c r="A104" s="21" t="s">
+        <v>103</v>
+      </c>
       <c r="D104" s="8"/>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105"/>
+      <c r="A105" s="21" t="s">
+        <v>104</v>
+      </c>
       <c r="D105" s="8"/>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106"/>
+      <c r="A106" s="21" t="s">
+        <v>105</v>
+      </c>
       <c r="D106" s="8"/>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107"/>
+      <c r="A107" s="21" t="s">
+        <v>106</v>
+      </c>
       <c r="D107" s="8"/>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108"/>
+      <c r="A108" s="21" t="s">
+        <v>107</v>
+      </c>
       <c r="D108" s="8"/>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109"/>
+      <c r="A109" s="21" t="s">
+        <v>108</v>
+      </c>
       <c r="D109" s="8"/>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110"/>
+      <c r="A110" s="21" t="s">
+        <v>109</v>
+      </c>
       <c r="D110" s="8"/>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111"/>
+      <c r="A111" s="21" t="s">
+        <v>110</v>
+      </c>
       <c r="D111" s="8"/>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112"/>
+      <c r="A112" s="21" t="s">
+        <v>111</v>
+      </c>
       <c r="D112" s="8"/>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113"/>
+      <c r="A113" s="21" t="s">
+        <v>112</v>
+      </c>
       <c r="D113" s="8"/>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114"/>
+      <c r="A114" s="21" t="s">
+        <v>113</v>
+      </c>
       <c r="D114" s="8"/>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115"/>
+      <c r="A115" s="21" t="s">
+        <v>114</v>
+      </c>
       <c r="D115" s="8"/>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116"/>
+      <c r="A116" s="21" t="s">
+        <v>115</v>
+      </c>
       <c r="D116" s="8"/>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117"/>
+      <c r="A117" s="21" t="s">
+        <v>116</v>
+      </c>
       <c r="D117" s="8"/>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118"/>
+      <c r="A118" s="21" t="s">
+        <v>117</v>
+      </c>
       <c r="D118" s="8"/>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119"/>
+      <c r="A119" s="21" t="s">
+        <v>118</v>
+      </c>
       <c r="D119" s="8"/>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120"/>
+      <c r="A120" s="21" t="s">
+        <v>119</v>
+      </c>
       <c r="D120" s="8"/>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121"/>
+      <c r="A121" s="21" t="s">
+        <v>120</v>
+      </c>
       <c r="D121" s="8"/>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122"/>
+      <c r="A122" s="21" t="s">
+        <v>121</v>
+      </c>
       <c r="D122" s="8"/>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123"/>
+      <c r="A123" s="21" t="s">
+        <v>122</v>
+      </c>
       <c r="D123" s="8"/>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124"/>
+      <c r="A124" s="21" t="s">
+        <v>123</v>
+      </c>
       <c r="D124" s="8"/>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125"/>
+      <c r="A125" s="21" t="s">
+        <v>124</v>
+      </c>
       <c r="D125" s="8"/>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126"/>
+      <c r="A126" s="21" t="s">
+        <v>125</v>
+      </c>
       <c r="D126" s="8"/>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127"/>
+      <c r="A127" s="21" t="s">
+        <v>126</v>
+      </c>
       <c r="D127" s="8"/>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128"/>
+      <c r="A128" s="21" t="s">
+        <v>127</v>
+      </c>
       <c r="D128" s="8"/>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129"/>
+      <c r="A129" s="21" t="s">
+        <v>128</v>
+      </c>
       <c r="D129" s="8"/>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130"/>
+      <c r="A130" s="21" t="s">
+        <v>129</v>
+      </c>
       <c r="D130" s="8"/>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131"/>
+      <c r="A131" s="21" t="s">
+        <v>130</v>
+      </c>
       <c r="D131" s="8"/>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132"/>
+      <c r="A132" s="21" t="s">
+        <v>131</v>
+      </c>
       <c r="D132" s="8"/>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133"/>
+      <c r="A133" s="21" t="s">
+        <v>132</v>
+      </c>
       <c r="D133" s="8"/>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134"/>
+      <c r="A134" s="21" t="s">
+        <v>133</v>
+      </c>
       <c r="D134" s="8"/>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135"/>
+      <c r="A135" s="21" t="s">
+        <v>134</v>
+      </c>
       <c r="D135" s="8"/>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136"/>
+      <c r="A136" s="21" t="s">
+        <v>135</v>
+      </c>
       <c r="D136" s="8"/>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137"/>
+      <c r="A137" s="21" t="s">
+        <v>136</v>
+      </c>
       <c r="D137" s="8"/>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138"/>
+      <c r="A138" s="21" t="s">
+        <v>137</v>
+      </c>
       <c r="D138" s="8"/>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139"/>
+      <c r="A139" s="21" t="s">
+        <v>138</v>
+      </c>
       <c r="D139" s="8"/>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140"/>
+      <c r="A140" s="21" t="s">
+        <v>139</v>
+      </c>
       <c r="D140" s="8"/>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141"/>
+      <c r="A141" s="21" t="s">
+        <v>140</v>
+      </c>
       <c r="D141" s="8"/>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142"/>
+      <c r="A142" s="21" t="s">
+        <v>141</v>
+      </c>
       <c r="D142" s="8"/>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143"/>
+      <c r="A143" s="21" t="s">
+        <v>142</v>
+      </c>
       <c r="D143" s="8"/>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144"/>
+      <c r="A144" s="21" t="s">
+        <v>143</v>
+      </c>
       <c r="D144" s="8"/>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145"/>
+      <c r="A145" s="21" t="s">
+        <v>144</v>
+      </c>
       <c r="D145" s="8"/>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146"/>
+      <c r="A146" s="21" t="s">
+        <v>145</v>
+      </c>
       <c r="D146" s="8"/>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147"/>
+      <c r="A147" s="21" t="s">
+        <v>146</v>
+      </c>
       <c r="D147" s="8"/>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148"/>
+      <c r="A148" s="21" t="s">
+        <v>147</v>
+      </c>
       <c r="D148" s="8"/>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149"/>
+      <c r="A149" s="21" t="s">
+        <v>148</v>
+      </c>
       <c r="D149" s="8"/>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150"/>
+      <c r="A150" s="21" t="s">
+        <v>149</v>
+      </c>
       <c r="D150" s="8"/>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A151"/>
+      <c r="A151" s="21" t="s">
+        <v>150</v>
+      </c>
       <c r="D151" s="8"/>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A152"/>
+      <c r="A152" s="21" t="s">
+        <v>151</v>
+      </c>
       <c r="D152" s="8"/>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153"/>
+      <c r="A153" s="21" t="s">
+        <v>152</v>
+      </c>
       <c r="D153" s="8"/>
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154"/>
+      <c r="A154" s="21" t="s">
+        <v>153</v>
+      </c>
       <c r="D154" s="8"/>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155"/>
+      <c r="A155" s="21" t="s">
+        <v>154</v>
+      </c>
       <c r="D155" s="8"/>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156"/>
+      <c r="A156" s="21" t="s">
+        <v>155</v>
+      </c>
       <c r="D156" s="8"/>
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157"/>
+      <c r="A157" s="21" t="s">
+        <v>156</v>
+      </c>
       <c r="D157" s="8"/>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158"/>
+      <c r="A158" s="21" t="s">
+        <v>157</v>
+      </c>
       <c r="D158" s="8"/>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159"/>
+      <c r="A159" s="21" t="s">
+        <v>158</v>
+      </c>
       <c r="D159" s="8"/>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160"/>
+      <c r="A160" s="21" t="s">
+        <v>159</v>
+      </c>
       <c r="D160" s="8"/>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161"/>
+      <c r="A161" s="21" t="s">
+        <v>160</v>
+      </c>
       <c r="D161" s="8"/>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162"/>
+      <c r="A162" s="21" t="s">
+        <v>161</v>
+      </c>
       <c r="D162" s="8"/>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163"/>
+      <c r="A163" s="21" t="s">
+        <v>162</v>
+      </c>
       <c r="D163" s="8"/>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A164"/>
+      <c r="A164" s="21" t="s">
+        <v>163</v>
+      </c>
       <c r="D164" s="8"/>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A165"/>
+      <c r="A165" s="21" t="s">
+        <v>164</v>
+      </c>
       <c r="D165" s="8"/>
     </row>
     <row r="166" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A166"/>
+      <c r="A166" s="21" t="s">
+        <v>165</v>
+      </c>
       <c r="D166" s="8"/>
     </row>
     <row r="167" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A167"/>
+      <c r="A167" s="21" t="s">
+        <v>166</v>
+      </c>
       <c r="D167" s="8"/>
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A168"/>
+      <c r="A168" s="21" t="s">
+        <v>167</v>
+      </c>
       <c r="D168" s="8"/>
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A169"/>
+      <c r="A169" s="21" t="s">
+        <v>168</v>
+      </c>
       <c r="D169" s="8"/>
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A170"/>
+      <c r="A170" s="21" t="s">
+        <v>169</v>
+      </c>
       <c r="D170" s="8"/>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A171"/>
+      <c r="A171" s="21" t="s">
+        <v>170</v>
+      </c>
       <c r="D171" s="8"/>
     </row>
     <row r="172" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A172"/>
+      <c r="A172" s="21" t="s">
+        <v>171</v>
+      </c>
       <c r="D172" s="8"/>
     </row>
     <row r="173" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A173"/>
+      <c r="A173" s="21" t="s">
+        <v>172</v>
+      </c>
       <c r="D173" s="8"/>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A174"/>
+      <c r="A174" s="21" t="s">
+        <v>173</v>
+      </c>
       <c r="D174" s="8"/>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A175"/>
+      <c r="A175" s="21" t="s">
+        <v>174</v>
+      </c>
       <c r="D175" s="8"/>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A176"/>
+      <c r="A176" s="21" t="s">
+        <v>175</v>
+      </c>
       <c r="D176" s="8"/>
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A177"/>
+      <c r="A177" s="21" t="s">
+        <v>176</v>
+      </c>
       <c r="D177" s="8"/>
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A178"/>
+      <c r="A178" s="21" t="s">
+        <v>177</v>
+      </c>
       <c r="D178" s="8"/>
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A179"/>
+      <c r="A179" s="21" t="s">
+        <v>178</v>
+      </c>
       <c r="D179" s="8"/>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A180"/>
+      <c r="A180" s="21" t="s">
+        <v>179</v>
+      </c>
       <c r="D180" s="8"/>
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A181"/>
+      <c r="A181" s="21" t="s">
+        <v>180</v>
+      </c>
       <c r="D181" s="8"/>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182"/>
+      <c r="A182" s="21" t="s">
+        <v>181</v>
+      </c>
       <c r="D182" s="8"/>
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A183"/>
+      <c r="A183" s="21" t="s">
+        <v>182</v>
+      </c>
       <c r="D183" s="8"/>
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A184"/>
+      <c r="A184" s="21" t="s">
+        <v>183</v>
+      </c>
       <c r="D184" s="8"/>
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A185"/>
+      <c r="A185" s="21" t="s">
+        <v>184</v>
+      </c>
       <c r="D185" s="8"/>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A186"/>
+      <c r="A186" s="21" t="s">
+        <v>185</v>
+      </c>
       <c r="D186" s="8"/>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A187"/>
+      <c r="A187" s="21" t="s">
+        <v>186</v>
+      </c>
       <c r="D187" s="8"/>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A188"/>
+      <c r="A188" s="21" t="s">
+        <v>187</v>
+      </c>
       <c r="D188" s="8"/>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A189"/>
+      <c r="A189" s="21" t="s">
+        <v>188</v>
+      </c>
       <c r="D189" s="8"/>
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190"/>
+      <c r="A190" s="21" t="s">
+        <v>189</v>
+      </c>
       <c r="D190" s="8"/>
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A191"/>
+      <c r="A191" s="21" t="s">
+        <v>190</v>
+      </c>
       <c r="D191" s="8"/>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A192"/>
+      <c r="A192" s="21" t="s">
+        <v>191</v>
+      </c>
       <c r="D192" s="8"/>
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A193"/>
+      <c r="A193" s="21" t="s">
+        <v>192</v>
+      </c>
       <c r="D193" s="8"/>
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194"/>
+      <c r="A194" s="21" t="s">
+        <v>193</v>
+      </c>
       <c r="D194" s="8"/>
     </row>
     <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195"/>
+      <c r="A195" s="21" t="s">
+        <v>194</v>
+      </c>
       <c r="D195" s="8"/>
     </row>
     <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196"/>
+      <c r="A196" s="21" t="s">
+        <v>195</v>
+      </c>
       <c r="D196" s="8"/>
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197"/>
+      <c r="A197" s="21" t="s">
+        <v>196</v>
+      </c>
       <c r="D197" s="8"/>
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198"/>
+      <c r="A198" s="21" t="s">
+        <v>197</v>
+      </c>
       <c r="D198" s="8"/>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199"/>
+      <c r="A199" s="21" t="s">
+        <v>198</v>
+      </c>
       <c r="D199" s="8"/>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200"/>
+      <c r="A200" s="21" t="s">
+        <v>199</v>
+      </c>
       <c r="D200" s="8"/>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201"/>
+      <c r="A201" s="21" t="s">
+        <v>200</v>
+      </c>
       <c r="D201" s="8"/>
     </row>
     <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202"/>
+      <c r="A202" s="21" t="s">
+        <v>201</v>
+      </c>
       <c r="D202" s="8"/>
     </row>
     <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203"/>
+      <c r="A203" s="21" t="s">
+        <v>202</v>
+      </c>
       <c r="D203" s="8"/>
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204"/>
+      <c r="A204" s="21" t="s">
+        <v>203</v>
+      </c>
       <c r="D204" s="8"/>
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205"/>
+      <c r="A205" s="21" t="s">
+        <v>204</v>
+      </c>
       <c r="D205" s="8"/>
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206"/>
+      <c r="A206" s="21" t="s">
+        <v>205</v>
+      </c>
       <c r="D206" s="8"/>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207"/>
+      <c r="A207" s="21" t="s">
+        <v>206</v>
+      </c>
       <c r="D207" s="8"/>
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208"/>
+      <c r="A208" s="21" t="s">
+        <v>207</v>
+      </c>
       <c r="D208" s="8"/>
     </row>
     <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209"/>
+      <c r="A209" s="21" t="s">
+        <v>208</v>
+      </c>
       <c r="D209" s="8"/>
     </row>
     <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210"/>
+      <c r="A210" s="21" t="s">
+        <v>209</v>
+      </c>
       <c r="D210" s="8"/>
     </row>
     <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211"/>
+      <c r="A211" s="21" t="s">
+        <v>210</v>
+      </c>
       <c r="D211" s="8"/>
     </row>
     <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212"/>
+      <c r="A212" s="21" t="s">
+        <v>211</v>
+      </c>
       <c r="D212" s="8"/>
     </row>
     <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213"/>
+      <c r="A213" s="21" t="s">
+        <v>212</v>
+      </c>
       <c r="D213" s="8"/>
     </row>
     <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214"/>
+      <c r="A214" s="21" t="s">
+        <v>213</v>
+      </c>
       <c r="D214" s="8"/>
     </row>
     <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215"/>
+      <c r="A215" s="21" t="s">
+        <v>214</v>
+      </c>
       <c r="D215" s="8"/>
     </row>
     <row r="216" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A216"/>
+      <c r="A216" s="21" t="s">
+        <v>215</v>
+      </c>
       <c r="D216" s="8"/>
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A217"/>
+      <c r="A217" s="21" t="s">
+        <v>216</v>
+      </c>
       <c r="D217" s="8"/>
     </row>
     <row r="218" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A218"/>
+      <c r="A218" s="21" t="s">
+        <v>217</v>
+      </c>
       <c r="D218" s="8"/>
     </row>
     <row r="219" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A219"/>
+      <c r="A219" s="21" t="s">
+        <v>218</v>
+      </c>
       <c r="D219" s="8"/>
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A220"/>
+      <c r="A220" s="21" t="s">
+        <v>219</v>
+      </c>
       <c r="D220" s="8"/>
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A221"/>
+      <c r="A221" s="21" t="s">
+        <v>220</v>
+      </c>
       <c r="D221" s="8"/>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A222"/>
+      <c r="A222" s="21" t="s">
+        <v>221</v>
+      </c>
       <c r="D222" s="8"/>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A223"/>
+      <c r="A223" s="21" t="s">
+        <v>222</v>
+      </c>
       <c r="D223" s="8"/>
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A224"/>
+      <c r="A224" s="21" t="s">
+        <v>223</v>
+      </c>
       <c r="D224" s="8"/>
     </row>
     <row r="225" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A225"/>
+      <c r="A225" s="21" t="s">
+        <v>224</v>
+      </c>
       <c r="D225" s="8"/>
     </row>
     <row r="226" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A226"/>
+      <c r="A226" s="21" t="s">
+        <v>225</v>
+      </c>
       <c r="D226" s="8"/>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A227"/>
+      <c r="A227" s="21" t="s">
+        <v>226</v>
+      </c>
       <c r="D227" s="8"/>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228"/>
+      <c r="A228" s="21" t="s">
+        <v>227</v>
+      </c>
       <c r="D228" s="8"/>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229"/>
+      <c r="A229" s="21" t="s">
+        <v>228</v>
+      </c>
       <c r="D229" s="8"/>
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A230"/>
+      <c r="A230" s="21" t="s">
+        <v>229</v>
+      </c>
       <c r="D230" s="8"/>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A231"/>
+      <c r="A231" s="21" t="s">
+        <v>230</v>
+      </c>
       <c r="D231" s="8"/>
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A232"/>
+      <c r="A232" s="21" t="s">
+        <v>231</v>
+      </c>
       <c r="D232" s="8"/>
     </row>
     <row r="233" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A233"/>
+      <c r="A233" s="21" t="s">
+        <v>232</v>
+      </c>
       <c r="D233" s="8"/>
     </row>
     <row r="234" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A234"/>
+      <c r="A234" s="21" t="s">
+        <v>233</v>
+      </c>
       <c r="D234" s="8"/>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A235"/>
+      <c r="A235" s="21" t="s">
+        <v>234</v>
+      </c>
       <c r="D235" s="8"/>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A236"/>
+      <c r="A236" s="21" t="s">
+        <v>235</v>
+      </c>
       <c r="D236" s="8"/>
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A237"/>
+      <c r="A237" s="21" t="s">
+        <v>236</v>
+      </c>
       <c r="D237" s="8"/>
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A238"/>
+      <c r="A238" s="21" t="s">
+        <v>237</v>
+      </c>
       <c r="D238" s="8"/>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A239"/>
+      <c r="A239" s="21" t="s">
+        <v>238</v>
+      </c>
       <c r="D239" s="8"/>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A240"/>
+      <c r="A240" s="21" t="s">
+        <v>239</v>
+      </c>
       <c r="D240" s="8"/>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A241"/>
+      <c r="A241" s="21" t="s">
+        <v>240</v>
+      </c>
       <c r="D241" s="8"/>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A242"/>
+      <c r="A242" s="21" t="s">
+        <v>241</v>
+      </c>
       <c r="D242" s="8"/>
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A243"/>
+      <c r="A243" s="21" t="s">
+        <v>242</v>
+      </c>
       <c r="D243" s="8"/>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A244"/>
+      <c r="A244" s="21" t="s">
+        <v>243</v>
+      </c>
       <c r="D244" s="8"/>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A245"/>
+      <c r="A245" s="21" t="s">
+        <v>244</v>
+      </c>
       <c r="D245" s="8"/>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A246"/>
+      <c r="A246" s="21" t="s">
+        <v>245</v>
+      </c>
       <c r="D246" s="8"/>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A247"/>
+      <c r="A247" s="21" t="s">
+        <v>246</v>
+      </c>
       <c r="D247" s="8"/>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A248"/>
+      <c r="A248" s="21" t="s">
+        <v>247</v>
+      </c>
       <c r="D248" s="8"/>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A249"/>
+      <c r="A249" s="21" t="s">
+        <v>248</v>
+      </c>
       <c r="D249" s="8"/>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A250"/>
+      <c r="A250" s="21" t="s">
+        <v>249</v>
+      </c>
       <c r="D250" s="8"/>
     </row>
     <row r="251" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A251"/>
+      <c r="A251" s="21" t="s">
+        <v>250</v>
+      </c>
       <c r="D251" s="8"/>
     </row>
     <row r="252" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A252"/>
+      <c r="A252" s="21" t="s">
+        <v>251</v>
+      </c>
       <c r="D252" s="8"/>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A253"/>
+      <c r="A253" s="21" t="s">
+        <v>252</v>
+      </c>
       <c r="D253" s="8"/>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A254"/>
+      <c r="A254" s="21" t="s">
+        <v>253</v>
+      </c>
       <c r="D254" s="8"/>
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A255"/>
+      <c r="A255" s="21" t="s">
+        <v>254</v>
+      </c>
       <c r="D255" s="8"/>
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A256"/>
+      <c r="A256" s="21" t="s">
+        <v>255</v>
+      </c>
       <c r="D256" s="8"/>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A257"/>
+      <c r="A257" s="21" t="s">
+        <v>256</v>
+      </c>
       <c r="D257" s="8"/>
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A258"/>
+      <c r="A258" s="21" t="s">
+        <v>257</v>
+      </c>
       <c r="D258" s="8"/>
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A259"/>
+      <c r="A259" s="21" t="s">
+        <v>258</v>
+      </c>
       <c r="D259" s="8"/>
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A260"/>
+      <c r="A260" s="21" t="s">
+        <v>259</v>
+      </c>
       <c r="D260" s="8"/>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A261"/>
+      <c r="A261" s="21" t="s">
+        <v>260</v>
+      </c>
       <c r="D261" s="8"/>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A262"/>
+      <c r="A262" s="21" t="s">
+        <v>261</v>
+      </c>
       <c r="D262" s="8"/>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A263"/>
+      <c r="A263" s="21" t="s">
+        <v>262</v>
+      </c>
       <c r="D263" s="8"/>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A264"/>
+      <c r="A264" s="21" t="s">
+        <v>263</v>
+      </c>
       <c r="D264" s="8"/>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A265"/>
+      <c r="A265" s="21" t="s">
+        <v>264</v>
+      </c>
       <c r="D265" s="8"/>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A266"/>
+      <c r="A266" s="21" t="s">
+        <v>265</v>
+      </c>
       <c r="D266" s="8"/>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A267"/>
+      <c r="A267" s="21" t="s">
+        <v>266</v>
+      </c>
       <c r="D267" s="8"/>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A268"/>
+      <c r="A268" s="21" t="s">
+        <v>267</v>
+      </c>
       <c r="D268" s="8"/>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A269"/>
+      <c r="A269" s="21" t="s">
+        <v>268</v>
+      </c>
       <c r="D269" s="8"/>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A270"/>
+      <c r="A270" s="21" t="s">
+        <v>269</v>
+      </c>
       <c r="D270" s="8"/>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A271"/>
+      <c r="A271" s="21" t="s">
+        <v>270</v>
+      </c>
       <c r="D271" s="8"/>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A272"/>
+      <c r="A272" s="21" t="s">
+        <v>271</v>
+      </c>
       <c r="D272" s="8"/>
     </row>
     <row r="273" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A273"/>
+      <c r="A273" s="21" t="s">
+        <v>272</v>
+      </c>
       <c r="D273" s="8"/>
     </row>
     <row r="274" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A274"/>
+      <c r="A274" s="21" t="s">
+        <v>273</v>
+      </c>
       <c r="D274" s="8"/>
     </row>
     <row r="275" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A275"/>
+      <c r="A275" s="21" t="s">
+        <v>274</v>
+      </c>
       <c r="D275" s="8"/>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A276"/>
+      <c r="A276" s="21" t="s">
+        <v>275</v>
+      </c>
       <c r="D276" s="8"/>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A277"/>
+      <c r="A277" s="21" t="s">
+        <v>276</v>
+      </c>
       <c r="D277" s="8"/>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A278"/>
+      <c r="A278" s="21" t="s">
+        <v>277</v>
+      </c>
       <c r="D278" s="8"/>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A279"/>
+      <c r="A279" s="21" t="s">
+        <v>278</v>
+      </c>
       <c r="D279" s="8"/>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A280"/>
+      <c r="A280" s="21" t="s">
+        <v>279</v>
+      </c>
       <c r="D280" s="8"/>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A281"/>
+      <c r="A281" s="21" t="s">
+        <v>280</v>
+      </c>
       <c r="D281" s="8"/>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A282"/>
+      <c r="A282" s="21" t="s">
+        <v>281</v>
+      </c>
       <c r="D282" s="8"/>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A283"/>
+      <c r="A283" s="21" t="s">
+        <v>282</v>
+      </c>
       <c r="D283" s="8"/>
     </row>
     <row r="284" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A284"/>
+      <c r="A284" s="21" t="s">
+        <v>283</v>
+      </c>
       <c r="D284" s="8"/>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A285"/>
+      <c r="A285" s="21" t="s">
+        <v>284</v>
+      </c>
       <c r="D285" s="8"/>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A286"/>
+      <c r="A286" s="21" t="s">
+        <v>285</v>
+      </c>
       <c r="D286" s="8"/>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A287"/>
+      <c r="A287" s="21" t="s">
+        <v>286</v>
+      </c>
       <c r="D287" s="8"/>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A288"/>
+      <c r="A288" s="21" t="s">
+        <v>287</v>
+      </c>
       <c r="D288" s="8"/>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A289"/>
+      <c r="A289" s="21" t="s">
+        <v>288</v>
+      </c>
       <c r="D289" s="8"/>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A290"/>
+      <c r="A290" s="21" t="s">
+        <v>289</v>
+      </c>
       <c r="D290" s="8"/>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A291"/>
+      <c r="A291" s="21" t="s">
+        <v>290</v>
+      </c>
       <c r="D291" s="8"/>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A292"/>
+      <c r="A292" s="21" t="s">
+        <v>291</v>
+      </c>
       <c r="D292" s="8"/>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A293"/>
+      <c r="A293" s="21" t="s">
+        <v>292</v>
+      </c>
       <c r="D293" s="8"/>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A294"/>
+      <c r="A294" s="21" t="s">
+        <v>293</v>
+      </c>
       <c r="D294" s="8"/>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A295"/>
+      <c r="A295" s="21" t="s">
+        <v>294</v>
+      </c>
       <c r="D295" s="8"/>
     </row>
     <row r="296" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A296"/>
+      <c r="A296" s="21" t="s">
+        <v>295</v>
+      </c>
       <c r="D296" s="8"/>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A297"/>
+      <c r="A297" s="21" t="s">
+        <v>296</v>
+      </c>
       <c r="D297" s="8"/>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A298"/>
+      <c r="A298" s="21" t="s">
+        <v>297</v>
+      </c>
       <c r="D298" s="8"/>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A299"/>
+      <c r="A299" s="21" t="s">
+        <v>298</v>
+      </c>
       <c r="D299" s="8"/>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A300"/>
+      <c r="A300" s="21" t="s">
+        <v>299</v>
+      </c>
       <c r="D300" s="8"/>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A301"/>
+      <c r="A301" s="21" t="s">
+        <v>300</v>
+      </c>
       <c r="D301" s="8"/>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A302"/>
+      <c r="A302" s="21" t="s">
+        <v>301</v>
+      </c>
       <c r="D302" s="8"/>
     </row>
     <row r="303" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A303"/>
+      <c r="A303" s="21" t="s">
+        <v>302</v>
+      </c>
       <c r="D303" s="8"/>
     </row>
     <row r="304" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A304"/>
+      <c r="A304" s="21" t="s">
+        <v>303</v>
+      </c>
       <c r="D304" s="8"/>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A305"/>
+      <c r="A305" s="21" t="s">
+        <v>304</v>
+      </c>
       <c r="D305" s="8"/>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A306"/>
+      <c r="A306" s="21" t="s">
+        <v>305</v>
+      </c>
       <c r="D306" s="8"/>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A307"/>
+      <c r="A307" s="21" t="s">
+        <v>306</v>
+      </c>
       <c r="D307" s="8"/>
     </row>
     <row r="308" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A308"/>
+      <c r="A308" s="21" t="s">
+        <v>307</v>
+      </c>
       <c r="D308" s="8"/>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A309"/>
+      <c r="A309" s="21" t="s">
+        <v>308</v>
+      </c>
       <c r="D309" s="8"/>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A310"/>
+      <c r="A310" s="21" t="s">
+        <v>309</v>
+      </c>
       <c r="D310" s="8"/>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A311"/>
+      <c r="A311" s="21" t="s">
+        <v>310</v>
+      </c>
       <c r="D311" s="8"/>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A312"/>
+      <c r="A312" s="21" t="s">
+        <v>311</v>
+      </c>
       <c r="D312" s="8"/>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A313"/>
+      <c r="A313" s="21" t="s">
+        <v>312</v>
+      </c>
       <c r="D313" s="8"/>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A314"/>
+      <c r="A314" s="21" t="s">
+        <v>313</v>
+      </c>
       <c r="D314" s="8"/>
     </row>
     <row r="315" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A315"/>
+      <c r="A315" s="21" t="s">
+        <v>314</v>
+      </c>
       <c r="D315" s="8"/>
     </row>
     <row r="316" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A316"/>
+      <c r="A316" s="21" t="s">
+        <v>315</v>
+      </c>
       <c r="D316" s="8"/>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A317"/>
+      <c r="A317" s="21" t="s">
+        <v>316</v>
+      </c>
       <c r="D317" s="8"/>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A318"/>
+      <c r="A318" s="21" t="s">
+        <v>317</v>
+      </c>
       <c r="D318" s="8"/>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A319"/>
+      <c r="A319" s="21" t="s">
+        <v>318</v>
+      </c>
       <c r="D319" s="8"/>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A320"/>
+      <c r="A320" s="21" t="s">
+        <v>319</v>
+      </c>
       <c r="D320" s="8"/>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A321"/>
+      <c r="A321" s="21" t="s">
+        <v>320</v>
+      </c>
       <c r="D321" s="8"/>
     </row>
     <row r="322" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A322"/>
+      <c r="A322" s="21" t="s">
+        <v>321</v>
+      </c>
       <c r="D322" s="8"/>
     </row>
     <row r="323" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A323"/>
+      <c r="A323" s="21" t="s">
+        <v>322</v>
+      </c>
       <c r="D323" s="8"/>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A324"/>
+      <c r="A324" s="21" t="s">
+        <v>323</v>
+      </c>
       <c r="D324" s="8"/>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A325"/>
+      <c r="A325" s="21" t="s">
+        <v>324</v>
+      </c>
       <c r="D325" s="8"/>
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A326"/>
+      <c r="A326" s="21" t="s">
+        <v>325</v>
+      </c>
       <c r="D326" s="8"/>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A327"/>
+      <c r="A327" s="21" t="s">
+        <v>326</v>
+      </c>
       <c r="D327" s="8"/>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A328"/>
+      <c r="A328" s="21" t="s">
+        <v>327</v>
+      </c>
       <c r="D328" s="8"/>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A329"/>
+      <c r="A329" s="21" t="s">
+        <v>328</v>
+      </c>
       <c r="D329" s="8"/>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A330"/>
+      <c r="A330" s="21" t="s">
+        <v>329</v>
+      </c>
       <c r="D330" s="8"/>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A331"/>
+      <c r="A331" s="21" t="s">
+        <v>330</v>
+      </c>
       <c r="D331" s="8"/>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A332"/>
+      <c r="A332" s="21" t="s">
+        <v>331</v>
+      </c>
       <c r="D332" s="8"/>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A333"/>
+      <c r="A333" s="21" t="s">
+        <v>332</v>
+      </c>
       <c r="D333" s="8"/>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A334"/>
+      <c r="A334" s="21" t="s">
+        <v>333</v>
+      </c>
       <c r="D334" s="8"/>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A335"/>
+      <c r="A335" s="21" t="s">
+        <v>334</v>
+      </c>
       <c r="D335" s="8"/>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A336"/>
+      <c r="A336" s="21" t="s">
+        <v>335</v>
+      </c>
       <c r="D336" s="8"/>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A337"/>
+      <c r="A337" s="21" t="s">
+        <v>336</v>
+      </c>
       <c r="D337" s="8"/>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A338"/>
+      <c r="A338" s="21" t="s">
+        <v>337</v>
+      </c>
       <c r="D338" s="8"/>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A339"/>
+      <c r="A339" s="21" t="s">
+        <v>338</v>
+      </c>
       <c r="D339" s="8"/>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A340"/>
+      <c r="A340" s="21" t="s">
+        <v>339</v>
+      </c>
       <c r="D340" s="8"/>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A341"/>
+      <c r="A341" s="21" t="s">
+        <v>340</v>
+      </c>
       <c r="D341" s="8"/>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A342"/>
+      <c r="A342" s="21" t="s">
+        <v>341</v>
+      </c>
       <c r="D342" s="8"/>
     </row>
     <row r="343" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A343"/>
+      <c r="A343" s="21" t="s">
+        <v>342</v>
+      </c>
       <c r="D343" s="8"/>
     </row>
     <row r="344" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A344"/>
+      <c r="A344" s="21" t="s">
+        <v>343</v>
+      </c>
       <c r="D344" s="8"/>
     </row>
     <row r="345" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A345"/>
+      <c r="A345" s="21" t="s">
+        <v>344</v>
+      </c>
       <c r="D345" s="8"/>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A346"/>
+      <c r="A346" s="21" t="s">
+        <v>345</v>
+      </c>
       <c r="D346" s="8"/>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A347"/>
+      <c r="A347" s="21" t="s">
+        <v>346</v>
+      </c>
       <c r="D347" s="8"/>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A348"/>
+      <c r="A348" s="21" t="s">
+        <v>347</v>
+      </c>
       <c r="D348" s="8"/>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A349"/>
+      <c r="A349" s="21" t="s">
+        <v>348</v>
+      </c>
       <c r="D349" s="8"/>
     </row>
     <row r="350" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A350"/>
+      <c r="A350" s="21" t="s">
+        <v>349</v>
+      </c>
       <c r="D350" s="8"/>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A351"/>
+      <c r="A351" s="21" t="s">
+        <v>350</v>
+      </c>
       <c r="D351" s="8"/>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A352"/>
+      <c r="A352" s="21" t="s">
+        <v>351</v>
+      </c>
       <c r="D352" s="8"/>
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A353"/>
+      <c r="A353" s="21" t="s">
+        <v>352</v>
+      </c>
       <c r="D353" s="8"/>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A354"/>
+      <c r="A354" s="21" t="s">
+        <v>353</v>
+      </c>
       <c r="D354" s="8"/>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A355"/>
+      <c r="A355" s="21" t="s">
+        <v>354</v>
+      </c>
       <c r="D355" s="8"/>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A356"/>
+      <c r="A356" s="21" t="s">
+        <v>355</v>
+      </c>
       <c r="D356" s="8"/>
     </row>
     <row r="357" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A357"/>
+      <c r="A357" s="21" t="s">
+        <v>356</v>
+      </c>
       <c r="D357" s="8"/>
     </row>
     <row r="358" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A358"/>
+      <c r="A358" s="21" t="s">
+        <v>357</v>
+      </c>
       <c r="D358" s="8"/>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A359"/>
+      <c r="A359" s="21" t="s">
+        <v>358</v>
+      </c>
       <c r="D359" s="8"/>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A360"/>
+      <c r="A360" s="21" t="s">
+        <v>359</v>
+      </c>
       <c r="D360" s="8"/>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A361"/>
+      <c r="A361" s="21" t="s">
+        <v>360</v>
+      </c>
       <c r="D361" s="8"/>
     </row>
     <row r="362" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A362"/>
+      <c r="A362" s="21" t="s">
+        <v>361</v>
+      </c>
       <c r="D362" s="8"/>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A363"/>
+      <c r="A363" s="21" t="s">
+        <v>362</v>
+      </c>
       <c r="D363" s="8"/>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A364"/>
+      <c r="A364" s="21" t="s">
+        <v>363</v>
+      </c>
       <c r="D364" s="8"/>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A365"/>
+      <c r="A365" s="21" t="s">
+        <v>364</v>
+      </c>
       <c r="D365" s="8"/>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A366"/>
+      <c r="A366" s="21" t="s">
+        <v>365</v>
+      </c>
       <c r="D366" s="8"/>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A367"/>
+      <c r="A367" s="21" t="s">
+        <v>366</v>
+      </c>
       <c r="D367" s="8"/>
     </row>
     <row r="368" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A368"/>
+      <c r="A368" s="21" t="s">
+        <v>367</v>
+      </c>
       <c r="D368" s="8"/>
     </row>
     <row r="369" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A369"/>
+      <c r="A369" s="21" t="s">
+        <v>368</v>
+      </c>
       <c r="D369" s="8"/>
     </row>
     <row r="370" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A370"/>
+      <c r="A370" s="21" t="s">
+        <v>368</v>
+      </c>
       <c r="D370" s="8"/>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A371"/>
+      <c r="A371" s="21" t="s">
+        <v>369</v>
+      </c>
       <c r="D371" s="8"/>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A372"/>
+      <c r="A372" s="21" t="s">
+        <v>369</v>
+      </c>
       <c r="D372" s="8"/>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A373"/>
+      <c r="A373" s="21" t="s">
+        <v>370</v>
+      </c>
       <c r="D373" s="8"/>
     </row>
     <row r="374" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A374"/>
+      <c r="A374" s="21" t="s">
+        <v>371</v>
+      </c>
       <c r="D374" s="8"/>
     </row>
     <row r="375" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A375"/>
+      <c r="A375" s="21" t="s">
+        <v>372</v>
+      </c>
       <c r="D375" s="8"/>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A376"/>
+      <c r="A376" s="21" t="s">
+        <v>373</v>
+      </c>
       <c r="D376" s="8"/>
     </row>
     <row r="377" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A377"/>
+      <c r="A377" s="21" t="s">
+        <v>374</v>
+      </c>
       <c r="D377" s="8"/>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A378"/>
+      <c r="A378" s="21" t="s">
+        <v>375</v>
+      </c>
       <c r="D378" s="8"/>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A379"/>
+      <c r="A379" s="21" t="s">
+        <v>376</v>
+      </c>
       <c r="D379" s="8"/>
     </row>
     <row r="380" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A380"/>
+      <c r="A380" s="21" t="s">
+        <v>377</v>
+      </c>
       <c r="D380" s="8"/>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A381"/>
+      <c r="A381" s="21" t="s">
+        <v>378</v>
+      </c>
       <c r="D381" s="8"/>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A382"/>
+      <c r="A382" s="21" t="s">
+        <v>379</v>
+      </c>
       <c r="D382" s="8"/>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A383"/>
+      <c r="A383" s="21" t="s">
+        <v>380</v>
+      </c>
       <c r="D383" s="8"/>
     </row>
     <row r="384" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A384"/>
+      <c r="A384" s="21" t="s">
+        <v>381</v>
+      </c>
       <c r="D384" s="8"/>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A385"/>
+      <c r="A385" s="21" t="s">
+        <v>382</v>
+      </c>
       <c r="D385" s="8"/>
     </row>
     <row r="386" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A386"/>
+      <c r="A386" s="21" t="s">
+        <v>383</v>
+      </c>
       <c r="D386" s="8"/>
     </row>
     <row r="387" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A387"/>
+      <c r="A387" s="21" t="s">
+        <v>384</v>
+      </c>
       <c r="D387" s="8"/>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A388"/>
+      <c r="A388" s="21" t="s">
+        <v>385</v>
+      </c>
       <c r="D388" s="8"/>
     </row>
     <row r="389" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A389"/>
+      <c r="A389" s="21" t="s">
+        <v>386</v>
+      </c>
       <c r="D389" s="8"/>
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A390"/>
+      <c r="A390" s="21" t="s">
+        <v>387</v>
+      </c>
       <c r="D390" s="8"/>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A391"/>
+      <c r="A391" s="21" t="s">
+        <v>388</v>
+      </c>
       <c r="D391" s="8"/>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A392"/>
+      <c r="A392" s="21" t="s">
+        <v>389</v>
+      </c>
       <c r="D392" s="8"/>
     </row>
     <row r="393" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A393"/>
+      <c r="A393" s="21" t="s">
+        <v>390</v>
+      </c>
       <c r="D393" s="8"/>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A394"/>
+      <c r="A394" s="21" t="s">
+        <v>391</v>
+      </c>
       <c r="D394" s="8"/>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A395"/>
+      <c r="A395" s="21" t="s">
+        <v>392</v>
+      </c>
       <c r="D395" s="8"/>
     </row>
     <row r="396" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A396"/>
+      <c r="A396" s="21" t="s">
+        <v>393</v>
+      </c>
       <c r="D396" s="8"/>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A397"/>
+      <c r="A397" s="21" t="s">
+        <v>394</v>
+      </c>
       <c r="D397" s="8"/>
     </row>
     <row r="398" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A398"/>
+      <c r="A398" s="21" t="s">
+        <v>395</v>
+      </c>
       <c r="D398" s="8"/>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A399"/>
+      <c r="A399" s="21" t="s">
+        <v>396</v>
+      </c>
       <c r="D399" s="8"/>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A400"/>
+      <c r="A400" s="21" t="s">
+        <v>397</v>
+      </c>
       <c r="D400" s="8"/>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A401"/>
+      <c r="A401" s="21" t="s">
+        <v>398</v>
+      </c>
       <c r="D401" s="8"/>
     </row>
     <row r="402" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A402"/>
+      <c r="A402" s="21" t="s">
+        <v>399</v>
+      </c>
       <c r="D402" s="8"/>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A403"/>
+      <c r="A403" s="21" t="s">
+        <v>400</v>
+      </c>
       <c r="D403" s="8"/>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A404"/>
+      <c r="A404" s="21" t="s">
+        <v>401</v>
+      </c>
       <c r="D404" s="8"/>
     </row>
     <row r="405" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A405"/>
+      <c r="A405" s="21" t="s">
+        <v>402</v>
+      </c>
       <c r="D405" s="8"/>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A406"/>
+      <c r="A406" s="21" t="s">
+        <v>403</v>
+      </c>
       <c r="D406" s="8"/>
     </row>
     <row r="407" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A407"/>
+      <c r="A407" s="21" t="s">
+        <v>404</v>
+      </c>
       <c r="D407" s="8"/>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A408"/>
+      <c r="A408" s="21" t="s">
+        <v>405</v>
+      </c>
       <c r="D408" s="8"/>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A409"/>
+      <c r="A409" s="21" t="s">
+        <v>406</v>
+      </c>
       <c r="D409" s="8"/>
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A410"/>
+      <c r="A410" s="21" t="s">
+        <v>407</v>
+      </c>
       <c r="D410" s="8"/>
     </row>
     <row r="411" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A411"/>
+      <c r="A411" s="21" t="s">
+        <v>408</v>
+      </c>
       <c r="D411" s="8"/>
     </row>
     <row r="412" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A412"/>
+      <c r="A412" s="21" t="s">
+        <v>409</v>
+      </c>
       <c r="D412" s="8"/>
     </row>
     <row r="413" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A413"/>
+      <c r="A413" s="21" t="s">
+        <v>410</v>
+      </c>
       <c r="D413" s="8"/>
     </row>
     <row r="414" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A414"/>
+      <c r="A414" s="21" t="s">
+        <v>411</v>
+      </c>
       <c r="D414" s="8"/>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A415"/>
+      <c r="A415" s="21" t="s">
+        <v>412</v>
+      </c>
       <c r="D415" s="8"/>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A416"/>
+      <c r="A416" s="21" t="s">
+        <v>413</v>
+      </c>
       <c r="D416" s="8"/>
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A417"/>
+      <c r="A417" s="21" t="s">
+        <v>414</v>
+      </c>
       <c r="D417" s="8"/>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A418"/>
+      <c r="A418" s="21" t="s">
+        <v>415</v>
+      </c>
       <c r="D418" s="8"/>
     </row>
     <row r="419" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A419"/>
+      <c r="A419" s="21" t="s">
+        <v>416</v>
+      </c>
       <c r="D419" s="8"/>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A420"/>
+      <c r="A420" s="21" t="s">
+        <v>417</v>
+      </c>
       <c r="D420" s="8"/>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A421"/>
+      <c r="A421" s="21" t="s">
+        <v>418</v>
+      </c>
       <c r="D421" s="8"/>
     </row>
     <row r="422" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A422"/>
+      <c r="A422" s="21" t="s">
+        <v>419</v>
+      </c>
       <c r="D422" s="8"/>
     </row>
     <row r="423" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A423"/>
+      <c r="A423" s="21" t="s">
+        <v>420</v>
+      </c>
       <c r="D423" s="8"/>
     </row>
     <row r="424" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A424"/>
+      <c r="A424" s="21" t="s">
+        <v>421</v>
+      </c>
       <c r="D424" s="8"/>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A425"/>
+      <c r="A425" s="21" t="s">
+        <v>422</v>
+      </c>
       <c r="D425" s="8"/>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A426"/>
+      <c r="A426" s="21" t="s">
+        <v>423</v>
+      </c>
       <c r="D426" s="8"/>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A427"/>
+      <c r="A427" s="21" t="s">
+        <v>424</v>
+      </c>
       <c r="D427" s="8"/>
     </row>
     <row r="428" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A428"/>
+      <c r="A428" s="21" t="s">
+        <v>425</v>
+      </c>
       <c r="D428" s="8"/>
     </row>
     <row r="429" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A429"/>
+      <c r="A429" s="21" t="s">
+        <v>426</v>
+      </c>
       <c r="D429" s="8"/>
     </row>
     <row r="430" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A430"/>
+      <c r="A430" s="21" t="s">
+        <v>427</v>
+      </c>
       <c r="D430" s="8"/>
     </row>
     <row r="431" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A431"/>
+      <c r="A431" s="21" t="s">
+        <v>428</v>
+      </c>
       <c r="D431" s="8"/>
     </row>
     <row r="432" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A432"/>
+      <c r="A432" s="21" t="s">
+        <v>429</v>
+      </c>
       <c r="D432" s="8"/>
     </row>
     <row r="433" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A433"/>
+      <c r="A433" s="21" t="s">
+        <v>430</v>
+      </c>
       <c r="D433" s="8"/>
     </row>
     <row r="434" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A434"/>
+      <c r="A434" s="21" t="s">
+        <v>431</v>
+      </c>
       <c r="D434" s="8"/>
     </row>
     <row r="435" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A435"/>
+      <c r="A435" s="21" t="s">
+        <v>432</v>
+      </c>
       <c r="D435" s="8"/>
     </row>
     <row r="436" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A436"/>
+      <c r="A436" s="21" t="s">
+        <v>433</v>
+      </c>
       <c r="D436" s="8"/>
     </row>
     <row r="437" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A437"/>
+      <c r="A437" s="21" t="s">
+        <v>434</v>
+      </c>
       <c r="D437" s="8"/>
     </row>
     <row r="438" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A438"/>
+      <c r="A438" s="21" t="s">
+        <v>435</v>
+      </c>
       <c r="D438" s="8"/>
     </row>
     <row r="439" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A439"/>
+      <c r="A439" s="21" t="s">
+        <v>436</v>
+      </c>
       <c r="D439" s="8"/>
     </row>
     <row r="440" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A440"/>
+      <c r="A440" s="21" t="s">
+        <v>437</v>
+      </c>
       <c r="D440" s="8"/>
     </row>
     <row r="441" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A441"/>
+      <c r="A441" s="21" t="s">
+        <v>438</v>
+      </c>
       <c r="D441" s="8"/>
     </row>
     <row r="442" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A442"/>
+      <c r="A442" s="21" t="s">
+        <v>439</v>
+      </c>
       <c r="D442" s="8"/>
     </row>
     <row r="443" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A443"/>
+      <c r="A443" s="21" t="s">
+        <v>440</v>
+      </c>
       <c r="D443" s="8"/>
     </row>
     <row r="444" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A444"/>
+      <c r="A444" s="21" t="s">
+        <v>441</v>
+      </c>
       <c r="D444" s="8"/>
     </row>
     <row r="445" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A445"/>
+      <c r="A445" s="21" t="s">
+        <v>442</v>
+      </c>
       <c r="D445" s="8"/>
     </row>
     <row r="446" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A446"/>
+      <c r="A446" s="21" t="s">
+        <v>443</v>
+      </c>
       <c r="D446" s="8"/>
     </row>
     <row r="447" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A447"/>
+      <c r="A447" s="21" t="s">
+        <v>444</v>
+      </c>
       <c r="D447" s="8"/>
     </row>
     <row r="448" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A448"/>
+      <c r="A448" s="21" t="s">
+        <v>445</v>
+      </c>
       <c r="D448" s="8"/>
     </row>
     <row r="449" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A449"/>
+      <c r="A449" s="21" t="s">
+        <v>446</v>
+      </c>
       <c r="D449" s="8"/>
     </row>
     <row r="450" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A450"/>
+      <c r="A450" s="21" t="s">
+        <v>447</v>
+      </c>
       <c r="D450" s="8"/>
     </row>
     <row r="451" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A451"/>
+      <c r="A451" s="21" t="s">
+        <v>448</v>
+      </c>
       <c r="D451" s="8"/>
     </row>
     <row r="452" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A452"/>
+      <c r="A452" s="21" t="s">
+        <v>449</v>
+      </c>
       <c r="D452" s="8"/>
     </row>
     <row r="453" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A453"/>
+      <c r="A453" s="21" t="s">
+        <v>450</v>
+      </c>
       <c r="D453" s="8"/>
     </row>
     <row r="454" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A454"/>
+      <c r="A454" s="21" t="s">
+        <v>451</v>
+      </c>
       <c r="D454" s="8"/>
     </row>
     <row r="455" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A455"/>
+      <c r="A455" s="21" t="s">
+        <v>452</v>
+      </c>
       <c r="D455" s="8"/>
     </row>
     <row r="456" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A456"/>
+      <c r="A456" s="21" t="s">
+        <v>453</v>
+      </c>
       <c r="D456" s="8"/>
     </row>
     <row r="457" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A457"/>
+      <c r="A457" s="21" t="s">
+        <v>454</v>
+      </c>
       <c r="D457" s="8"/>
     </row>
     <row r="458" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A458"/>
+      <c r="A458" s="21" t="s">
+        <v>455</v>
+      </c>
       <c r="D458" s="8"/>
     </row>
     <row r="459" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A459"/>
+      <c r="A459" s="21" t="s">
+        <v>456</v>
+      </c>
       <c r="D459" s="8"/>
     </row>
     <row r="460" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A460"/>
+      <c r="A460" s="21" t="s">
+        <v>457</v>
+      </c>
       <c r="D460" s="8"/>
     </row>
     <row r="461" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A461"/>
+      <c r="A461" s="21" t="s">
+        <v>458</v>
+      </c>
       <c r="D461" s="8"/>
     </row>
     <row r="462" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A462"/>
+      <c r="A462" s="21" t="s">
+        <v>459</v>
+      </c>
       <c r="D462" s="8"/>
     </row>
     <row r="463" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A463"/>
+      <c r="A463" s="21" t="s">
+        <v>460</v>
+      </c>
       <c r="D463" s="8"/>
     </row>
     <row r="464" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A464"/>
+      <c r="A464" s="21" t="s">
+        <v>461</v>
+      </c>
       <c r="D464" s="8"/>
     </row>
     <row r="465" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A465"/>
+      <c r="A465" s="21" t="s">
+        <v>462</v>
+      </c>
       <c r="D465" s="8"/>
     </row>
     <row r="466" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A466"/>
+      <c r="A466" s="21" t="s">
+        <v>463</v>
+      </c>
       <c r="D466" s="8"/>
     </row>
     <row r="467" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A467"/>
+      <c r="A467" s="21" t="s">
+        <v>464</v>
+      </c>
       <c r="D467" s="8"/>
     </row>
     <row r="468" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A468"/>
+      <c r="A468" s="21" t="s">
+        <v>465</v>
+      </c>
       <c r="D468" s="8"/>
     </row>
     <row r="469" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A469"/>
+      <c r="A469" s="21" t="s">
+        <v>466</v>
+      </c>
       <c r="D469" s="8"/>
     </row>
     <row r="470" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A470"/>
+      <c r="A470" s="21" t="s">
+        <v>467</v>
+      </c>
       <c r="D470" s="8"/>
     </row>
     <row r="471" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A471"/>
+      <c r="A471" s="21" t="s">
+        <v>468</v>
+      </c>
       <c r="D471" s="8"/>
     </row>
     <row r="472" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A472"/>
+      <c r="A472" s="21" t="s">
+        <v>469</v>
+      </c>
       <c r="D472" s="8"/>
     </row>
     <row r="473" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A473"/>
+      <c r="A473" s="21" t="s">
+        <v>470</v>
+      </c>
       <c r="D473" s="8"/>
     </row>
     <row r="474" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A474"/>
+      <c r="A474" s="21" t="s">
+        <v>471</v>
+      </c>
       <c r="D474" s="8"/>
     </row>
     <row r="475" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A475"/>
+      <c r="A475" s="21" t="s">
+        <v>472</v>
+      </c>
       <c r="D475" s="8"/>
     </row>
     <row r="476" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A476"/>
+      <c r="A476" s="21" t="s">
+        <v>473</v>
+      </c>
       <c r="D476" s="8"/>
     </row>
     <row r="477" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A477"/>
+      <c r="A477" s="21" t="s">
+        <v>474</v>
+      </c>
       <c r="D477" s="8"/>
     </row>
     <row r="478" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A478"/>
+      <c r="A478" s="21" t="s">
+        <v>475</v>
+      </c>
       <c r="D478" s="8"/>
     </row>
     <row r="479" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A479"/>
+      <c r="A479" s="21" t="s">
+        <v>476</v>
+      </c>
       <c r="D479" s="8"/>
     </row>
     <row r="480" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A480"/>
+      <c r="A480" s="21" t="s">
+        <v>477</v>
+      </c>
       <c r="D480" s="8"/>
     </row>
     <row r="481" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A481"/>
+      <c r="A481" s="21" t="s">
+        <v>478</v>
+      </c>
       <c r="D481" s="8"/>
     </row>
     <row r="482" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A482"/>
+      <c r="A482" s="21" t="s">
+        <v>479</v>
+      </c>
       <c r="D482" s="8"/>
     </row>
     <row r="483" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A483"/>
+      <c r="A483" s="21" t="s">
+        <v>480</v>
+      </c>
       <c r="D483" s="8"/>
     </row>
     <row r="484" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A484"/>
+      <c r="A484" s="21" t="s">
+        <v>481</v>
+      </c>
       <c r="D484" s="8"/>
     </row>
     <row r="485" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A485"/>
+      <c r="A485" s="21" t="s">
+        <v>482</v>
+      </c>
       <c r="D485" s="8"/>
     </row>
     <row r="486" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A486"/>
+      <c r="A486" s="21" t="s">
+        <v>483</v>
+      </c>
       <c r="D486" s="8"/>
     </row>
     <row r="487" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A487"/>
+      <c r="A487" s="21" t="s">
+        <v>484</v>
+      </c>
       <c r="D487" s="8"/>
     </row>
     <row r="488" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A488"/>
+      <c r="A488" s="21" t="s">
+        <v>485</v>
+      </c>
       <c r="D488" s="8"/>
     </row>
     <row r="489" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A489"/>
+      <c r="A489" s="21" t="s">
+        <v>486</v>
+      </c>
       <c r="D489" s="8"/>
     </row>
     <row r="490" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A490"/>
+      <c r="A490" s="21" t="s">
+        <v>487</v>
+      </c>
       <c r="D490" s="8"/>
     </row>
     <row r="491" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A491"/>
+      <c r="A491" s="21" t="s">
+        <v>488</v>
+      </c>
       <c r="D491" s="8"/>
     </row>
     <row r="492" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A492"/>
+      <c r="A492" s="21" t="s">
+        <v>489</v>
+      </c>
       <c r="D492" s="8"/>
     </row>
     <row r="493" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A493"/>
+      <c r="A493" s="21" t="s">
+        <v>490</v>
+      </c>
       <c r="D493" s="8"/>
     </row>
     <row r="494" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A494"/>
+      <c r="A494" s="21" t="s">
+        <v>491</v>
+      </c>
       <c r="D494" s="8"/>
     </row>
     <row r="495" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A495"/>
+      <c r="A495" s="21" t="s">
+        <v>492</v>
+      </c>
       <c r="D495" s="8"/>
     </row>
     <row r="496" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A496"/>
+      <c r="A496" s="21" t="s">
+        <v>493</v>
+      </c>
       <c r="D496" s="8"/>
     </row>
     <row r="497" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A497"/>
+      <c r="A497" s="21" t="s">
+        <v>494</v>
+      </c>
       <c r="D497" s="8"/>
     </row>
     <row r="498" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A498"/>
+      <c r="A498" s="21" t="s">
+        <v>495</v>
+      </c>
       <c r="D498" s="8"/>
     </row>
     <row r="499" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A499"/>
+      <c r="A499" s="21" t="s">
+        <v>496</v>
+      </c>
       <c r="D499" s="8"/>
     </row>
     <row r="500" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A500"/>
+      <c r="A500" s="21" t="s">
+        <v>497</v>
+      </c>
       <c r="D500" s="8"/>
     </row>
     <row r="501" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A501"/>
+      <c r="A501" s="21" t="s">
+        <v>498</v>
+      </c>
       <c r="D501" s="8"/>
     </row>
     <row r="502" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A502"/>
+      <c r="A502" s="21" t="s">
+        <v>499</v>
+      </c>
       <c r="D502" s="8"/>
     </row>
     <row r="503" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A503"/>
+      <c r="A503" s="21" t="s">
+        <v>500</v>
+      </c>
       <c r="D503" s="8"/>
     </row>
     <row r="504" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A504"/>
+      <c r="A504" s="21" t="s">
+        <v>501</v>
+      </c>
       <c r="D504" s="8"/>
     </row>
     <row r="505" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A505"/>
+      <c r="A505" s="21" t="s">
+        <v>502</v>
+      </c>
       <c r="D505" s="8"/>
     </row>
     <row r="506" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A506"/>
+      <c r="A506" s="21" t="s">
+        <v>503</v>
+      </c>
       <c r="D506" s="8"/>
     </row>
     <row r="507" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A507"/>
+      <c r="A507" s="21" t="s">
+        <v>504</v>
+      </c>
       <c r="D507" s="8"/>
     </row>
     <row r="508" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A508"/>
+      <c r="A508" s="21" t="s">
+        <v>505</v>
+      </c>
       <c r="D508" s="8"/>
     </row>
     <row r="509" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A509"/>
+      <c r="A509" s="21" t="s">
+        <v>506</v>
+      </c>
       <c r="D509" s="8"/>
     </row>
     <row r="510" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A510"/>
+      <c r="A510" s="21" t="s">
+        <v>507</v>
+      </c>
       <c r="D510" s="8"/>
     </row>
     <row r="511" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A511"/>
+      <c r="A511" s="21" t="s">
+        <v>508</v>
+      </c>
       <c r="D511" s="8"/>
     </row>
     <row r="512" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A512"/>
+      <c r="A512" s="21" t="s">
+        <v>509</v>
+      </c>
       <c r="D512" s="8"/>
     </row>
     <row r="513" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A513"/>
+      <c r="A513" s="21" t="s">
+        <v>510</v>
+      </c>
       <c r="D513" s="8"/>
     </row>
     <row r="514" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A514"/>
+      <c r="A514" s="21" t="s">
+        <v>511</v>
+      </c>
       <c r="D514" s="8"/>
     </row>
     <row r="515" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A515"/>
+      <c r="A515" s="21" t="s">
+        <v>512</v>
+      </c>
       <c r="D515" s="8"/>
     </row>
     <row r="516" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A516"/>
+      <c r="A516" s="21" t="s">
+        <v>513</v>
+      </c>
       <c r="D516" s="8"/>
     </row>
     <row r="517" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A517"/>
+      <c r="A517" s="21" t="s">
+        <v>514</v>
+      </c>
       <c r="D517" s="8"/>
     </row>
     <row r="518" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A518"/>
+      <c r="A518" s="21" t="s">
+        <v>515</v>
+      </c>
       <c r="D518" s="8"/>
     </row>
     <row r="519" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A519"/>
+      <c r="A519" s="21" t="s">
+        <v>516</v>
+      </c>
       <c r="D519" s="8"/>
     </row>
     <row r="520" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A520"/>
+      <c r="A520" s="21" t="s">
+        <v>517</v>
+      </c>
       <c r="D520" s="8"/>
     </row>
     <row r="521" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A521"/>
+      <c r="A521" s="21" t="s">
+        <v>518</v>
+      </c>
       <c r="D521" s="8"/>
     </row>
     <row r="522" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A522"/>
+      <c r="A522" s="21" t="s">
+        <v>519</v>
+      </c>
       <c r="D522" s="8"/>
     </row>
     <row r="523" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A523"/>
+      <c r="A523" s="21" t="s">
+        <v>520</v>
+      </c>
       <c r="D523" s="8"/>
     </row>
     <row r="524" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A524"/>
+      <c r="A524" s="21" t="s">
+        <v>521</v>
+      </c>
       <c r="D524" s="8"/>
     </row>
     <row r="525" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A525"/>
+      <c r="A525" s="21" t="s">
+        <v>522</v>
+      </c>
       <c r="D525" s="8"/>
     </row>
     <row r="526" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A526"/>
+      <c r="A526" s="21" t="s">
+        <v>523</v>
+      </c>
       <c r="D526" s="8"/>
     </row>
     <row r="527" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A527"/>
+      <c r="A527" s="21" t="s">
+        <v>524</v>
+      </c>
       <c r="D527" s="8"/>
     </row>
     <row r="528" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A528"/>
+      <c r="A528" s="21" t="s">
+        <v>525</v>
+      </c>
       <c r="D528" s="8"/>
     </row>
     <row r="529" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A529"/>
+      <c r="A529" s="21" t="s">
+        <v>526</v>
+      </c>
       <c r="D529" s="8"/>
     </row>
     <row r="530" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A530"/>
+      <c r="A530" s="21" t="s">
+        <v>527</v>
+      </c>
       <c r="D530" s="8"/>
     </row>
     <row r="531" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A531"/>
+      <c r="A531" s="21" t="s">
+        <v>528</v>
+      </c>
       <c r="D531" s="8"/>
     </row>
     <row r="532" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A532"/>
+      <c r="A532" s="21" t="s">
+        <v>529</v>
+      </c>
       <c r="D532" s="8"/>
     </row>
     <row r="533" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A533"/>
+      <c r="A533" s="21" t="s">
+        <v>530</v>
+      </c>
       <c r="D533" s="8"/>
     </row>
     <row r="534" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A534"/>
+      <c r="A534" s="21" t="s">
+        <v>531</v>
+      </c>
       <c r="D534" s="8"/>
     </row>
     <row r="535" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A535"/>
+      <c r="A535" s="21" t="s">
+        <v>532</v>
+      </c>
       <c r="D535" s="8"/>
     </row>
     <row r="536" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A536"/>
+      <c r="A536" s="21" t="s">
+        <v>533</v>
+      </c>
       <c r="D536" s="8"/>
     </row>
     <row r="537" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A537"/>
+      <c r="A537" s="21" t="s">
+        <v>534</v>
+      </c>
       <c r="D537" s="8"/>
     </row>
     <row r="538" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A538"/>
+      <c r="A538" s="21" t="s">
+        <v>535</v>
+      </c>
       <c r="D538" s="8"/>
     </row>
     <row r="539" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A539"/>
+      <c r="A539" s="21" t="s">
+        <v>536</v>
+      </c>
       <c r="D539" s="8"/>
     </row>
     <row r="540" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A540"/>
+      <c r="A540" s="21" t="s">
+        <v>537</v>
+      </c>
       <c r="D540" s="8"/>
     </row>
     <row r="541" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A541"/>
+      <c r="A541" s="21" t="s">
+        <v>538</v>
+      </c>
       <c r="D541" s="8"/>
     </row>
     <row r="542" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A542"/>
+      <c r="A542" s="21" t="s">
+        <v>539</v>
+      </c>
       <c r="D542" s="8"/>
     </row>
     <row r="543" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A543"/>
+      <c r="A543" s="21" t="s">
+        <v>540</v>
+      </c>
       <c r="D543" s="8"/>
     </row>
     <row r="544" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A544"/>
+      <c r="A544" s="21" t="s">
+        <v>541</v>
+      </c>
       <c r="D544" s="8"/>
     </row>
     <row r="545" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A545"/>
+      <c r="A545" s="21" t="s">
+        <v>542</v>
+      </c>
       <c r="D545" s="8"/>
     </row>
     <row r="546" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A546"/>
+      <c r="A546" s="21" t="s">
+        <v>543</v>
+      </c>
       <c r="D546" s="8"/>
     </row>
     <row r="547" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A547"/>
+      <c r="A547" s="21" t="s">
+        <v>544</v>
+      </c>
       <c r="D547" s="8"/>
     </row>
     <row r="548" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A548"/>
+      <c r="A548" s="21" t="s">
+        <v>545</v>
+      </c>
       <c r="D548" s="8"/>
     </row>
     <row r="549" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A549"/>
+      <c r="A549" s="21" t="s">
+        <v>546</v>
+      </c>
       <c r="D549" s="8"/>
     </row>
     <row r="550" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A550"/>
+      <c r="A550" s="21" t="s">
+        <v>547</v>
+      </c>
       <c r="D550" s="8"/>
     </row>
     <row r="551" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A551"/>
+      <c r="A551" s="21" t="s">
+        <v>548</v>
+      </c>
       <c r="D551" s="8"/>
     </row>
     <row r="552" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A552"/>
+      <c r="A552" s="21" t="s">
+        <v>549</v>
+      </c>
       <c r="D552" s="8"/>
     </row>
     <row r="553" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A553"/>
+      <c r="A553" s="21" t="s">
+        <v>550</v>
+      </c>
       <c r="D553" s="8"/>
     </row>
     <row r="554" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A554"/>
+      <c r="A554" s="21" t="s">
+        <v>551</v>
+      </c>
       <c r="D554" s="8"/>
     </row>
     <row r="555" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A555"/>
+      <c r="A555" s="21" t="s">
+        <v>552</v>
+      </c>
       <c r="D555" s="8"/>
     </row>
     <row r="556" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A556"/>
+      <c r="A556" s="21" t="s">
+        <v>553</v>
+      </c>
       <c r="D556" s="8"/>
     </row>
     <row r="557" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A557"/>
+      <c r="A557" s="21" t="s">
+        <v>554</v>
+      </c>
       <c r="D557" s="8"/>
     </row>
     <row r="558" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A558"/>
+      <c r="A558" s="21" t="s">
+        <v>555</v>
+      </c>
       <c r="D558" s="8"/>
     </row>
     <row r="559" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A559"/>
+      <c r="A559" s="21" t="s">
+        <v>556</v>
+      </c>
       <c r="D559" s="8"/>
     </row>
     <row r="560" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A560"/>
+      <c r="A560" s="21" t="s">
+        <v>557</v>
+      </c>
       <c r="D560" s="8"/>
     </row>
     <row r="561" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A561"/>
+      <c r="A561" s="21" t="s">
+        <v>558</v>
+      </c>
       <c r="D561" s="8"/>
     </row>
     <row r="562" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A562"/>
+      <c r="A562" s="21" t="s">
+        <v>559</v>
+      </c>
       <c r="D562" s="8"/>
     </row>
     <row r="563" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A563"/>
+      <c r="A563" s="21" t="s">
+        <v>560</v>
+      </c>
       <c r="D563" s="8"/>
     </row>
     <row r="564" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A564"/>
+      <c r="A564" s="21" t="s">
+        <v>561</v>
+      </c>
       <c r="D564" s="8"/>
     </row>
     <row r="565" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A565"/>
+      <c r="A565" s="21" t="s">
+        <v>562</v>
+      </c>
       <c r="D565" s="8"/>
     </row>
     <row r="566" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A566"/>
+      <c r="A566" s="21" t="s">
+        <v>563</v>
+      </c>
       <c r="D566" s="8"/>
     </row>
     <row r="567" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A567"/>
+      <c r="A567" s="21" t="s">
+        <v>564</v>
+      </c>
       <c r="D567" s="8"/>
     </row>
     <row r="568" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A568"/>
+      <c r="A568" s="21" t="s">
+        <v>565</v>
+      </c>
       <c r="D568" s="8"/>
     </row>
     <row r="569" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A569"/>
+      <c r="A569" s="21" t="s">
+        <v>566</v>
+      </c>
       <c r="D569" s="8"/>
     </row>
     <row r="570" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A570"/>
+      <c r="A570" s="21" t="s">
+        <v>567</v>
+      </c>
       <c r="D570" s="8"/>
     </row>
     <row r="571" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A571"/>
+      <c r="A571" s="21" t="s">
+        <v>568</v>
+      </c>
       <c r="D571" s="8"/>
     </row>
     <row r="572" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A572"/>
+      <c r="A572" s="21" t="s">
+        <v>569</v>
+      </c>
       <c r="D572" s="8"/>
     </row>
     <row r="573" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A573"/>
+      <c r="A573" s="21" t="s">
+        <v>570</v>
+      </c>
       <c r="D573" s="8"/>
     </row>
     <row r="574" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A574"/>
+      <c r="A574" s="21" t="s">
+        <v>571</v>
+      </c>
       <c r="D574" s="8"/>
     </row>
     <row r="575" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A575"/>
+      <c r="A575" s="21" t="s">
+        <v>572</v>
+      </c>
       <c r="D575" s="8"/>
     </row>
     <row r="576" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A576"/>
+      <c r="A576" s="21" t="s">
+        <v>573</v>
+      </c>
       <c r="D576" s="8"/>
     </row>
     <row r="577" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A577"/>
+      <c r="A577" s="21" t="s">
+        <v>574</v>
+      </c>
       <c r="D577" s="8"/>
     </row>
     <row r="578" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A578"/>
+      <c r="A578" s="21" t="s">
+        <v>575</v>
+      </c>
       <c r="D578" s="8"/>
     </row>
     <row r="579" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A579"/>
+      <c r="A579" s="21" t="s">
+        <v>576</v>
+      </c>
       <c r="D579" s="8"/>
     </row>
     <row r="580" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A580"/>
+      <c r="A580" s="21" t="s">
+        <v>577</v>
+      </c>
       <c r="D580" s="8"/>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A581"/>
+      <c r="A581" s="21" t="s">
+        <v>578</v>
+      </c>
       <c r="D581" s="8"/>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A582"/>
+      <c r="A582" s="21" t="s">
+        <v>579</v>
+      </c>
       <c r="D582" s="8"/>
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A583"/>
+      <c r="A583" s="21" t="s">
+        <v>580</v>
+      </c>
       <c r="D583" s="8"/>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A584"/>
+      <c r="A584" s="21" t="s">
+        <v>581</v>
+      </c>
       <c r="D584" s="8"/>
     </row>
     <row r="585" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A585"/>
+      <c r="A585" s="21" t="s">
+        <v>582</v>
+      </c>
       <c r="D585" s="8"/>
     </row>
     <row r="586" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A586"/>
+      <c r="A586" s="21" t="s">
+        <v>583</v>
+      </c>
       <c r="D586" s="8"/>
     </row>
     <row r="587" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A587"/>
+      <c r="A587" s="21" t="s">
+        <v>584</v>
+      </c>
       <c r="D587" s="8"/>
     </row>
     <row r="588" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A588"/>
+      <c r="A588" s="21" t="s">
+        <v>585</v>
+      </c>
       <c r="D588" s="8"/>
     </row>
     <row r="589" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A589"/>
+      <c r="A589" s="21" t="s">
+        <v>586</v>
+      </c>
       <c r="D589" s="8"/>
     </row>
     <row r="590" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A590"/>
+      <c r="A590" s="21" t="s">
+        <v>587</v>
+      </c>
       <c r="D590" s="8"/>
     </row>
     <row r="591" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A591"/>
+      <c r="A591" s="21" t="s">
+        <v>588</v>
+      </c>
       <c r="D591" s="8"/>
     </row>
     <row r="592" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A592"/>
+      <c r="A592" s="21" t="s">
+        <v>589</v>
+      </c>
       <c r="D592" s="8"/>
     </row>
     <row r="593" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A593"/>
+      <c r="A593" s="21" t="s">
+        <v>590</v>
+      </c>
       <c r="D593" s="8"/>
     </row>
     <row r="594" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A594"/>
+      <c r="A594" s="21" t="s">
+        <v>591</v>
+      </c>
       <c r="D594" s="8"/>
     </row>
     <row r="595" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A595"/>
+      <c r="A595" s="21" t="s">
+        <v>592</v>
+      </c>
       <c r="D595" s="8"/>
     </row>
     <row r="596" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A596"/>
+      <c r="A596" s="21" t="s">
+        <v>593</v>
+      </c>
       <c r="D596" s="8"/>
     </row>
     <row r="597" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A597"/>
+      <c r="A597" s="21" t="s">
+        <v>594</v>
+      </c>
       <c r="D597" s="8"/>
     </row>
     <row r="598" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A598"/>
+      <c r="A598" s="21" t="s">
+        <v>595</v>
+      </c>
       <c r="D598" s="8"/>
     </row>
     <row r="599" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A599"/>
+      <c r="A599" s="21" t="s">
+        <v>596</v>
+      </c>
       <c r="D599" s="8"/>
     </row>
     <row r="600" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A600"/>
+      <c r="A600" s="21" t="s">
+        <v>597</v>
+      </c>
       <c r="D600" s="8"/>
     </row>
     <row r="601" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A601"/>
+      <c r="A601" s="21" t="s">
+        <v>598</v>
+      </c>
       <c r="D601" s="8"/>
     </row>
     <row r="602" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A602"/>
+      <c r="A602" s="21" t="s">
+        <v>599</v>
+      </c>
       <c r="D602" s="8"/>
     </row>
     <row r="603" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A603"/>
+      <c r="A603" s="21" t="s">
+        <v>600</v>
+      </c>
       <c r="D603" s="8"/>
     </row>
     <row r="604" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A604"/>
+      <c r="A604" s="21" t="s">
+        <v>601</v>
+      </c>
       <c r="D604" s="8"/>
     </row>
     <row r="605" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A605"/>
+      <c r="A605" s="21" t="s">
+        <v>602</v>
+      </c>
       <c r="D605" s="8"/>
     </row>
     <row r="606" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A606"/>
+      <c r="A606" s="21" t="s">
+        <v>603</v>
+      </c>
       <c r="D606" s="8"/>
     </row>
     <row r="607" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A607"/>
+      <c r="A607" s="21" t="s">
+        <v>604</v>
+      </c>
       <c r="D607" s="8"/>
     </row>
     <row r="608" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A608"/>
+      <c r="A608" s="21" t="s">
+        <v>605</v>
+      </c>
       <c r="D608" s="8"/>
     </row>
     <row r="609" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A609"/>
+      <c r="A609" s="21" t="s">
+        <v>606</v>
+      </c>
       <c r="D609" s="8"/>
     </row>
     <row r="610" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A610"/>
+      <c r="A610" s="21" t="s">
+        <v>607</v>
+      </c>
       <c r="D610" s="8"/>
     </row>
     <row r="611" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A611"/>
+      <c r="A611" s="21" t="s">
+        <v>608</v>
+      </c>
       <c r="D611" s="8"/>
     </row>
     <row r="612" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A612"/>
+      <c r="A612" s="21" t="s">
+        <v>609</v>
+      </c>
       <c r="D612" s="8"/>
     </row>
     <row r="613" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A613"/>
+      <c r="A613" s="21" t="s">
+        <v>610</v>
+      </c>
       <c r="D613" s="8"/>
     </row>
     <row r="614" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A614"/>
+      <c r="A614" s="21" t="s">
+        <v>611</v>
+      </c>
       <c r="D614" s="8"/>
     </row>
     <row r="615" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A615"/>
+      <c r="A615" s="21" t="s">
+        <v>612</v>
+      </c>
       <c r="D615" s="8"/>
     </row>
     <row r="616" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A616"/>
+      <c r="A616" s="21" t="s">
+        <v>613</v>
+      </c>
       <c r="D616" s="8"/>
     </row>
     <row r="617" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A617"/>
+      <c r="A617" s="21" t="s">
+        <v>614</v>
+      </c>
       <c r="D617" s="8"/>
     </row>
     <row r="618" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A618"/>
+      <c r="A618" s="21" t="s">
+        <v>615</v>
+      </c>
       <c r="D618" s="8"/>
     </row>
     <row r="619" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A619"/>
+      <c r="A619" s="21" t="s">
+        <v>616</v>
+      </c>
       <c r="D619" s="8"/>
     </row>
     <row r="620" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A620"/>
+      <c r="A620" s="21" t="s">
+        <v>617</v>
+      </c>
       <c r="D620" s="8"/>
     </row>
     <row r="621" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A621"/>
+      <c r="A621" s="21" t="s">
+        <v>618</v>
+      </c>
       <c r="D621" s="8"/>
     </row>
     <row r="622" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A622"/>
+      <c r="A622" s="21" t="s">
+        <v>619</v>
+      </c>
       <c r="D622" s="8"/>
     </row>
     <row r="623" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A623"/>
+      <c r="A623" s="21" t="s">
+        <v>620</v>
+      </c>
       <c r="D623" s="8"/>
     </row>
     <row r="624" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A624"/>
+      <c r="A624" s="21" t="s">
+        <v>621</v>
+      </c>
       <c r="D624" s="8"/>
     </row>
     <row r="625" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A625"/>
+      <c r="A625" s="21" t="s">
+        <v>622</v>
+      </c>
       <c r="D625" s="8"/>
     </row>
     <row r="626" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A626"/>
+      <c r="A626" s="21" t="s">
+        <v>623</v>
+      </c>
       <c r="D626" s="8"/>
     </row>
     <row r="627" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A627"/>
+      <c r="A627" s="21" t="s">
+        <v>624</v>
+      </c>
       <c r="D627" s="8"/>
     </row>
     <row r="628" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A628"/>
+      <c r="A628" s="21" t="s">
+        <v>625</v>
+      </c>
       <c r="D628" s="8"/>
     </row>
     <row r="629" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A629"/>
+      <c r="A629" s="21" t="s">
+        <v>625</v>
+      </c>
       <c r="D629" s="8"/>
     </row>
     <row r="630" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A630"/>
+      <c r="A630" s="21" t="s">
+        <v>626</v>
+      </c>
       <c r="D630" s="8"/>
     </row>
     <row r="631" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A631"/>
+      <c r="A631" s="21" t="s">
+        <v>627</v>
+      </c>
       <c r="D631" s="8"/>
     </row>
     <row r="632" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A632"/>
+      <c r="A632" s="21" t="s">
+        <v>628</v>
+      </c>
       <c r="D632" s="8"/>
     </row>
     <row r="633" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A633"/>
+      <c r="A633" s="21" t="s">
+        <v>629</v>
+      </c>
       <c r="D633" s="8"/>
     </row>
     <row r="634" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A634"/>
+      <c r="A634" s="21" t="s">
+        <v>630</v>
+      </c>
       <c r="D634" s="8"/>
     </row>
     <row r="635" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A635"/>
+      <c r="A635" s="21" t="s">
+        <v>631</v>
+      </c>
       <c r="D635" s="8"/>
     </row>
     <row r="636" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A636"/>
+      <c r="A636" s="21" t="s">
+        <v>632</v>
+      </c>
       <c r="D636" s="8"/>
     </row>
     <row r="637" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A637"/>
+      <c r="A637" s="21" t="s">
+        <v>633</v>
+      </c>
       <c r="D637" s="8"/>
     </row>
     <row r="638" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A638"/>
+      <c r="A638" s="21" t="s">
+        <v>634</v>
+      </c>
       <c r="D638" s="8"/>
     </row>
     <row r="639" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A639"/>
+      <c r="A639" s="21" t="s">
+        <v>635</v>
+      </c>
       <c r="D639" s="8"/>
     </row>
     <row r="640" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A640"/>
+      <c r="A640" s="21" t="s">
+        <v>636</v>
+      </c>
       <c r="D640" s="8"/>
     </row>
     <row r="641" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A641"/>
+      <c r="A641" s="21" t="s">
+        <v>637</v>
+      </c>
       <c r="D641" s="8"/>
     </row>
     <row r="642" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A642"/>
+      <c r="A642" s="21" t="s">
+        <v>638</v>
+      </c>
       <c r="D642" s="8"/>
     </row>
     <row r="643" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A643"/>
+      <c r="A643" s="21" t="s">
+        <v>639</v>
+      </c>
       <c r="D643" s="8"/>
     </row>
     <row r="644" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A644"/>
+      <c r="A644" s="21" t="s">
+        <v>640</v>
+      </c>
       <c r="D644" s="8"/>
     </row>
     <row r="645" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A645"/>
+      <c r="A645" s="21" t="s">
+        <v>641</v>
+      </c>
       <c r="D645" s="8"/>
     </row>
     <row r="646" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A646"/>
+      <c r="A646" s="21" t="s">
+        <v>642</v>
+      </c>
       <c r="D646" s="8"/>
     </row>
     <row r="647" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A647"/>
+      <c r="A647" s="21" t="s">
+        <v>643</v>
+      </c>
       <c r="D647" s="8"/>
     </row>
     <row r="648" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A648"/>
+      <c r="A648" s="21" t="s">
+        <v>644</v>
+      </c>
       <c r="D648" s="8"/>
     </row>
     <row r="649" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A649"/>
+      <c r="A649" s="21" t="s">
+        <v>645</v>
+      </c>
       <c r="D649" s="8"/>
     </row>
     <row r="650" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A650"/>
+      <c r="A650" s="21" t="s">
+        <v>646</v>
+      </c>
       <c r="D650" s="8"/>
     </row>
     <row r="651" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A651"/>
+      <c r="A651" s="21" t="s">
+        <v>647</v>
+      </c>
       <c r="D651" s="8"/>
     </row>
     <row r="652" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A652"/>
+      <c r="A652" s="21" t="s">
+        <v>648</v>
+      </c>
       <c r="D652" s="8"/>
     </row>
     <row r="653" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A653"/>
+      <c r="A653" s="21" t="s">
+        <v>649</v>
+      </c>
       <c r="D653" s="8"/>
     </row>
     <row r="654" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A654"/>
+      <c r="A654" s="21" t="s">
+        <v>649</v>
+      </c>
       <c r="D654" s="8"/>
     </row>
     <row r="655" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A655"/>
+      <c r="A655" s="21" t="s">
+        <v>650</v>
+      </c>
       <c r="D655" s="8"/>
     </row>
     <row r="656" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A656"/>
+      <c r="A656" s="21" t="s">
+        <v>651</v>
+      </c>
       <c r="D656" s="8"/>
     </row>
     <row r="657" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A657"/>
+      <c r="A657" s="21" t="s">
+        <v>652</v>
+      </c>
       <c r="D657" s="8"/>
     </row>
     <row r="658" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A658"/>
+      <c r="A658" s="21" t="s">
+        <v>653</v>
+      </c>
       <c r="D658" s="8"/>
     </row>
     <row r="659" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A659"/>
+      <c r="A659" s="21" t="s">
+        <v>654</v>
+      </c>
       <c r="D659" s="8"/>
     </row>
     <row r="660" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A660"/>
+      <c r="A660" s="21" t="s">
+        <v>655</v>
+      </c>
       <c r="D660" s="8"/>
     </row>
     <row r="661" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A661"/>
+      <c r="A661" s="21" t="s">
+        <v>656</v>
+      </c>
       <c r="D661" s="8"/>
     </row>
     <row r="662" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A662"/>
+      <c r="A662" s="21" t="s">
+        <v>657</v>
+      </c>
       <c r="D662" s="8"/>
     </row>
     <row r="663" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A663"/>
+      <c r="A663" s="21" t="s">
+        <v>658</v>
+      </c>
       <c r="D663" s="8"/>
     </row>
     <row r="664" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A664"/>
+      <c r="A664" s="21" t="s">
+        <v>658</v>
+      </c>
       <c r="D664" s="8"/>
     </row>
     <row r="665" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A665"/>
+      <c r="A665" s="21" t="s">
+        <v>659</v>
+      </c>
       <c r="D665" s="8"/>
     </row>
     <row r="666" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A666"/>
+      <c r="A666" s="21" t="s">
+        <v>660</v>
+      </c>
       <c r="D666" s="8"/>
     </row>
     <row r="667" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A667"/>
+      <c r="A667" s="21" t="s">
+        <v>661</v>
+      </c>
       <c r="D667" s="8"/>
     </row>
     <row r="668" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A668"/>
+      <c r="A668" s="21" t="s">
+        <v>662</v>
+      </c>
       <c r="D668" s="8"/>
     </row>
     <row r="669" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A669"/>
+      <c r="A669" s="21" t="s">
+        <v>663</v>
+      </c>
       <c r="D669" s="8"/>
     </row>
     <row r="670" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A670"/>
+      <c r="A670" s="21" t="s">
+        <v>664</v>
+      </c>
       <c r="D670" s="8"/>
     </row>
     <row r="671" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A671"/>
+      <c r="A671" s="21" t="s">
+        <v>665</v>
+      </c>
       <c r="D671" s="8"/>
     </row>
     <row r="672" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A672"/>
+      <c r="A672" s="21" t="s">
+        <v>666</v>
+      </c>
       <c r="D672" s="8"/>
     </row>
     <row r="673" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A673"/>
+      <c r="A673" s="21" t="s">
+        <v>667</v>
+      </c>
       <c r="D673" s="8"/>
     </row>
     <row r="674" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A674"/>
+      <c r="A674" s="21" t="s">
+        <v>668</v>
+      </c>
       <c r="D674" s="8"/>
     </row>
     <row r="675" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A675"/>
+      <c r="A675" s="21" t="s">
+        <v>669</v>
+      </c>
       <c r="D675" s="8"/>
     </row>
     <row r="676" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A676"/>
+      <c r="A676" s="21" t="s">
+        <v>670</v>
+      </c>
       <c r="D676" s="8"/>
     </row>
     <row r="677" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A677"/>
+      <c r="A677" s="21" t="s">
+        <v>671</v>
+      </c>
       <c r="D677" s="8"/>
     </row>
     <row r="678" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A678"/>
+      <c r="A678" s="21" t="s">
+        <v>672</v>
+      </c>
       <c r="D678" s="8"/>
     </row>
     <row r="679" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A679"/>
+      <c r="A679" s="21" t="s">
+        <v>673</v>
+      </c>
       <c r="D679" s="8"/>
     </row>
     <row r="680" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A680"/>
+      <c r="A680" s="21" t="s">
+        <v>674</v>
+      </c>
       <c r="D680" s="8"/>
     </row>
     <row r="681" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A681"/>
+      <c r="A681" s="21" t="s">
+        <v>675</v>
+      </c>
       <c r="D681" s="8"/>
     </row>
     <row r="682" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A682"/>
+      <c r="A682" s="21" t="s">
+        <v>676</v>
+      </c>
       <c r="D682" s="8"/>
     </row>
     <row r="683" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A683"/>
+      <c r="A683" s="21" t="s">
+        <v>677</v>
+      </c>
       <c r="D683" s="8"/>
     </row>
     <row r="684" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A684"/>
+      <c r="A684" s="21" t="s">
+        <v>678</v>
+      </c>
       <c r="D684" s="8"/>
     </row>
     <row r="685" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A685"/>
+      <c r="A685" s="21" t="s">
+        <v>679</v>
+      </c>
       <c r="D685" s="8"/>
     </row>
     <row r="686" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A686"/>
+      <c r="A686" s="21" t="s">
+        <v>680</v>
+      </c>
       <c r="D686" s="8"/>
     </row>
     <row r="687" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A687"/>
+      <c r="A687" s="21" t="s">
+        <v>681</v>
+      </c>
       <c r="D687" s="8"/>
     </row>
     <row r="688" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A688"/>
+      <c r="A688" s="21" t="s">
+        <v>682</v>
+      </c>
       <c r="D688" s="8"/>
     </row>
     <row r="689" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A689"/>
+      <c r="A689" s="21" t="s">
+        <v>683</v>
+      </c>
       <c r="D689" s="8"/>
     </row>
     <row r="690" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A690"/>
+      <c r="A690" s="21" t="s">
+        <v>684</v>
+      </c>
       <c r="D690" s="8"/>
     </row>
     <row r="691" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A691"/>
+      <c r="A691" s="21" t="s">
+        <v>685</v>
+      </c>
       <c r="D691" s="8"/>
     </row>
     <row r="692" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A692"/>
+      <c r="A692" s="21" t="s">
+        <v>686</v>
+      </c>
       <c r="D692" s="8"/>
     </row>
     <row r="693" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A693"/>
+      <c r="A693" s="21" t="s">
+        <v>687</v>
+      </c>
       <c r="D693" s="8"/>
     </row>
     <row r="694" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A694"/>
+      <c r="A694" s="21" t="s">
+        <v>688</v>
+      </c>
       <c r="D694" s="8"/>
     </row>
     <row r="695" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A695"/>
+      <c r="A695" s="21" t="s">
+        <v>689</v>
+      </c>
       <c r="D695" s="8"/>
     </row>
     <row r="696" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A696"/>
+      <c r="A696" s="21" t="s">
+        <v>690</v>
+      </c>
       <c r="D696" s="8"/>
     </row>
     <row r="697" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A697"/>
+      <c r="A697" s="21" t="s">
+        <v>691</v>
+      </c>
       <c r="D697" s="8"/>
     </row>
     <row r="698" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A698"/>
+      <c r="A698" s="21" t="s">
+        <v>692</v>
+      </c>
       <c r="D698" s="8"/>
     </row>
     <row r="699" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A699"/>
+      <c r="A699" s="21" t="s">
+        <v>693</v>
+      </c>
       <c r="D699" s="8"/>
     </row>
     <row r="700" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A700"/>
+      <c r="A700" s="21" t="s">
+        <v>694</v>
+      </c>
       <c r="D700" s="8"/>
     </row>
     <row r="701" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A701"/>
+      <c r="A701" s="21" t="s">
+        <v>695</v>
+      </c>
       <c r="D701" s="8"/>
     </row>
     <row r="702" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A702"/>
+      <c r="A702" s="21" t="s">
+        <v>696</v>
+      </c>
       <c r="D702" s="8"/>
     </row>
     <row r="703" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A703"/>
+      <c r="A703" s="21" t="s">
+        <v>697</v>
+      </c>
       <c r="D703" s="8"/>
     </row>
     <row r="704" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A704"/>
+      <c r="A704" s="21" t="s">
+        <v>698</v>
+      </c>
       <c r="D704" s="8"/>
     </row>
     <row r="705" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A705"/>
+      <c r="A705" s="21" t="s">
+        <v>699</v>
+      </c>
       <c r="D705" s="8"/>
     </row>
     <row r="706" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A706"/>
+      <c r="A706" s="21" t="s">
+        <v>700</v>
+      </c>
       <c r="D706" s="8"/>
     </row>
     <row r="707" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A707"/>
+      <c r="A707" s="21" t="s">
+        <v>701</v>
+      </c>
       <c r="D707" s="8"/>
     </row>
     <row r="708" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A708"/>
+      <c r="A708" s="21" t="s">
+        <v>702</v>
+      </c>
       <c r="D708" s="8"/>
     </row>
     <row r="709" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A709"/>
+      <c r="A709" s="21" t="s">
+        <v>703</v>
+      </c>
       <c r="D709" s="8"/>
     </row>
     <row r="710" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A710"/>
+      <c r="A710" s="21" t="s">
+        <v>704</v>
+      </c>
       <c r="D710" s="8"/>
     </row>
     <row r="711" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A711"/>
+      <c r="A711" s="21" t="s">
+        <v>705</v>
+      </c>
       <c r="D711" s="8"/>
     </row>
     <row r="712" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A712"/>
+      <c r="A712" s="21" t="s">
+        <v>706</v>
+      </c>
       <c r="D712" s="8"/>
     </row>
     <row r="713" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A713"/>
+      <c r="A713" s="21" t="s">
+        <v>707</v>
+      </c>
       <c r="D713" s="8"/>
     </row>
     <row r="714" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A714"/>
+      <c r="A714" s="21" t="s">
+        <v>708</v>
+      </c>
       <c r="D714" s="8"/>
     </row>
     <row r="715" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A715"/>
+      <c r="A715" s="21" t="s">
+        <v>709</v>
+      </c>
       <c r="D715" s="8"/>
     </row>
     <row r="716" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A716"/>
+      <c r="A716" s="21" t="s">
+        <v>710</v>
+      </c>
       <c r="D716" s="8"/>
     </row>
     <row r="717" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A717"/>
+      <c r="A717" s="21" t="s">
+        <v>711</v>
+      </c>
       <c r="D717" s="8"/>
     </row>
     <row r="718" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A718"/>
+      <c r="A718" s="21" t="s">
+        <v>712</v>
+      </c>
       <c r="D718" s="8"/>
     </row>
     <row r="719" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A719"/>
+      <c r="A719" s="21" t="s">
+        <v>713</v>
+      </c>
       <c r="D719" s="8"/>
     </row>
     <row r="720" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A720"/>
+      <c r="A720" s="21" t="s">
+        <v>714</v>
+      </c>
       <c r="D720" s="8"/>
     </row>
     <row r="721" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A721"/>
+      <c r="A721" s="21" t="s">
+        <v>715</v>
+      </c>
       <c r="D721" s="8"/>
     </row>
     <row r="722" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A722"/>
+      <c r="A722" s="21" t="s">
+        <v>716</v>
+      </c>
       <c r="D722" s="8"/>
     </row>
     <row r="723" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A723"/>
+      <c r="A723" s="21" t="s">
+        <v>717</v>
+      </c>
       <c r="D723" s="8"/>
     </row>
     <row r="724" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A724"/>
+      <c r="A724" s="21" t="s">
+        <v>718</v>
+      </c>
       <c r="D724" s="8"/>
     </row>
     <row r="725" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A725"/>
+      <c r="A725" s="21" t="s">
+        <v>719</v>
+      </c>
       <c r="D725" s="8"/>
     </row>
     <row r="726" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A726"/>
+      <c r="A726" s="21" t="s">
+        <v>720</v>
+      </c>
       <c r="D726" s="8"/>
     </row>
     <row r="727" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A727"/>
+      <c r="A727" s="21" t="s">
+        <v>721</v>
+      </c>
       <c r="D727" s="8"/>
     </row>
     <row r="728" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A728"/>
+      <c r="A728" s="21" t="s">
+        <v>722</v>
+      </c>
       <c r="D728" s="8"/>
     </row>
     <row r="729" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A729"/>
+      <c r="A729" s="21" t="s">
+        <v>723</v>
+      </c>
       <c r="D729" s="8"/>
     </row>
     <row r="730" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A730"/>
+      <c r="A730" s="21" t="s">
+        <v>724</v>
+      </c>
       <c r="D730" s="8"/>
     </row>
     <row r="731" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A731"/>
+      <c r="A731" s="21" t="s">
+        <v>725</v>
+      </c>
       <c r="D731" s="8"/>
     </row>
     <row r="732" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A732"/>
+      <c r="A732" s="21" t="s">
+        <v>726</v>
+      </c>
       <c r="D732" s="8"/>
     </row>
     <row r="733" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A733"/>
+      <c r="A733" s="21" t="s">
+        <v>727</v>
+      </c>
       <c r="D733" s="8"/>
     </row>
     <row r="734" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A734"/>
+      <c r="A734" s="21" t="s">
+        <v>728</v>
+      </c>
       <c r="D734" s="8"/>
     </row>
     <row r="735" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A735"/>
+      <c r="A735" s="21" t="s">
+        <v>729</v>
+      </c>
       <c r="D735" s="8"/>
     </row>
     <row r="736" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A736"/>
+      <c r="A736" s="21" t="s">
+        <v>730</v>
+      </c>
       <c r="D736" s="8"/>
     </row>
     <row r="737" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A737"/>
+      <c r="A737" s="21" t="s">
+        <v>731</v>
+      </c>
       <c r="D737" s="8"/>
     </row>
     <row r="738" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A738"/>
+      <c r="A738" s="21" t="s">
+        <v>732</v>
+      </c>
       <c r="D738" s="8"/>
     </row>
     <row r="739" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A739"/>
+      <c r="A739" s="21" t="s">
+        <v>733</v>
+      </c>
       <c r="D739" s="8"/>
     </row>
     <row r="740" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A740"/>
+      <c r="A740" s="21" t="s">
+        <v>734</v>
+      </c>
       <c r="D740" s="8"/>
     </row>
     <row r="741" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A741"/>
+      <c r="A741" s="21" t="s">
+        <v>735</v>
+      </c>
       <c r="D741" s="8"/>
     </row>
     <row r="742" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A742"/>
+      <c r="A742" s="21" t="s">
+        <v>736</v>
+      </c>
       <c r="D742" s="8"/>
     </row>
     <row r="743" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A743"/>
+      <c r="A743" s="21" t="s">
+        <v>737</v>
+      </c>
       <c r="D743" s="8"/>
     </row>
     <row r="744" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A744"/>
+      <c r="A744" s="21" t="s">
+        <v>738</v>
+      </c>
       <c r="D744" s="8"/>
     </row>
     <row r="745" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A745"/>
+      <c r="A745" s="21" t="s">
+        <v>739</v>
+      </c>
       <c r="D745" s="8"/>
     </row>
     <row r="746" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A746"/>
+      <c r="A746" s="21" t="s">
+        <v>740</v>
+      </c>
       <c r="D746" s="8"/>
     </row>
     <row r="747" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A747"/>
+      <c r="A747" s="21" t="s">
+        <v>741</v>
+      </c>
       <c r="D747" s="8"/>
     </row>
     <row r="748" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A748"/>
+      <c r="A748" s="21" t="s">
+        <v>742</v>
+      </c>
       <c r="D748" s="8"/>
     </row>
     <row r="749" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A749"/>
+      <c r="A749" s="21" t="s">
+        <v>743</v>
+      </c>
       <c r="D749" s="8"/>
     </row>
     <row r="750" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A750"/>
+      <c r="A750" s="21" t="s">
+        <v>744</v>
+      </c>
       <c r="D750" s="8"/>
     </row>
     <row r="751" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A751"/>
+      <c r="A751" s="21" t="s">
+        <v>745</v>
+      </c>
       <c r="D751" s="8"/>
     </row>
     <row r="752" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A752"/>
+      <c r="A752" s="21" t="s">
+        <v>746</v>
+      </c>
       <c r="D752" s="8"/>
     </row>
     <row r="753" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A753"/>
+      <c r="A753" s="21" t="s">
+        <v>747</v>
+      </c>
       <c r="D753" s="8"/>
     </row>
     <row r="754" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A754"/>
+      <c r="A754" s="21" t="s">
+        <v>748</v>
+      </c>
       <c r="D754" s="8"/>
     </row>
     <row r="755" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A755"/>
+      <c r="A755" s="21" t="s">
+        <v>749</v>
+      </c>
       <c r="D755" s="8"/>
     </row>
     <row r="756" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A756"/>
+      <c r="A756" s="21" t="s">
+        <v>750</v>
+      </c>
       <c r="D756" s="8"/>
     </row>
     <row r="757" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A757"/>
+      <c r="A757" s="21" t="s">
+        <v>751</v>
+      </c>
       <c r="D757" s="8"/>
     </row>
     <row r="758" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A758"/>
+      <c r="A758" s="21" t="s">
+        <v>752</v>
+      </c>
       <c r="D758" s="8"/>
     </row>
     <row r="759" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A759"/>
+      <c r="A759" s="21" t="s">
+        <v>753</v>
+      </c>
       <c r="D759" s="8"/>
     </row>
     <row r="760" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A760"/>
+      <c r="A760" s="21" t="s">
+        <v>754</v>
+      </c>
       <c r="D760" s="8"/>
     </row>
     <row r="761" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A761"/>
+      <c r="A761" s="21" t="s">
+        <v>755</v>
+      </c>
       <c r="D761" s="8"/>
     </row>
     <row r="762" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A762"/>
+      <c r="A762" s="21" t="s">
+        <v>756</v>
+      </c>
       <c r="D762" s="8"/>
     </row>
     <row r="763" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A763"/>
+      <c r="A763" s="21" t="s">
+        <v>757</v>
+      </c>
       <c r="D763" s="8"/>
     </row>
     <row r="764" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A764"/>
+      <c r="A764" s="21" t="s">
+        <v>758</v>
+      </c>
       <c r="D764" s="8"/>
     </row>
     <row r="765" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A765"/>
+      <c r="A765" s="21" t="s">
+        <v>759</v>
+      </c>
       <c r="D765" s="8"/>
     </row>
     <row r="766" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A766"/>
+      <c r="A766" s="21" t="s">
+        <v>760</v>
+      </c>
       <c r="D766" s="8"/>
     </row>
     <row r="767" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A767"/>
+      <c r="A767" s="21" t="s">
+        <v>761</v>
+      </c>
       <c r="D767" s="8"/>
     </row>
     <row r="768" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A768"/>
+      <c r="A768" s="21" t="s">
+        <v>762</v>
+      </c>
       <c r="D768" s="8"/>
     </row>
     <row r="769" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A769"/>
+      <c r="A769" s="21" t="s">
+        <v>763</v>
+      </c>
       <c r="D769" s="8"/>
     </row>
     <row r="770" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A770"/>
+      <c r="A770" s="21" t="s">
+        <v>764</v>
+      </c>
       <c r="D770" s="8"/>
     </row>
     <row r="771" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A771"/>
+      <c r="A771" s="21" t="s">
+        <v>765</v>
+      </c>
       <c r="D771" s="8"/>
     </row>
     <row r="772" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A772"/>
+      <c r="A772" s="21" t="s">
+        <v>766</v>
+      </c>
       <c r="D772" s="8"/>
     </row>
     <row r="773" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A773"/>
+      <c r="A773" s="21" t="s">
+        <v>767</v>
+      </c>
       <c r="D773" s="8"/>
     </row>
     <row r="774" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A774"/>
+      <c r="A774" s="21" t="s">
+        <v>768</v>
+      </c>
       <c r="D774" s="8"/>
     </row>
     <row r="775" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A775"/>
+      <c r="A775" s="21" t="s">
+        <v>769</v>
+      </c>
       <c r="D775" s="8"/>
     </row>
     <row r="776" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A776"/>
+      <c r="A776" s="21" t="s">
+        <v>770</v>
+      </c>
       <c r="D776" s="8"/>
     </row>
     <row r="777" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A777"/>
+      <c r="A777" s="21" t="s">
+        <v>771</v>
+      </c>
       <c r="D777" s="8"/>
     </row>
     <row r="778" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A778"/>
+      <c r="A778" s="21" t="s">
+        <v>772</v>
+      </c>
       <c r="D778" s="8"/>
     </row>
     <row r="779" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A779"/>
+      <c r="A779" s="21" t="s">
+        <v>773</v>
+      </c>
       <c r="D779" s="8"/>
     </row>
     <row r="780" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A780"/>
+      <c r="A780" s="21" t="s">
+        <v>774</v>
+      </c>
       <c r="D780" s="8"/>
     </row>
     <row r="781" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A781"/>
+      <c r="A781" s="21" t="s">
+        <v>775</v>
+      </c>
       <c r="D781" s="8"/>
     </row>
     <row r="782" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A782"/>
+      <c r="A782" s="21" t="s">
+        <v>776</v>
+      </c>
       <c r="D782" s="8"/>
     </row>
     <row r="783" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A783"/>
+      <c r="A783" s="21" t="s">
+        <v>777</v>
+      </c>
       <c r="D783" s="8"/>
     </row>
     <row r="784" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A784"/>
+      <c r="A784" s="21" t="s">
+        <v>778</v>
+      </c>
       <c r="D784" s="8"/>
     </row>
     <row r="785" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A785"/>
+      <c r="A785" s="21" t="s">
+        <v>779</v>
+      </c>
       <c r="D785" s="8"/>
     </row>
     <row r="786" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A786"/>
+      <c r="A786" s="21" t="s">
+        <v>780</v>
+      </c>
       <c r="D786" s="8"/>
     </row>
     <row r="787" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A787"/>
+      <c r="A787" s="21" t="s">
+        <v>781</v>
+      </c>
       <c r="D787" s="8"/>
     </row>
     <row r="788" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A788"/>
+      <c r="A788" s="21" t="s">
+        <v>782</v>
+      </c>
       <c r="D788" s="8"/>
     </row>
     <row r="789" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A789"/>
+      <c r="A789" s="21" t="s">
+        <v>783</v>
+      </c>
       <c r="D789" s="8"/>
     </row>
     <row r="790" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A790"/>
+      <c r="A790" s="21" t="s">
+        <v>784</v>
+      </c>
       <c r="D790" s="8"/>
     </row>
     <row r="791" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A791"/>
+      <c r="A791" s="21" t="s">
+        <v>785</v>
+      </c>
       <c r="D791" s="8"/>
     </row>
     <row r="792" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A792"/>
+      <c r="A792" s="21" t="s">
+        <v>786</v>
+      </c>
       <c r="D792" s="8"/>
     </row>
     <row r="793" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A793"/>
+      <c r="A793" s="21" t="s">
+        <v>787</v>
+      </c>
       <c r="D793" s="8"/>
     </row>
     <row r="794" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A794"/>
+      <c r="A794" s="21" t="s">
+        <v>788</v>
+      </c>
       <c r="D794" s="8"/>
     </row>
     <row r="795" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A795"/>
+      <c r="A795" s="21" t="s">
+        <v>789</v>
+      </c>
       <c r="D795" s="8"/>
     </row>
     <row r="796" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A796"/>
+      <c r="A796" s="21" t="s">
+        <v>790</v>
+      </c>
       <c r="D796" s="8"/>
     </row>
     <row r="797" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A797"/>
+      <c r="A797" s="21" t="s">
+        <v>791</v>
+      </c>
       <c r="D797" s="8"/>
     </row>
     <row r="798" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A798"/>
+      <c r="A798" s="21" t="s">
+        <v>791</v>
+      </c>
       <c r="D798" s="8"/>
     </row>
     <row r="799" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A799"/>
+      <c r="A799" s="21" t="s">
+        <v>577</v>
+      </c>
       <c r="D799" s="8"/>
     </row>
     <row r="800" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A800"/>
+      <c r="A800" s="21" t="s">
+        <v>792</v>
+      </c>
       <c r="D800" s="8"/>
     </row>
     <row r="801" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A801"/>
+      <c r="A801" s="21" t="s">
+        <v>793</v>
+      </c>
       <c r="D801" s="8"/>
     </row>
     <row r="802" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A802"/>
+      <c r="A802" s="21" t="s">
+        <v>794</v>
+      </c>
       <c r="D802" s="8"/>
     </row>
     <row r="803" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A803"/>
+      <c r="A803" s="21" t="s">
+        <v>795</v>
+      </c>
       <c r="D803" s="8"/>
     </row>
     <row r="804" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A804"/>
+      <c r="A804" s="21" t="s">
+        <v>796</v>
+      </c>
       <c r="D804" s="8"/>
     </row>
     <row r="805" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A805"/>
+      <c r="A805" s="21" t="s">
+        <v>797</v>
+      </c>
       <c r="D805" s="8"/>
     </row>
     <row r="806" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A806"/>
+      <c r="A806" s="21" t="s">
+        <v>798</v>
+      </c>
       <c r="D806" s="8"/>
     </row>
     <row r="807" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A807"/>
+      <c r="A807" s="21" t="s">
+        <v>799</v>
+      </c>
       <c r="D807" s="8"/>
     </row>
     <row r="808" spans="1:4" x14ac:dyDescent="0.2">
@@ -8918,38 +12888,38 @@
       <c r="D1942" s="8"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="A2">
+    <cfRule type="duplicateValues" dxfId="10" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="duplicateValues" dxfId="9" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A4">
+    <cfRule type="duplicateValues" dxfId="8" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A1943:A1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="118"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11">
-    <cfRule type="duplicateValues" dxfId="9" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="125"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E19">
-    <cfRule type="duplicateValues" dxfId="8" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="124"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E24">
-    <cfRule type="duplicateValues" dxfId="7" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="123"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E29">
-    <cfRule type="duplicateValues" dxfId="6" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="122"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E33">
-    <cfRule type="duplicateValues" dxfId="5" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="121"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E37">
-    <cfRule type="duplicateValues" dxfId="4" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="120"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G73">
-    <cfRule type="duplicateValues" dxfId="3" priority="119"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A3">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="119"/>
   </conditionalFormatting>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
